--- a/SourceData/globals/GBModData.xlsx
+++ b/SourceData/globals/GBModData.xlsx
@@ -1,19 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25F1EB00-253B-42EF-97EC-571CD6BCDA07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E59839D0-76E9-4BA5-A26C-2F6E54EC14EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="517" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="517" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CountryMaster" sheetId="1" r:id="rId1"/>
-    <sheet name="WPP" sheetId="2" r:id="rId2"/>
-    <sheet name="GBD" sheetId="3" r:id="rId3"/>
-    <sheet name="DisabilityWeights" sheetId="4" r:id="rId4"/>
-    <sheet name="Revision Log" sheetId="5" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="6" r:id="rId2"/>
+    <sheet name="WPP" sheetId="2" r:id="rId3"/>
+    <sheet name="GBD" sheetId="3" r:id="rId4"/>
+    <sheet name="DisabilityWeights" sheetId="4" r:id="rId5"/>
+    <sheet name="Revision Log" sheetId="5" r:id="rId6"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId7"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -35,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3961" uniqueCount="1495">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4379" uniqueCount="1496">
   <si>
     <t>Country Code</t>
   </si>
@@ -4520,6 +4524,9 @@
   </si>
   <si>
     <t>1994 DHS, 1999 DHS, 2005 DHS, 2009 MICS, 2010 DHS, 2014 MICS, 2015 DHS</t>
+  </si>
+  <si>
+    <t>UNAIDS 2026</t>
   </si>
 </sst>
 </file>
@@ -4607,6 +4614,4411 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="All Data"/>
+      <sheetName val="All Data (Uninterpolated)"/>
+      <sheetName val="MAR"/>
+      <sheetName val="MAR (Uninterpolated)"/>
+      <sheetName val="MARUMSA"/>
+      <sheetName val="MARUMSA (Uninterpolated)"/>
+      <sheetName val="Proxies"/>
+      <sheetName val="Single Year Data"/>
+      <sheetName val="Sources"/>
+      <sheetName val="Public Notes"/>
+      <sheetName val="Avenir Notes"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8">
+        <row r="1">
+          <cell r="A1" t="str">
+            <v>ISOCode</v>
+          </cell>
+          <cell r="B1" t="str">
+            <v>ISOAlph</v>
+          </cell>
+          <cell r="C1" t="str">
+            <v>Type</v>
+          </cell>
+          <cell r="D1" t="str">
+            <v>Note_Mar</v>
+          </cell>
+          <cell r="E1" t="str">
+            <v>Note_MarUMSA</v>
+          </cell>
+          <cell r="F1" t="str">
+            <v>Note_All</v>
+          </cell>
+          <cell r="G1" t="str">
+            <v>ProxyNote_MAR</v>
+          </cell>
+          <cell r="H1" t="str">
+            <v>ProxyNote_MARUMSA</v>
+          </cell>
+          <cell r="I1" t="str">
+            <v>ProxyNote_All</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="A2">
+            <v>4</v>
+          </cell>
+          <cell r="B2" t="str">
+            <v>AFG</v>
+          </cell>
+          <cell r="C2" t="str">
+            <v>Afghanistan</v>
+          </cell>
+          <cell r="D2" t="str">
+            <v>2010 MICS, 2015 DHS</v>
+          </cell>
+          <cell r="E2" t="str">
+            <v>2010 MICS, 2015 DHS</v>
+          </cell>
+          <cell r="F2" t="str">
+            <v>2010 MICS, 2015 DHS</v>
+          </cell>
+          <cell r="J2" t="str">
+            <v>2010 MICS, 2015 DHS</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="A3">
+            <v>8</v>
+          </cell>
+          <cell r="B3" t="str">
+            <v>ALB</v>
+          </cell>
+          <cell r="C3" t="str">
+            <v>Albania</v>
+          </cell>
+          <cell r="D3" t="str">
+            <v>2000 MICS, 2005 MICS, 2008 DHS, 2017 DHS</v>
+          </cell>
+          <cell r="E3" t="str">
+            <v>2008 DHS, 2017 DHS</v>
+          </cell>
+          <cell r="F3" t="str">
+            <v>2005 MICS, 2008 DHS, 2017 DHS</v>
+          </cell>
+          <cell r="J3" t="str">
+            <v>2005 MICS, 2008 DHS, 2017 DHS</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="A4">
+            <v>12</v>
+          </cell>
+          <cell r="B4" t="str">
+            <v>DZA</v>
+          </cell>
+          <cell r="C4" t="str">
+            <v>Algeria</v>
+          </cell>
+          <cell r="D4" t="str">
+            <v>2012 MICS, 2018 MICS</v>
+          </cell>
+          <cell r="E4" t="str">
+            <v>2012 MICS, 2018 MICS</v>
+          </cell>
+          <cell r="F4" t="str">
+            <v>2012 MICS, 2018 MICS</v>
+          </cell>
+          <cell r="G4" t="str">
+            <v>Some data from proxy country: 818</v>
+          </cell>
+          <cell r="H4" t="str">
+            <v>Some data from proxy country: 818</v>
+          </cell>
+          <cell r="I4" t="str">
+            <v>Some data from proxy country: 818</v>
+          </cell>
+          <cell r="J4" t="str">
+            <v>2012 MICS, 2018 MICS Some data from proxy country: Egypt</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="A5">
+            <v>24</v>
+          </cell>
+          <cell r="B5" t="str">
+            <v>AGO</v>
+          </cell>
+          <cell r="C5" t="str">
+            <v>Angola</v>
+          </cell>
+          <cell r="D5" t="str">
+            <v>2001 MICS, 2015 DHS, 2023 DHS</v>
+          </cell>
+          <cell r="E5" t="str">
+            <v>2015 DHS, 2023 DHS</v>
+          </cell>
+          <cell r="F5" t="str">
+            <v>2001 MICS, 2015 DHS, 2023 DHS</v>
+          </cell>
+          <cell r="J5" t="str">
+            <v>2001 MICS, 2015 DHS, 2023 DHS</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="A6">
+            <v>28</v>
+          </cell>
+          <cell r="B6" t="str">
+            <v>ATG</v>
+          </cell>
+          <cell r="C6" t="str">
+            <v>Antigua and Barbuda</v>
+          </cell>
+          <cell r="G6" t="str">
+            <v>Some data from proxy country: 214</v>
+          </cell>
+          <cell r="H6" t="str">
+            <v>Some data from proxy country: 214</v>
+          </cell>
+          <cell r="I6" t="str">
+            <v>Some data from proxy country: 214</v>
+          </cell>
+          <cell r="J6" t="str">
+            <v>Some data from proxy country: Dominican Republic</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="A7">
+            <v>32</v>
+          </cell>
+          <cell r="B7" t="str">
+            <v>ARG</v>
+          </cell>
+          <cell r="C7" t="str">
+            <v>Argentina</v>
+          </cell>
+          <cell r="D7" t="str">
+            <v>2019 MICS</v>
+          </cell>
+          <cell r="E7" t="str">
+            <v>2019 MICS</v>
+          </cell>
+          <cell r="F7" t="str">
+            <v>2011 MICS, 2019 MICS</v>
+          </cell>
+          <cell r="G7" t="str">
+            <v>Some data from proxy country: 76</v>
+          </cell>
+          <cell r="H7" t="str">
+            <v>Some data from proxy country: 76</v>
+          </cell>
+          <cell r="I7" t="str">
+            <v>Some data from proxy country: 76</v>
+          </cell>
+          <cell r="J7" t="str">
+            <v>2011 MICS, 2019 MICS Some data from proxy country: Brazil</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="A8">
+            <v>51</v>
+          </cell>
+          <cell r="B8" t="str">
+            <v>ARM</v>
+          </cell>
+          <cell r="C8" t="str">
+            <v>Armenia</v>
+          </cell>
+          <cell r="D8" t="str">
+            <v>2000 DHS, 2005 DHS, 2010 DHS, 2015 DHS</v>
+          </cell>
+          <cell r="E8" t="str">
+            <v>2000 DHS, 2005 DHS, 2010 DHS, 2015 DHS</v>
+          </cell>
+          <cell r="F8" t="str">
+            <v>2000 DHS, 2005 DHS, 2010 DHS, 2015 DHS</v>
+          </cell>
+          <cell r="J8" t="str">
+            <v>2000 DHS, 2005 DHS, 2010 DHS, 2015 DHS</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="A9">
+            <v>533</v>
+          </cell>
+          <cell r="B9" t="str">
+            <v>ABW</v>
+          </cell>
+          <cell r="C9" t="str">
+            <v>Aruba</v>
+          </cell>
+          <cell r="G9" t="str">
+            <v>Some data from proxy country: 214</v>
+          </cell>
+          <cell r="H9" t="str">
+            <v>Some data from proxy country: 214</v>
+          </cell>
+          <cell r="I9" t="str">
+            <v>Some data from proxy country: 214</v>
+          </cell>
+          <cell r="J9" t="str">
+            <v>Some data from proxy country: Dominican Republic</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="A10">
+            <v>31</v>
+          </cell>
+          <cell r="B10" t="str">
+            <v>AZE</v>
+          </cell>
+          <cell r="C10" t="str">
+            <v>Azerbaijan</v>
+          </cell>
+          <cell r="D10" t="str">
+            <v>2000 MICS, 2006 DHS, 2023 MICS</v>
+          </cell>
+          <cell r="E10" t="str">
+            <v>2000 MICS, 2006 DHS, 2023 MICS</v>
+          </cell>
+          <cell r="F10" t="str">
+            <v>2000 MICS, 2006 DHS, 2023 MICS</v>
+          </cell>
+          <cell r="J10" t="str">
+            <v>2000 MICS, 2006 DHS, 2023 MICS</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="A11">
+            <v>44</v>
+          </cell>
+          <cell r="B11" t="str">
+            <v>BHS</v>
+          </cell>
+          <cell r="C11" t="str">
+            <v>Bahamas</v>
+          </cell>
+          <cell r="G11" t="str">
+            <v>Some data from proxy country: 214</v>
+          </cell>
+          <cell r="H11" t="str">
+            <v>Some data from proxy country: 214</v>
+          </cell>
+          <cell r="I11" t="str">
+            <v>Some data from proxy country: 214</v>
+          </cell>
+          <cell r="J11" t="str">
+            <v>Some data from proxy country: Dominican Republic</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="A12">
+            <v>48</v>
+          </cell>
+          <cell r="B12" t="str">
+            <v>BHR</v>
+          </cell>
+          <cell r="C12" t="str">
+            <v>Bahrain</v>
+          </cell>
+          <cell r="G12" t="str">
+            <v>Some data from proxy country: 764</v>
+          </cell>
+          <cell r="H12" t="str">
+            <v>Some data from proxy country: 704</v>
+          </cell>
+          <cell r="I12" t="str">
+            <v>Some data from proxy country: 764</v>
+          </cell>
+          <cell r="J12" t="str">
+            <v>Some data from proxy country: Thailand</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="A13">
+            <v>50</v>
+          </cell>
+          <cell r="B13" t="str">
+            <v>BGD</v>
+          </cell>
+          <cell r="C13" t="str">
+            <v>Bangladesh</v>
+          </cell>
+          <cell r="D13" t="str">
+            <v>1993 DHS, 1996 DHS, 1999 DHS, 2004 DHS, 2007 DHS, 2011 DHS, 2012 MICS, 2014 DHS, 2017 DHS, 2019 MICS, 2022 DHS</v>
+          </cell>
+          <cell r="E13" t="str">
+            <v>1993 DHS, 1996 DHS, 1999 DHS, 2004 DHS, 2007 DHS, 2011 DHS, 2012 MICS, 2014 DHS, 2017 DHS, 2019 MICS, 2022 DHS</v>
+          </cell>
+          <cell r="F13" t="str">
+            <v>1993 DHS, 1996 DHS, 1999 DHS, 2004 DHS, 2007 DHS, 2011 DHS, 2012 MICS, 2014 DHS, 2017 DHS, 2019 MICS, 2022 DHS</v>
+          </cell>
+          <cell r="J13" t="str">
+            <v>1993 DHS, 1996 DHS, 1999 DHS, 2004 DHS, 2007 DHS, 2011 DHS, 2012 MICS, 2014 DHS, 2017 DHS, 2019 MICS, 2022 DHS</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="A14">
+            <v>52</v>
+          </cell>
+          <cell r="B14" t="str">
+            <v>BRB</v>
+          </cell>
+          <cell r="C14" t="str">
+            <v>Barbados</v>
+          </cell>
+          <cell r="D14" t="str">
+            <v>2012 MICS</v>
+          </cell>
+          <cell r="E14" t="str">
+            <v>2012 MICS</v>
+          </cell>
+          <cell r="F14" t="str">
+            <v>2012 MICS</v>
+          </cell>
+          <cell r="G14" t="str">
+            <v>Some data from proxy country: 214</v>
+          </cell>
+          <cell r="H14" t="str">
+            <v>Some data from proxy country: 214</v>
+          </cell>
+          <cell r="I14" t="str">
+            <v>Some data from proxy country: 214</v>
+          </cell>
+          <cell r="J14" t="str">
+            <v>2012 MICS Some data from proxy country: Dominican Republic</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="A15">
+            <v>112</v>
+          </cell>
+          <cell r="B15" t="str">
+            <v>BLR</v>
+          </cell>
+          <cell r="C15" t="str">
+            <v>Belarus</v>
+          </cell>
+          <cell r="D15" t="str">
+            <v>2005 MICS, 2012 MICS, 2019 MICS</v>
+          </cell>
+          <cell r="E15" t="str">
+            <v>2012 MICS, 2019 MICS</v>
+          </cell>
+          <cell r="F15" t="str">
+            <v>2005 MICS, 2012 MICS, 2019 MICS</v>
+          </cell>
+          <cell r="G15" t="str">
+            <v>Some data from proxy country: 804</v>
+          </cell>
+          <cell r="H15" t="str">
+            <v>Some data from proxy country: 804</v>
+          </cell>
+          <cell r="I15" t="str">
+            <v>Some data from proxy country: 804</v>
+          </cell>
+          <cell r="J15" t="str">
+            <v>2005 MICS, 2012 MICS, 2019 MICS Some data from proxy country: Ukraine</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="A16">
+            <v>84</v>
+          </cell>
+          <cell r="B16" t="str">
+            <v>BLZ</v>
+          </cell>
+          <cell r="C16" t="str">
+            <v>Belize</v>
+          </cell>
+          <cell r="D16" t="str">
+            <v>2011 MICS, 2015 MICS</v>
+          </cell>
+          <cell r="E16" t="str">
+            <v>2011 MICS, 2015 MICS</v>
+          </cell>
+          <cell r="F16" t="str">
+            <v>2006 MICS, 2011 MICS, 2015 MICS</v>
+          </cell>
+          <cell r="G16" t="str">
+            <v>Some data from proxy country: 320</v>
+          </cell>
+          <cell r="H16" t="str">
+            <v>Some data from proxy country: 320</v>
+          </cell>
+          <cell r="I16" t="str">
+            <v>Some data from proxy country: 320</v>
+          </cell>
+          <cell r="J16" t="str">
+            <v>2006 MICS, 2011 MICS, 2015 MICS Some data from proxy country: Guatemala</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="A17">
+            <v>204</v>
+          </cell>
+          <cell r="B17" t="str">
+            <v>BEN</v>
+          </cell>
+          <cell r="C17" t="str">
+            <v>Benin</v>
+          </cell>
+          <cell r="D17" t="str">
+            <v>1996 DHS, 2001 DHS, 2006 DHS, 2011 DHS, 2014 MICS, 2017 DHS, 2021 MICS</v>
+          </cell>
+          <cell r="E17" t="str">
+            <v>1996 DHS, 2001 DHS, 2006 DHS, 2011 DHS, 2014 MICS, 2017 DHS</v>
+          </cell>
+          <cell r="F17" t="str">
+            <v>1996 DHS, 2001 DHS, 2006 DHS, 2011 DHS, 2014 MICS, 2017 DHS, 2021 MICS</v>
+          </cell>
+          <cell r="J17" t="str">
+            <v>1996 DHS, 2001 DHS, 2006 DHS, 2011 DHS, 2014 MICS, 2017 DHS, 2021 MICS</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="A18">
+            <v>64</v>
+          </cell>
+          <cell r="B18" t="str">
+            <v>BTN</v>
+          </cell>
+          <cell r="C18" t="str">
+            <v>Bhutan</v>
+          </cell>
+          <cell r="D18" t="str">
+            <v>2010 MICS</v>
+          </cell>
+          <cell r="E18" t="str">
+            <v>2010 MICS</v>
+          </cell>
+          <cell r="F18" t="str">
+            <v>2010 MICS</v>
+          </cell>
+          <cell r="G18" t="str">
+            <v>Some data from proxy country: 524</v>
+          </cell>
+          <cell r="H18" t="str">
+            <v>Some data from proxy country: 524</v>
+          </cell>
+          <cell r="I18" t="str">
+            <v>Some data from proxy country: 524</v>
+          </cell>
+          <cell r="J18" t="str">
+            <v>2010 MICS Some data from proxy country: Nepal</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="A19">
+            <v>68</v>
+          </cell>
+          <cell r="B19" t="str">
+            <v>BOL</v>
+          </cell>
+          <cell r="C19" t="str">
+            <v>Bolivia (Plurinational State of)</v>
+          </cell>
+          <cell r="D19" t="str">
+            <v>1994 DHS, 1998 DHS, 2000 MICS, 2003 DHS, 2008 DHS</v>
+          </cell>
+          <cell r="E19" t="str">
+            <v>1994 DHS, 1998 DHS, 2003 DHS, 2008 DHS</v>
+          </cell>
+          <cell r="F19" t="str">
+            <v>1994 DHS, 1998 DHS, 2003 DHS, 2008 DHS</v>
+          </cell>
+          <cell r="J19" t="str">
+            <v>1994 DHS, 1998 DHS, 2003 DHS, 2008 DHS</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="A20">
+            <v>70</v>
+          </cell>
+          <cell r="B20" t="str">
+            <v>BIH</v>
+          </cell>
+          <cell r="C20" t="str">
+            <v>Bosnia and Herzegovina</v>
+          </cell>
+          <cell r="D20" t="str">
+            <v>2000 MICS, 2006 MICS, 2011 MICS</v>
+          </cell>
+          <cell r="E20" t="str">
+            <v>2011 MICS</v>
+          </cell>
+          <cell r="F20" t="str">
+            <v>2006 MICS, 2011 MICS</v>
+          </cell>
+          <cell r="G20" t="str">
+            <v>Some data from proxy country: 498</v>
+          </cell>
+          <cell r="H20" t="str">
+            <v>Some data from proxy country: 498</v>
+          </cell>
+          <cell r="I20" t="str">
+            <v>Some data from proxy country: 498</v>
+          </cell>
+          <cell r="J20" t="str">
+            <v>2006 MICS, 2011 MICS Some data from proxy country: Moldova</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="A21">
+            <v>72</v>
+          </cell>
+          <cell r="B21" t="str">
+            <v>BWA</v>
+          </cell>
+          <cell r="C21" t="str">
+            <v>Botswana</v>
+          </cell>
+          <cell r="G21" t="str">
+            <v>Some data from proxy country: 516</v>
+          </cell>
+          <cell r="H21" t="str">
+            <v>Some data from proxy country: 516</v>
+          </cell>
+          <cell r="I21" t="str">
+            <v>Some data from proxy country: 516</v>
+          </cell>
+          <cell r="J21" t="str">
+            <v>Some data from proxy country: Namibia</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="A22">
+            <v>76</v>
+          </cell>
+          <cell r="B22" t="str">
+            <v>BRA</v>
+          </cell>
+          <cell r="C22" t="str">
+            <v>Brazil</v>
+          </cell>
+          <cell r="D22" t="str">
+            <v>1991 DHS, 1996 DHS</v>
+          </cell>
+          <cell r="E22" t="str">
+            <v>1991 DHS, 1996 DHS</v>
+          </cell>
+          <cell r="F22" t="str">
+            <v>1991 DHS, 1996 DHS</v>
+          </cell>
+          <cell r="J22" t="str">
+            <v>1991 DHS, 1996 DHS</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="A23">
+            <v>96</v>
+          </cell>
+          <cell r="B23" t="str">
+            <v>BRN</v>
+          </cell>
+          <cell r="C23" t="str">
+            <v>Brunei Darussalam</v>
+          </cell>
+          <cell r="G23" t="str">
+            <v>Some data from proxy country: 360</v>
+          </cell>
+          <cell r="H23" t="str">
+            <v>Some data from proxy country: 360</v>
+          </cell>
+          <cell r="I23" t="str">
+            <v>Some data from proxy country: 360</v>
+          </cell>
+          <cell r="J23" t="str">
+            <v>Some data from proxy country: Indonesia</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="A24">
+            <v>100</v>
+          </cell>
+          <cell r="B24" t="str">
+            <v>BGR</v>
+          </cell>
+          <cell r="C24" t="str">
+            <v>Bulgaria</v>
+          </cell>
+          <cell r="G24" t="str">
+            <v>Some data from proxy country: 804</v>
+          </cell>
+          <cell r="H24" t="str">
+            <v>Some data from proxy country: 804</v>
+          </cell>
+          <cell r="I24" t="str">
+            <v>Some data from proxy country: 804</v>
+          </cell>
+          <cell r="J24" t="str">
+            <v>Some data from proxy country: Ukraine</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="A25">
+            <v>854</v>
+          </cell>
+          <cell r="B25" t="str">
+            <v>BFA</v>
+          </cell>
+          <cell r="C25" t="str">
+            <v>Burkina Faso</v>
+          </cell>
+          <cell r="D25" t="str">
+            <v>1993 DHS, 1998 DHS, 2003 DHS, 2006 MICS, 2010 DHS, 2021 DHS</v>
+          </cell>
+          <cell r="E25" t="str">
+            <v>1993 DHS, 1998 DHS, 2003 DHS, 2010 DHS, 2021 DHS</v>
+          </cell>
+          <cell r="F25" t="str">
+            <v>1993 DHS, 1998 DHS, 2003 DHS, 2006 MICS, 2010 DHS, 2021 DHS</v>
+          </cell>
+          <cell r="J25" t="str">
+            <v>1993 DHS, 1998 DHS, 2003 DHS, 2006 MICS, 2010 DHS, 2021 DHS</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="A26">
+            <v>108</v>
+          </cell>
+          <cell r="B26" t="str">
+            <v>BDI</v>
+          </cell>
+          <cell r="C26" t="str">
+            <v>Burundi</v>
+          </cell>
+          <cell r="D26" t="str">
+            <v>2005 MICS, 2010 DHS, 2016 DHS</v>
+          </cell>
+          <cell r="E26" t="str">
+            <v>2010 DHS, 2016 DHS</v>
+          </cell>
+          <cell r="F26" t="str">
+            <v>2005 MICS, 2010 DHS, 2016 DHS</v>
+          </cell>
+          <cell r="J26" t="str">
+            <v>2005 MICS, 2010 DHS, 2016 DHS</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="A27">
+            <v>132</v>
+          </cell>
+          <cell r="B27" t="str">
+            <v>CPV</v>
+          </cell>
+          <cell r="C27" t="str">
+            <v>Cabo Verde</v>
+          </cell>
+          <cell r="G27" t="str">
+            <v>Some data from proxy country: 504</v>
+          </cell>
+          <cell r="H27" t="str">
+            <v>Some data from proxy country: 504</v>
+          </cell>
+          <cell r="I27" t="str">
+            <v>Some data from proxy country: 504</v>
+          </cell>
+          <cell r="J27" t="str">
+            <v>Some data from proxy country: Morocco</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="A28">
+            <v>116</v>
+          </cell>
+          <cell r="B28" t="str">
+            <v>KHM</v>
+          </cell>
+          <cell r="C28" t="str">
+            <v>Cambodia</v>
+          </cell>
+          <cell r="D28" t="str">
+            <v>2000 DHS, 2005 DHS, 2010 DHS, 2014 DHS, 2021 DHS</v>
+          </cell>
+          <cell r="E28" t="str">
+            <v>2000 DHS, 2005 DHS, 2010 DHS, 2014 DHS, 2021 DHS</v>
+          </cell>
+          <cell r="F28" t="str">
+            <v>2000 DHS, 2005 DHS, 2010 DHS, 2014 DHS, 2021 DHS</v>
+          </cell>
+          <cell r="J28" t="str">
+            <v>2000 DHS, 2005 DHS, 2010 DHS, 2014 DHS, 2021 DHS</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="A29">
+            <v>120</v>
+          </cell>
+          <cell r="B29" t="str">
+            <v>CMR</v>
+          </cell>
+          <cell r="C29" t="str">
+            <v>Cameroon</v>
+          </cell>
+          <cell r="D29" t="str">
+            <v>1991 DHS, 1998 DHS, 2000 MICS, 2004 DHS, 2006 MICS, 2011 DHS, 2014 MICS, 2018 DHS</v>
+          </cell>
+          <cell r="E29" t="str">
+            <v>1991 DHS, 1998 DHS, 2004 DHS, 2011 DHS, 2014 MICS, 2018 DHS</v>
+          </cell>
+          <cell r="F29" t="str">
+            <v>1991 DHS, 1998 DHS, 2004 DHS, 2006 MICS, 2011 DHS, 2014 MICS, 2018 DHS</v>
+          </cell>
+          <cell r="J29" t="str">
+            <v>1991 DHS, 1998 DHS, 2004 DHS, 2006 MICS, 2011 DHS, 2014 MICS, 2018 DHS</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="A30">
+            <v>140</v>
+          </cell>
+          <cell r="B30" t="str">
+            <v>CAF</v>
+          </cell>
+          <cell r="C30" t="str">
+            <v>Central African Republic</v>
+          </cell>
+          <cell r="D30" t="str">
+            <v>1994 DHS, 2000 MICS, 2006 MICS, 2010 MICS, 2018 MICS</v>
+          </cell>
+          <cell r="E30" t="str">
+            <v>1994 DHS, 2010 MICS, 2018 MICS</v>
+          </cell>
+          <cell r="F30" t="str">
+            <v>1994 DHS, 2010 MICS, 2018 MICS</v>
+          </cell>
+          <cell r="J30" t="str">
+            <v>1994 DHS, 2010 MICS, 2018 MICS</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="A31">
+            <v>148</v>
+          </cell>
+          <cell r="B31" t="str">
+            <v>TCD</v>
+          </cell>
+          <cell r="C31" t="str">
+            <v>Chad</v>
+          </cell>
+          <cell r="D31" t="str">
+            <v>1996 DHS, 2000 MICS, 2004 DHS, 2010 MICS, 2014 DHS, 2019 MICS</v>
+          </cell>
+          <cell r="E31" t="str">
+            <v>1996 DHS, 2004 DHS, 2010 MICS, 2014 DHS, 2019 MICS</v>
+          </cell>
+          <cell r="F31" t="str">
+            <v>1996 DHS, 2004 DHS, 2010 MICS, 2014 DHS, 2019 MICS</v>
+          </cell>
+          <cell r="J31" t="str">
+            <v>1996 DHS, 2004 DHS, 2010 MICS, 2014 DHS, 2019 MICS</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="A32">
+            <v>152</v>
+          </cell>
+          <cell r="B32" t="str">
+            <v>CHL</v>
+          </cell>
+          <cell r="C32" t="str">
+            <v>Chile</v>
+          </cell>
+          <cell r="G32" t="str">
+            <v>Some data from proxy country: 76</v>
+          </cell>
+          <cell r="H32" t="str">
+            <v>Some data from proxy country: 76</v>
+          </cell>
+          <cell r="I32" t="str">
+            <v>Some data from proxy country: 76</v>
+          </cell>
+          <cell r="J32" t="str">
+            <v>Some data from proxy country: Brazil</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="A33">
+            <v>156</v>
+          </cell>
+          <cell r="B33" t="str">
+            <v>CHN</v>
+          </cell>
+          <cell r="C33" t="str">
+            <v>China</v>
+          </cell>
+          <cell r="G33" t="str">
+            <v>Some data from proxy country: 704</v>
+          </cell>
+          <cell r="H33" t="str">
+            <v>Some data from proxy country: 704</v>
+          </cell>
+          <cell r="I33" t="str">
+            <v>Some data from proxy country: 704</v>
+          </cell>
+          <cell r="J33" t="str">
+            <v>Some data from proxy country: Viet Nam</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="A34">
+            <v>170</v>
+          </cell>
+          <cell r="B34" t="str">
+            <v>COL</v>
+          </cell>
+          <cell r="C34" t="str">
+            <v>Colombia</v>
+          </cell>
+          <cell r="D34" t="str">
+            <v>1990 DHS, 1995 DHS, 2000 DHS, 2005 DHS, 2010 DHS, 2015 DHS</v>
+          </cell>
+          <cell r="E34" t="str">
+            <v>1990 DHS, 1995 DHS, 2000 DHS, 2005 DHS, 2010 DHS, 2015 DHS</v>
+          </cell>
+          <cell r="F34" t="str">
+            <v>1990 DHS, 1995 DHS, 2000 DHS, 2005 DHS, 2010 DHS, 2015 DHS</v>
+          </cell>
+          <cell r="J34" t="str">
+            <v>1990 DHS, 1995 DHS, 2000 DHS, 2005 DHS, 2010 DHS, 2015 DHS</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="A35">
+            <v>174</v>
+          </cell>
+          <cell r="B35" t="str">
+            <v>COM</v>
+          </cell>
+          <cell r="C35" t="str">
+            <v>Comoros</v>
+          </cell>
+          <cell r="D35" t="str">
+            <v>1996 DHS, 2000 MICS, 2012 DHS, 2022 MICS</v>
+          </cell>
+          <cell r="E35" t="str">
+            <v>1996 DHS, 2012 DHS, 2022 MICS</v>
+          </cell>
+          <cell r="F35" t="str">
+            <v>1996 DHS, 2000 MICS, 2012 DHS, 2022 MICS</v>
+          </cell>
+          <cell r="J35" t="str">
+            <v>1996 DHS, 2000 MICS, 2012 DHS, 2022 MICS</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="A36">
+            <v>178</v>
+          </cell>
+          <cell r="B36" t="str">
+            <v>COG</v>
+          </cell>
+          <cell r="C36" t="str">
+            <v>Congo</v>
+          </cell>
+          <cell r="D36" t="str">
+            <v>2005 DHS, 2011 DHS, 2014 MICS</v>
+          </cell>
+          <cell r="E36" t="str">
+            <v>2005 DHS, 2011 DHS, 2014 MICS</v>
+          </cell>
+          <cell r="F36" t="str">
+            <v>2005 DHS, 2011 DHS, 2014 MICS</v>
+          </cell>
+          <cell r="J36" t="str">
+            <v>2005 DHS, 2011 DHS, 2014 MICS</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="A37">
+            <v>188</v>
+          </cell>
+          <cell r="B37" t="str">
+            <v>CRI</v>
+          </cell>
+          <cell r="C37" t="str">
+            <v>Costa Rica</v>
+          </cell>
+          <cell r="D37" t="str">
+            <v>2011 MICS, 2018 MICS</v>
+          </cell>
+          <cell r="E37" t="str">
+            <v>2011 MICS, 2018 MICS</v>
+          </cell>
+          <cell r="F37" t="str">
+            <v>2011 MICS, 2018 MICS</v>
+          </cell>
+          <cell r="G37" t="str">
+            <v>Some data from proxy country: 320</v>
+          </cell>
+          <cell r="H37" t="str">
+            <v>Some data from proxy country: 320</v>
+          </cell>
+          <cell r="I37" t="str">
+            <v>Some data from proxy country: 320</v>
+          </cell>
+          <cell r="J37" t="str">
+            <v>2011 MICS, 2018 MICS Some data from proxy country: Guatemala</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="A38">
+            <v>384</v>
+          </cell>
+          <cell r="B38" t="str">
+            <v>CIV</v>
+          </cell>
+          <cell r="C38" t="str">
+            <v>Cote d'Ivoire</v>
+          </cell>
+          <cell r="D38" t="str">
+            <v>1994 DHS, 1998 DHS, 2006 MICS, 2011 DHS, 2016 MICS, 2021 DHS</v>
+          </cell>
+          <cell r="E38" t="str">
+            <v>1994 DHS, 1998 DHS, 2011 DHS, 2016 MICS, 2021 DHS</v>
+          </cell>
+          <cell r="F38" t="str">
+            <v>1994 DHS, 1998 DHS, 2006 MICS, 2011 DHS, 2016 MICS, 2021 DHS</v>
+          </cell>
+          <cell r="J38" t="str">
+            <v>1994 DHS, 1998 DHS, 2006 MICS, 2011 DHS, 2016 MICS, 2021 DHS</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="A39">
+            <v>191</v>
+          </cell>
+          <cell r="B39" t="str">
+            <v>HRV</v>
+          </cell>
+          <cell r="C39" t="str">
+            <v>Croatia</v>
+          </cell>
+          <cell r="G39" t="str">
+            <v>Some data from proxy country: 498</v>
+          </cell>
+          <cell r="H39" t="str">
+            <v>Some data from proxy country: 498</v>
+          </cell>
+          <cell r="I39" t="str">
+            <v>Some data from proxy country: 498</v>
+          </cell>
+          <cell r="J39" t="str">
+            <v>Some data from proxy country: Moldova</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="A40">
+            <v>192</v>
+          </cell>
+          <cell r="B40" t="str">
+            <v>CUB</v>
+          </cell>
+          <cell r="C40" t="str">
+            <v>Cuba</v>
+          </cell>
+          <cell r="D40" t="str">
+            <v>2011 MICS, 2014 MICS, 2019 MICS</v>
+          </cell>
+          <cell r="E40" t="str">
+            <v>2011 MICS, 2014 MICS, 2019 MICS</v>
+          </cell>
+          <cell r="F40" t="str">
+            <v>2011 MICS, 2014 MICS, 2019 MICS</v>
+          </cell>
+          <cell r="G40" t="str">
+            <v>Some data from proxy country: 214</v>
+          </cell>
+          <cell r="H40" t="str">
+            <v>Some data from proxy country: 214</v>
+          </cell>
+          <cell r="I40" t="str">
+            <v>Some data from proxy country: 214</v>
+          </cell>
+          <cell r="J40" t="str">
+            <v>2011 MICS, 2014 MICS, 2019 MICS Some data from proxy country: Dominican Republic</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="A41">
+            <v>531</v>
+          </cell>
+          <cell r="B41" t="str">
+            <v>CUW</v>
+          </cell>
+          <cell r="C41" t="str">
+            <v>Curacao</v>
+          </cell>
+          <cell r="G41" t="str">
+            <v>Some data from proxy country: 214</v>
+          </cell>
+          <cell r="H41" t="str">
+            <v>Some data from proxy country: 214</v>
+          </cell>
+          <cell r="I41" t="str">
+            <v>Some data from proxy country: 214</v>
+          </cell>
+          <cell r="J41" t="str">
+            <v>Some data from proxy country: Dominican Republic</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="A42">
+            <v>196</v>
+          </cell>
+          <cell r="B42" t="str">
+            <v>CYP</v>
+          </cell>
+          <cell r="C42" t="str">
+            <v>Cyprus</v>
+          </cell>
+          <cell r="G42" t="str">
+            <v>Some data from proxy country: 400</v>
+          </cell>
+          <cell r="H42" t="str">
+            <v>Some data from proxy country: 400</v>
+          </cell>
+          <cell r="I42" t="str">
+            <v>Some data from proxy country: 400</v>
+          </cell>
+          <cell r="J42" t="str">
+            <v>Some data from proxy country: Jordan</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="A43">
+            <v>203</v>
+          </cell>
+          <cell r="B43" t="str">
+            <v>CZE</v>
+          </cell>
+          <cell r="C43" t="str">
+            <v>Czechia</v>
+          </cell>
+          <cell r="G43" t="str">
+            <v>Some data from proxy country: 804</v>
+          </cell>
+          <cell r="H43" t="str">
+            <v>Some data from proxy country: 804</v>
+          </cell>
+          <cell r="I43" t="str">
+            <v>Some data from proxy country: 804</v>
+          </cell>
+          <cell r="J43" t="str">
+            <v>Some data from proxy country: Ukraine</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="A44">
+            <v>408</v>
+          </cell>
+          <cell r="B44" t="str">
+            <v>PRK</v>
+          </cell>
+          <cell r="C44" t="str">
+            <v>Dem. People's Republic of Korea</v>
+          </cell>
+          <cell r="G44" t="str">
+            <v>Some data from proxy country: 104</v>
+          </cell>
+          <cell r="H44" t="str">
+            <v>Some data from proxy country: 104</v>
+          </cell>
+          <cell r="I44" t="str">
+            <v>Some data from proxy country: 104</v>
+          </cell>
+          <cell r="J44" t="str">
+            <v>Some data from proxy country: Myanmar</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="A45">
+            <v>180</v>
+          </cell>
+          <cell r="B45" t="str">
+            <v>COD</v>
+          </cell>
+          <cell r="C45" t="str">
+            <v>Democratic Republic of the Congo</v>
+          </cell>
+          <cell r="D45" t="str">
+            <v>2001 MICS, 2007 DHS, 2010 MICS, 2013 DHS, 2017 MICS, 2023 DHS</v>
+          </cell>
+          <cell r="E45" t="str">
+            <v>2007 DHS, 2010 MICS, 2013 DHS, 2017 MICS, 2023 DHS</v>
+          </cell>
+          <cell r="F45" t="str">
+            <v>2001 MICS, 2007 DHS, 2010 MICS, 2013 DHS, 2017 MICS, 2023 DHS</v>
+          </cell>
+          <cell r="J45" t="str">
+            <v>2001 MICS, 2007 DHS, 2010 MICS, 2013 DHS, 2017 MICS, 2023 DHS</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="A46">
+            <v>262</v>
+          </cell>
+          <cell r="B46" t="str">
+            <v>DJI</v>
+          </cell>
+          <cell r="C46" t="str">
+            <v>Djibouti</v>
+          </cell>
+          <cell r="D46" t="str">
+            <v>2006 MICS</v>
+          </cell>
+          <cell r="E46" t="str">
+            <v>2006 MICS</v>
+          </cell>
+          <cell r="F46" t="str">
+            <v>2006 MICS</v>
+          </cell>
+          <cell r="G46" t="str">
+            <v>Some data from proxy country: 231</v>
+          </cell>
+          <cell r="H46" t="str">
+            <v>Some data from proxy country: 231</v>
+          </cell>
+          <cell r="I46" t="str">
+            <v>Some data from proxy country: 231</v>
+          </cell>
+          <cell r="J46" t="str">
+            <v>2006 MICS Some data from proxy country: Ethiopia</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="A47">
+            <v>214</v>
+          </cell>
+          <cell r="B47" t="str">
+            <v>DOM</v>
+          </cell>
+          <cell r="C47" t="str">
+            <v>Dominican Republic</v>
+          </cell>
+          <cell r="D47" t="str">
+            <v>1991 DHS, 1996 DHS, 1999 DHS, 2000 MICS, 2002 DHS, 2007 DHS, 2013 DHS, 2014 MICS, 2019 MICS</v>
+          </cell>
+          <cell r="E47" t="str">
+            <v>1991 DHS, 1996 DHS, 1999 DHS, 2002 DHS, 2007 DHS, 2013 DHS, 2014 MICS, 2019 MICS</v>
+          </cell>
+          <cell r="F47" t="str">
+            <v>1991 DHS, 1996 DHS, 1999 DHS, 2002 DHS, 2007 DHS, 2013 DHS, 2014 MICS, 2019 MICS</v>
+          </cell>
+          <cell r="J47" t="str">
+            <v>1991 DHS, 1996 DHS, 1999 DHS, 2002 DHS, 2007 DHS, 2013 DHS, 2014 MICS, 2019 MICS</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="A48">
+            <v>218</v>
+          </cell>
+          <cell r="B48" t="str">
+            <v>ECU</v>
+          </cell>
+          <cell r="C48" t="str">
+            <v>Ecuador</v>
+          </cell>
+          <cell r="G48" t="str">
+            <v>Some data from proxy country: 170</v>
+          </cell>
+          <cell r="H48" t="str">
+            <v>Some data from proxy country: 170</v>
+          </cell>
+          <cell r="I48" t="str">
+            <v>Some data from proxy country: 170</v>
+          </cell>
+          <cell r="J48" t="str">
+            <v>Some data from proxy country: Colombia</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="A49">
+            <v>818</v>
+          </cell>
+          <cell r="B49" t="str">
+            <v>EGY</v>
+          </cell>
+          <cell r="C49" t="str">
+            <v>Egypt</v>
+          </cell>
+          <cell r="D49" t="str">
+            <v>1992 DHS, 1995 DHS, 2000 DHS, 2003 DHS, 2005 DHS, 2008 DHS, 2014 DHS</v>
+          </cell>
+          <cell r="E49" t="str">
+            <v>1992 DHS, 1995 DHS, 2000 DHS, 2003 DHS, 2005 DHS, 2008 DHS, 2014 DHS</v>
+          </cell>
+          <cell r="F49" t="str">
+            <v>1992 DHS, 1995 DHS, 2000 DHS, 2003 DHS, 2005 DHS, 2008 DHS, 2014 DHS</v>
+          </cell>
+          <cell r="J49" t="str">
+            <v>1992 DHS, 1995 DHS, 2000 DHS, 2003 DHS, 2005 DHS, 2008 DHS, 2014 DHS</v>
+          </cell>
+        </row>
+        <row r="50">
+          <cell r="A50">
+            <v>222</v>
+          </cell>
+          <cell r="B50" t="str">
+            <v>SLV</v>
+          </cell>
+          <cell r="C50" t="str">
+            <v>El Salvador</v>
+          </cell>
+          <cell r="D50" t="str">
+            <v>2014 MICS</v>
+          </cell>
+          <cell r="E50" t="str">
+            <v>2014 MICS</v>
+          </cell>
+          <cell r="F50" t="str">
+            <v>2014 MICS</v>
+          </cell>
+          <cell r="G50" t="str">
+            <v>Some data from proxy country: 320</v>
+          </cell>
+          <cell r="H50" t="str">
+            <v>Some data from proxy country: 320</v>
+          </cell>
+          <cell r="I50" t="str">
+            <v>Some data from proxy country: 320</v>
+          </cell>
+          <cell r="J50" t="str">
+            <v>2014 MICS Some data from proxy country: Guatemala</v>
+          </cell>
+        </row>
+        <row r="51">
+          <cell r="A51">
+            <v>226</v>
+          </cell>
+          <cell r="B51" t="str">
+            <v>GNQ</v>
+          </cell>
+          <cell r="C51" t="str">
+            <v>Equatorial Guinea</v>
+          </cell>
+          <cell r="D51" t="str">
+            <v>2000 MICS</v>
+          </cell>
+          <cell r="G51" t="str">
+            <v>Some data from proxy country: 324</v>
+          </cell>
+          <cell r="H51" t="str">
+            <v>Some data from proxy country: 324</v>
+          </cell>
+          <cell r="I51" t="str">
+            <v>Some data from proxy country: 324</v>
+          </cell>
+          <cell r="J51" t="str">
+            <v>Some data from proxy country: Guinea</v>
+          </cell>
+        </row>
+        <row r="52">
+          <cell r="A52">
+            <v>232</v>
+          </cell>
+          <cell r="B52" t="str">
+            <v>ERI</v>
+          </cell>
+          <cell r="C52" t="str">
+            <v>Eritrea</v>
+          </cell>
+          <cell r="G52" t="str">
+            <v>Some data from proxy country: 800</v>
+          </cell>
+          <cell r="H52" t="str">
+            <v>Some data from proxy country: 800</v>
+          </cell>
+          <cell r="I52" t="str">
+            <v>Some data from proxy country: 800</v>
+          </cell>
+          <cell r="J52" t="str">
+            <v>Some data from proxy country: Uganda</v>
+          </cell>
+        </row>
+        <row r="53">
+          <cell r="A53">
+            <v>233</v>
+          </cell>
+          <cell r="B53" t="str">
+            <v>EST</v>
+          </cell>
+          <cell r="C53" t="str">
+            <v>Estonia</v>
+          </cell>
+          <cell r="G53" t="str">
+            <v>Some data from proxy country: 804</v>
+          </cell>
+          <cell r="H53" t="str">
+            <v>Some data from proxy country: 804</v>
+          </cell>
+          <cell r="I53" t="str">
+            <v>Some data from proxy country: 804</v>
+          </cell>
+          <cell r="J53" t="str">
+            <v>Some data from proxy country: Ukraine</v>
+          </cell>
+        </row>
+        <row r="54">
+          <cell r="A54">
+            <v>748</v>
+          </cell>
+          <cell r="B54" t="str">
+            <v>SWZ</v>
+          </cell>
+          <cell r="C54" t="str">
+            <v>Eswatini</v>
+          </cell>
+          <cell r="D54" t="str">
+            <v>2000 MICS, 2006 DHS, 2010 MICS, 2014 MICS, 2021 MICS</v>
+          </cell>
+          <cell r="E54" t="str">
+            <v>2006 DHS, 2010 MICS, 2014 MICS</v>
+          </cell>
+          <cell r="F54" t="str">
+            <v>2006 DHS, 2010 MICS, 2014 MICS, 2021 MICS</v>
+          </cell>
+          <cell r="J54" t="str">
+            <v>2006 DHS, 2010 MICS, 2014 MICS, 2021 MICS</v>
+          </cell>
+        </row>
+        <row r="55">
+          <cell r="A55">
+            <v>231</v>
+          </cell>
+          <cell r="B55" t="str">
+            <v>ETH</v>
+          </cell>
+          <cell r="C55" t="str">
+            <v>Ethiopia</v>
+          </cell>
+          <cell r="D55" t="str">
+            <v>2000 DHS, 2005 DHS, 2011 DHS, 2016 DHS</v>
+          </cell>
+          <cell r="E55" t="str">
+            <v>2000 DHS, 2005 DHS, 2011 DHS, 2016 DHS</v>
+          </cell>
+          <cell r="F55" t="str">
+            <v>2000 DHS, 2005 DHS, 2011 DHS, 2016 DHS</v>
+          </cell>
+          <cell r="J55" t="str">
+            <v>2000 DHS, 2005 DHS, 2011 DHS, 2016 DHS</v>
+          </cell>
+        </row>
+        <row r="56">
+          <cell r="A56">
+            <v>242</v>
+          </cell>
+          <cell r="B56" t="str">
+            <v>FJI</v>
+          </cell>
+          <cell r="C56" t="str">
+            <v>Fiji</v>
+          </cell>
+          <cell r="D56" t="str">
+            <v>2021 MICS</v>
+          </cell>
+          <cell r="E56" t="str">
+            <v>2021 MICS</v>
+          </cell>
+          <cell r="F56" t="str">
+            <v>2021 MICS</v>
+          </cell>
+          <cell r="G56" t="str">
+            <v>Some data from proxy country: 360</v>
+          </cell>
+          <cell r="H56" t="str">
+            <v>Some data from proxy country: 360</v>
+          </cell>
+          <cell r="I56" t="str">
+            <v>Some data from proxy country: 360</v>
+          </cell>
+          <cell r="J56" t="str">
+            <v>2021 MICS Some data from proxy country: Indonesia</v>
+          </cell>
+        </row>
+        <row r="57">
+          <cell r="A57">
+            <v>254</v>
+          </cell>
+          <cell r="B57" t="str">
+            <v>GUF</v>
+          </cell>
+          <cell r="C57" t="str">
+            <v>French Guiana</v>
+          </cell>
+          <cell r="G57" t="str">
+            <v>Some data from proxy country: 76</v>
+          </cell>
+          <cell r="H57" t="str">
+            <v>Some data from proxy country: 76</v>
+          </cell>
+          <cell r="I57" t="str">
+            <v>Some data from proxy country: 76</v>
+          </cell>
+          <cell r="J57" t="str">
+            <v>Some data from proxy country: Brazil</v>
+          </cell>
+        </row>
+        <row r="58">
+          <cell r="A58">
+            <v>258</v>
+          </cell>
+          <cell r="B58" t="str">
+            <v>PYF</v>
+          </cell>
+          <cell r="C58" t="str">
+            <v>French Polynesia</v>
+          </cell>
+          <cell r="G58" t="str">
+            <v>Some data from proxy country: 360</v>
+          </cell>
+          <cell r="H58" t="str">
+            <v>Some data from proxy country: 360</v>
+          </cell>
+          <cell r="I58" t="str">
+            <v>Some data from proxy country: 360</v>
+          </cell>
+          <cell r="J58" t="str">
+            <v>Some data from proxy country: Indonesia</v>
+          </cell>
+        </row>
+        <row r="59">
+          <cell r="A59">
+            <v>266</v>
+          </cell>
+          <cell r="B59" t="str">
+            <v>GAB</v>
+          </cell>
+          <cell r="C59" t="str">
+            <v>Gabon</v>
+          </cell>
+          <cell r="D59" t="str">
+            <v>2000 DHS, 2012 DHS, 2019 DHS</v>
+          </cell>
+          <cell r="E59" t="str">
+            <v>2000 DHS, 2012 DHS, 2019 DHS</v>
+          </cell>
+          <cell r="F59" t="str">
+            <v>2000 DHS, 2012 DHS, 2019 DHS</v>
+          </cell>
+          <cell r="J59" t="str">
+            <v>2000 DHS, 2012 DHS, 2019 DHS</v>
+          </cell>
+        </row>
+        <row r="60">
+          <cell r="A60">
+            <v>270</v>
+          </cell>
+          <cell r="B60" t="str">
+            <v>GMB</v>
+          </cell>
+          <cell r="C60" t="str">
+            <v>Gambia</v>
+          </cell>
+          <cell r="D60" t="str">
+            <v>2010 MICS, 2013 DHS, 2018 MICS, 2019 DHS</v>
+          </cell>
+          <cell r="E60" t="str">
+            <v>2010 MICS, 2013 DHS, 2018 MICS, 2019 DHS</v>
+          </cell>
+          <cell r="F60" t="str">
+            <v>2010 MICS, 2013 DHS, 2018 MICS, 2019 DHS</v>
+          </cell>
+          <cell r="J60" t="str">
+            <v>2010 MICS, 2013 DHS, 2018 MICS, 2019 DHS</v>
+          </cell>
+        </row>
+        <row r="61">
+          <cell r="A61">
+            <v>268</v>
+          </cell>
+          <cell r="B61" t="str">
+            <v>GEO</v>
+          </cell>
+          <cell r="C61" t="str">
+            <v>Georgia</v>
+          </cell>
+          <cell r="D61" t="str">
+            <v>2018 MICS</v>
+          </cell>
+          <cell r="F61" t="str">
+            <v>2018 MICS</v>
+          </cell>
+          <cell r="G61" t="str">
+            <v>Some data from proxy country: 51</v>
+          </cell>
+          <cell r="H61" t="str">
+            <v>Some data from proxy country: 51</v>
+          </cell>
+          <cell r="I61" t="str">
+            <v>Some data from proxy country: 51</v>
+          </cell>
+          <cell r="J61" t="str">
+            <v>2018 MICS Some data from proxy country: Armenia</v>
+          </cell>
+        </row>
+        <row r="62">
+          <cell r="A62">
+            <v>288</v>
+          </cell>
+          <cell r="B62" t="str">
+            <v>GHA</v>
+          </cell>
+          <cell r="C62" t="str">
+            <v>Ghana</v>
+          </cell>
+          <cell r="D62" t="str">
+            <v>1993 DHS, 1998 DHS, 2003 DHS, 2006 MICS, 2008 DHS, 2011 MICS, 2014 DHS, 2017 MICS, 2022 DHS</v>
+          </cell>
+          <cell r="E62" t="str">
+            <v>1993 DHS, 1998 DHS, 2003 DHS, 2006 MICS, 2008 DHS, 2011 MICS, 2014 DHS, 2017 MICS, 2022 DHS</v>
+          </cell>
+          <cell r="F62" t="str">
+            <v>1993 DHS, 1998 DHS, 2003 DHS, 2006 MICS, 2008 DHS, 2011 MICS, 2014 DHS, 2017 MICS, 2022 DHS</v>
+          </cell>
+          <cell r="J62" t="str">
+            <v>1993 DHS, 1998 DHS, 2003 DHS, 2006 MICS, 2008 DHS, 2011 MICS, 2014 DHS, 2017 MICS, 2022 DHS</v>
+          </cell>
+        </row>
+        <row r="63">
+          <cell r="A63">
+            <v>308</v>
+          </cell>
+          <cell r="B63" t="str">
+            <v>GRD</v>
+          </cell>
+          <cell r="C63" t="str">
+            <v>Grenada</v>
+          </cell>
+          <cell r="G63" t="str">
+            <v>Some data from proxy country: 214</v>
+          </cell>
+          <cell r="H63" t="str">
+            <v>Some data from proxy country: 214</v>
+          </cell>
+          <cell r="I63" t="str">
+            <v>Some data from proxy country: 214</v>
+          </cell>
+          <cell r="J63" t="str">
+            <v>Some data from proxy country: Dominican Republic</v>
+          </cell>
+        </row>
+        <row r="64">
+          <cell r="A64">
+            <v>312</v>
+          </cell>
+          <cell r="B64" t="str">
+            <v>GLP</v>
+          </cell>
+          <cell r="C64" t="str">
+            <v>Guadeloupe</v>
+          </cell>
+          <cell r="G64" t="str">
+            <v>Some data from proxy country: 214</v>
+          </cell>
+          <cell r="H64" t="str">
+            <v>Some data from proxy country: 214</v>
+          </cell>
+          <cell r="I64" t="str">
+            <v>Some data from proxy country: 214</v>
+          </cell>
+          <cell r="J64" t="str">
+            <v>Some data from proxy country: Dominican Republic</v>
+          </cell>
+        </row>
+        <row r="65">
+          <cell r="A65">
+            <v>316</v>
+          </cell>
+          <cell r="B65" t="str">
+            <v>GUM</v>
+          </cell>
+          <cell r="C65" t="str">
+            <v>Guam</v>
+          </cell>
+          <cell r="G65" t="str">
+            <v>Some data from proxy country: 360</v>
+          </cell>
+          <cell r="H65" t="str">
+            <v>Some data from proxy country: 360</v>
+          </cell>
+          <cell r="I65" t="str">
+            <v>Some data from proxy country: 360</v>
+          </cell>
+          <cell r="J65" t="str">
+            <v>Some data from proxy country: Indonesia</v>
+          </cell>
+        </row>
+        <row r="66">
+          <cell r="A66">
+            <v>320</v>
+          </cell>
+          <cell r="B66" t="str">
+            <v>GTM</v>
+          </cell>
+          <cell r="C66" t="str">
+            <v>Guatemala</v>
+          </cell>
+          <cell r="D66" t="str">
+            <v>1995 DHS, 2014 DHS</v>
+          </cell>
+          <cell r="E66" t="str">
+            <v>1995 DHS, 2014 DHS</v>
+          </cell>
+          <cell r="F66" t="str">
+            <v>1995 DHS, 2014 DHS</v>
+          </cell>
+          <cell r="J66" t="str">
+            <v>1995 DHS, 2014 DHS</v>
+          </cell>
+        </row>
+        <row r="67">
+          <cell r="A67">
+            <v>324</v>
+          </cell>
+          <cell r="B67" t="str">
+            <v>GIN</v>
+          </cell>
+          <cell r="C67" t="str">
+            <v>Guinea</v>
+          </cell>
+          <cell r="D67" t="str">
+            <v>1999 DHS, 2005 DHS, 2012 DHS, 2016 MICS, 2018 DHS</v>
+          </cell>
+          <cell r="E67" t="str">
+            <v>1999 DHS, 2005 DHS, 2012 DHS, 2016 MICS, 2018 DHS</v>
+          </cell>
+          <cell r="F67" t="str">
+            <v>1999 DHS, 2005 DHS, 2012 DHS, 2016 MICS, 2018 DHS</v>
+          </cell>
+          <cell r="J67" t="str">
+            <v>1999 DHS, 2005 DHS, 2012 DHS, 2016 MICS, 2018 DHS</v>
+          </cell>
+        </row>
+        <row r="68">
+          <cell r="A68">
+            <v>624</v>
+          </cell>
+          <cell r="B68" t="str">
+            <v>GNB</v>
+          </cell>
+          <cell r="C68" t="str">
+            <v>Guinea-Bissau</v>
+          </cell>
+          <cell r="D68" t="str">
+            <v>2000 MICS, 2006 MICS, 2014 MICS, 2018 MICS</v>
+          </cell>
+          <cell r="E68" t="str">
+            <v>2014 MICS, 2018 MICS</v>
+          </cell>
+          <cell r="F68" t="str">
+            <v>2000 MICS, 2006 MICS, 2014 MICS, 2018 MICS</v>
+          </cell>
+          <cell r="G68" t="str">
+            <v>Some data from proxy country: 324</v>
+          </cell>
+          <cell r="H68" t="str">
+            <v>Some data from proxy country: 324</v>
+          </cell>
+          <cell r="I68" t="str">
+            <v>Some data from proxy country: 324</v>
+          </cell>
+          <cell r="J68" t="str">
+            <v>2000 MICS, 2006 MICS, 2014 MICS, 2018 MICS Some data from proxy country: Guinea</v>
+          </cell>
+        </row>
+        <row r="69">
+          <cell r="A69">
+            <v>328</v>
+          </cell>
+          <cell r="B69" t="str">
+            <v>GUY</v>
+          </cell>
+          <cell r="C69" t="str">
+            <v>Guyana</v>
+          </cell>
+          <cell r="D69" t="str">
+            <v>2000 MICS, 2006 MICS, 2009 DHS, 2014 MICS, 2019 MICS</v>
+          </cell>
+          <cell r="E69" t="str">
+            <v>2009 DHS, 2014 MICS, 2019 MICS</v>
+          </cell>
+          <cell r="F69" t="str">
+            <v>2006 MICS, 2009 DHS, 2014 MICS, 2019 MICS</v>
+          </cell>
+          <cell r="J69" t="str">
+            <v>2006 MICS, 2009 DHS, 2014 MICS, 2019 MICS</v>
+          </cell>
+        </row>
+        <row r="70">
+          <cell r="A70">
+            <v>332</v>
+          </cell>
+          <cell r="B70" t="str">
+            <v>HTI</v>
+          </cell>
+          <cell r="C70" t="str">
+            <v>Haiti</v>
+          </cell>
+          <cell r="D70" t="str">
+            <v>1994 DHS, 2000 DHS, 2005 DHS, 2012 DHS, 2016 DHS</v>
+          </cell>
+          <cell r="E70" t="str">
+            <v>1994 DHS, 2000 DHS, 2005 DHS, 2012 DHS, 2016 DHS</v>
+          </cell>
+          <cell r="F70" t="str">
+            <v>1994 DHS, 2000 DHS, 2005 DHS, 2012 DHS, 2016 DHS</v>
+          </cell>
+          <cell r="J70" t="str">
+            <v>1994 DHS, 2000 DHS, 2005 DHS, 2012 DHS, 2016 DHS</v>
+          </cell>
+        </row>
+        <row r="71">
+          <cell r="A71">
+            <v>340</v>
+          </cell>
+          <cell r="B71" t="str">
+            <v>HND</v>
+          </cell>
+          <cell r="C71" t="str">
+            <v>Honduras</v>
+          </cell>
+          <cell r="D71" t="str">
+            <v>2005 DHS, 2011 DHS, 2019 MICS</v>
+          </cell>
+          <cell r="E71" t="str">
+            <v>2005 DHS, 2011 DHS, 2019 MICS</v>
+          </cell>
+          <cell r="F71" t="str">
+            <v>2005 DHS, 2011 DHS, 2019 MICS</v>
+          </cell>
+          <cell r="J71" t="str">
+            <v>2005 DHS, 2011 DHS, 2019 MICS</v>
+          </cell>
+        </row>
+        <row r="72">
+          <cell r="A72">
+            <v>348</v>
+          </cell>
+          <cell r="B72" t="str">
+            <v>HUN</v>
+          </cell>
+          <cell r="C72" t="str">
+            <v>Hungary</v>
+          </cell>
+          <cell r="G72" t="str">
+            <v>Some data from proxy country: 804</v>
+          </cell>
+          <cell r="H72" t="str">
+            <v>Some data from proxy country: 804</v>
+          </cell>
+          <cell r="I72" t="str">
+            <v>Some data from proxy country: 804</v>
+          </cell>
+          <cell r="J72" t="str">
+            <v>Some data from proxy country: Ukraine</v>
+          </cell>
+        </row>
+        <row r="73">
+          <cell r="A73">
+            <v>356</v>
+          </cell>
+          <cell r="B73" t="str">
+            <v>IND</v>
+          </cell>
+          <cell r="C73" t="str">
+            <v>India</v>
+          </cell>
+          <cell r="D73" t="str">
+            <v>1992 DHS, 1998 DHS, 2005 DHS, 2015 DHS, 2019 DHS</v>
+          </cell>
+          <cell r="E73" t="str">
+            <v>1992 DHS, 1998 DHS, 2005 DHS, 2015 DHS, 2019 DHS</v>
+          </cell>
+          <cell r="F73" t="str">
+            <v>1992 DHS, 1998 DHS, 2005 DHS, 2015 DHS, 2019 DHS</v>
+          </cell>
+          <cell r="J73" t="str">
+            <v>1992 DHS, 1998 DHS, 2005 DHS, 2015 DHS, 2019 DHS</v>
+          </cell>
+        </row>
+        <row r="74">
+          <cell r="A74">
+            <v>360</v>
+          </cell>
+          <cell r="B74" t="str">
+            <v>IDN</v>
+          </cell>
+          <cell r="C74" t="str">
+            <v>Indonesia</v>
+          </cell>
+          <cell r="D74" t="str">
+            <v>1991 DHS, 1994 DHS, 1997 DHS, 2002 DHS, 2007 DHS, 2012 DHS, 2017 DHS</v>
+          </cell>
+          <cell r="E74" t="str">
+            <v>1991 DHS, 1994 DHS, 1997 DHS, 2002 DHS, 2007 DHS, 2012 DHS, 2017 DHS</v>
+          </cell>
+          <cell r="F74" t="str">
+            <v>1991 DHS, 1994 DHS, 1997 DHS, 2002 DHS, 2007 DHS, 2012 DHS, 2017 DHS</v>
+          </cell>
+          <cell r="J74" t="str">
+            <v>1991 DHS, 1994 DHS, 1997 DHS, 2002 DHS, 2007 DHS, 2012 DHS, 2017 DHS</v>
+          </cell>
+        </row>
+        <row r="75">
+          <cell r="A75">
+            <v>364</v>
+          </cell>
+          <cell r="B75" t="str">
+            <v>IRN</v>
+          </cell>
+          <cell r="C75" t="str">
+            <v>Iran (Islamic Republic of)</v>
+          </cell>
+          <cell r="G75" t="str">
+            <v>Some data from proxy country: 400</v>
+          </cell>
+          <cell r="H75" t="str">
+            <v>Some data from proxy country: 400</v>
+          </cell>
+          <cell r="I75" t="str">
+            <v>Some data from proxy country: 400</v>
+          </cell>
+          <cell r="J75" t="str">
+            <v>Some data from proxy country: Jordan</v>
+          </cell>
+        </row>
+        <row r="76">
+          <cell r="A76">
+            <v>368</v>
+          </cell>
+          <cell r="B76" t="str">
+            <v>IRQ</v>
+          </cell>
+          <cell r="C76" t="str">
+            <v>Iraq</v>
+          </cell>
+          <cell r="D76" t="str">
+            <v>2000 MICS, 2006 MICS, 2011 MICS, 2018 MICS</v>
+          </cell>
+          <cell r="E76" t="str">
+            <v>2000 MICS, 2006 MICS, 2011 MICS, 2018 MICS</v>
+          </cell>
+          <cell r="F76" t="str">
+            <v>2000 MICS, 2006 MICS, 2011 MICS, 2018 MICS</v>
+          </cell>
+          <cell r="G76" t="str">
+            <v>Some data from proxy country: 792</v>
+          </cell>
+          <cell r="H76" t="str">
+            <v>Some data from proxy country: 792</v>
+          </cell>
+          <cell r="I76" t="str">
+            <v>Some data from proxy country: 792</v>
+          </cell>
+          <cell r="J76" t="str">
+            <v>2000 MICS, 2006 MICS, 2011 MICS, 2018 MICS Some data from proxy country: Turkey</v>
+          </cell>
+        </row>
+        <row r="77">
+          <cell r="A77">
+            <v>388</v>
+          </cell>
+          <cell r="B77" t="str">
+            <v>JAM</v>
+          </cell>
+          <cell r="C77" t="str">
+            <v>Jamaica</v>
+          </cell>
+          <cell r="G77" t="str">
+            <v>Some data from proxy country: 214</v>
+          </cell>
+          <cell r="H77" t="str">
+            <v>Some data from proxy country: 214</v>
+          </cell>
+          <cell r="I77" t="str">
+            <v>Some data from proxy country: 214</v>
+          </cell>
+          <cell r="J77" t="str">
+            <v>Some data from proxy country: Dominican Republic</v>
+          </cell>
+        </row>
+        <row r="78">
+          <cell r="A78">
+            <v>400</v>
+          </cell>
+          <cell r="B78" t="str">
+            <v>JOR</v>
+          </cell>
+          <cell r="C78" t="str">
+            <v>Jordan</v>
+          </cell>
+          <cell r="D78" t="str">
+            <v>1990 DHS, 1997 DHS, 2002 DHS, 2007 DHS, 2012 DHS, 2017 DHS, 2023 DHS</v>
+          </cell>
+          <cell r="E78" t="str">
+            <v>1990 DHS, 1997 DHS, 2002 DHS, 2007 DHS, 2012 DHS, 2017 DHS, 2023 DHS</v>
+          </cell>
+          <cell r="F78" t="str">
+            <v>1990 DHS, 1997 DHS, 2002 DHS, 2007 DHS, 2012 DHS, 2017 DHS, 2023 DHS</v>
+          </cell>
+          <cell r="J78" t="str">
+            <v>1990 DHS, 1997 DHS, 2002 DHS, 2007 DHS, 2012 DHS, 2017 DHS, 2023 DHS</v>
+          </cell>
+        </row>
+        <row r="79">
+          <cell r="A79">
+            <v>398</v>
+          </cell>
+          <cell r="B79" t="str">
+            <v>KAZ</v>
+          </cell>
+          <cell r="C79" t="str">
+            <v>Kazakhstan</v>
+          </cell>
+          <cell r="D79" t="str">
+            <v>1995 DHS, 1999 DHS, 2006 MICS, 2010 MICS, 2015 MICS, 2024 MICS</v>
+          </cell>
+          <cell r="E79" t="str">
+            <v>1995 DHS, 1999 DHS, 2015 MICS</v>
+          </cell>
+          <cell r="F79" t="str">
+            <v>1995 DHS, 1999 DHS, 2006 MICS, 2010 MICS, 2015 MICS, 2024 MICS</v>
+          </cell>
+          <cell r="J79" t="str">
+            <v>1995 DHS, 1999 DHS, 2006 MICS, 2010 MICS, 2015 MICS, 2024 MICS</v>
+          </cell>
+        </row>
+        <row r="80">
+          <cell r="A80">
+            <v>404</v>
+          </cell>
+          <cell r="B80" t="str">
+            <v>KEN</v>
+          </cell>
+          <cell r="C80" t="str">
+            <v>Kenya</v>
+          </cell>
+          <cell r="D80" t="str">
+            <v>1993 DHS, 1998 DHS, 2003 DHS, 2008 DHS, 2014 DHS, 2022 DHS</v>
+          </cell>
+          <cell r="E80" t="str">
+            <v>1993 DHS, 1998 DHS, 2003 DHS, 2008 DHS, 2014 DHS, 2022 DHS</v>
+          </cell>
+          <cell r="F80" t="str">
+            <v>1993 DHS, 1998 DHS, 2003 DHS, 2008 DHS, 2014 DHS, 2022 DHS</v>
+          </cell>
+          <cell r="J80" t="str">
+            <v>1993 DHS, 1998 DHS, 2003 DHS, 2008 DHS, 2014 DHS, 2022 DHS</v>
+          </cell>
+        </row>
+        <row r="81">
+          <cell r="A81">
+            <v>296</v>
+          </cell>
+          <cell r="B81" t="str">
+            <v>KIR</v>
+          </cell>
+          <cell r="C81" t="str">
+            <v>Kiribati</v>
+          </cell>
+          <cell r="D81" t="str">
+            <v>2018 MICS</v>
+          </cell>
+          <cell r="E81" t="str">
+            <v>2018 MICS</v>
+          </cell>
+          <cell r="F81" t="str">
+            <v>2018 MICS</v>
+          </cell>
+          <cell r="G81" t="str">
+            <v>Some data from proxy country: 360</v>
+          </cell>
+          <cell r="H81" t="str">
+            <v>Some data from proxy country: 360</v>
+          </cell>
+          <cell r="I81" t="str">
+            <v>Some data from proxy country: 360</v>
+          </cell>
+          <cell r="J81" t="str">
+            <v>2018 MICS Some data from proxy country: Indonesia</v>
+          </cell>
+        </row>
+        <row r="82">
+          <cell r="A82">
+            <v>414</v>
+          </cell>
+          <cell r="B82" t="str">
+            <v>KWT</v>
+          </cell>
+          <cell r="C82" t="str">
+            <v>Kuwait</v>
+          </cell>
+          <cell r="G82" t="str">
+            <v>Some data from proxy country: 792</v>
+          </cell>
+          <cell r="H82" t="str">
+            <v>Some data from proxy country: 792</v>
+          </cell>
+          <cell r="I82" t="str">
+            <v>Some data from proxy country: 792</v>
+          </cell>
+          <cell r="J82" t="str">
+            <v>Some data from proxy country: Turkey</v>
+          </cell>
+        </row>
+        <row r="83">
+          <cell r="A83">
+            <v>417</v>
+          </cell>
+          <cell r="B83" t="str">
+            <v>KGZ</v>
+          </cell>
+          <cell r="C83" t="str">
+            <v>Kyrgyzstan</v>
+          </cell>
+          <cell r="D83" t="str">
+            <v>1997 DHS, 2005 MICS, 2012 DHS, 2014 MICS, 2018 MICS, 2023 MICS</v>
+          </cell>
+          <cell r="E83" t="str">
+            <v>1997 DHS, 2012 DHS</v>
+          </cell>
+          <cell r="F83" t="str">
+            <v>1997 DHS, 2005 MICS, 2012 DHS, 2014 MICS, 2018 MICS, 2023 MICS</v>
+          </cell>
+          <cell r="J83" t="str">
+            <v>1997 DHS, 2005 MICS, 2012 DHS, 2014 MICS, 2018 MICS, 2023 MICS</v>
+          </cell>
+        </row>
+        <row r="84">
+          <cell r="A84">
+            <v>418</v>
+          </cell>
+          <cell r="B84" t="str">
+            <v>LAO</v>
+          </cell>
+          <cell r="C84" t="str">
+            <v>Lao People's Democratic Republic</v>
+          </cell>
+          <cell r="D84" t="str">
+            <v>2011 MICS, 2017 MICS, 2023 MICS</v>
+          </cell>
+          <cell r="E84" t="str">
+            <v>2011 MICS, 2017 MICS, 2023 MICS</v>
+          </cell>
+          <cell r="F84" t="str">
+            <v>2011 MICS, 2017 MICS, 2023 MICS</v>
+          </cell>
+          <cell r="G84" t="str">
+            <v>Some data from proxy country: 116</v>
+          </cell>
+          <cell r="H84" t="str">
+            <v>Some data from proxy country: 116</v>
+          </cell>
+          <cell r="I84" t="str">
+            <v>Some data from proxy country: 116</v>
+          </cell>
+          <cell r="J84" t="str">
+            <v>2011 MICS, 2017 MICS, 2023 MICS Some data from proxy country: Cambodia</v>
+          </cell>
+        </row>
+        <row r="85">
+          <cell r="A85">
+            <v>428</v>
+          </cell>
+          <cell r="B85" t="str">
+            <v>LVA</v>
+          </cell>
+          <cell r="C85" t="str">
+            <v>Latvia</v>
+          </cell>
+          <cell r="G85" t="str">
+            <v>Some data from proxy country: 804</v>
+          </cell>
+          <cell r="H85" t="str">
+            <v>Some data from proxy country: 804</v>
+          </cell>
+          <cell r="I85" t="str">
+            <v>Some data from proxy country: 804</v>
+          </cell>
+          <cell r="J85" t="str">
+            <v>Some data from proxy country: Ukraine</v>
+          </cell>
+        </row>
+        <row r="86">
+          <cell r="A86">
+            <v>422</v>
+          </cell>
+          <cell r="B86" t="str">
+            <v>LBN</v>
+          </cell>
+          <cell r="C86" t="str">
+            <v>Lebanon</v>
+          </cell>
+          <cell r="G86" t="str">
+            <v>Some data from proxy country: 792</v>
+          </cell>
+          <cell r="H86" t="str">
+            <v>Some data from proxy country: 792</v>
+          </cell>
+          <cell r="I86" t="str">
+            <v>Some data from proxy country: 792</v>
+          </cell>
+          <cell r="J86" t="str">
+            <v>Some data from proxy country: Turkey</v>
+          </cell>
+        </row>
+        <row r="87">
+          <cell r="A87">
+            <v>426</v>
+          </cell>
+          <cell r="B87" t="str">
+            <v>LSO</v>
+          </cell>
+          <cell r="C87" t="str">
+            <v>Lesotho</v>
+          </cell>
+          <cell r="D87" t="str">
+            <v>2004 DHS, 2009 DHS, 2014 DHS, 2018 MICS, 2023 DHS</v>
+          </cell>
+          <cell r="E87" t="str">
+            <v>2004 DHS, 2009 DHS, 2014 DHS, 2023 DHS</v>
+          </cell>
+          <cell r="F87" t="str">
+            <v>2004 DHS, 2009 DHS, 2014 DHS, 2018 MICS, 2023 DHS</v>
+          </cell>
+          <cell r="J87" t="str">
+            <v>2004 DHS, 2009 DHS, 2014 DHS, 2018 MICS, 2023 DHS</v>
+          </cell>
+        </row>
+        <row r="88">
+          <cell r="A88">
+            <v>430</v>
+          </cell>
+          <cell r="B88" t="str">
+            <v>LBR</v>
+          </cell>
+          <cell r="C88" t="str">
+            <v>Liberia</v>
+          </cell>
+          <cell r="D88" t="str">
+            <v>2007 DHS, 2013 DHS, 2019 DHS</v>
+          </cell>
+          <cell r="E88" t="str">
+            <v>2007 DHS, 2013 DHS, 2019 DHS</v>
+          </cell>
+          <cell r="F88" t="str">
+            <v>2007 DHS, 2013 DHS, 2019 DHS</v>
+          </cell>
+          <cell r="J88" t="str">
+            <v>2007 DHS, 2013 DHS, 2019 DHS</v>
+          </cell>
+        </row>
+        <row r="89">
+          <cell r="A89">
+            <v>434</v>
+          </cell>
+          <cell r="B89" t="str">
+            <v>LBY</v>
+          </cell>
+          <cell r="C89" t="str">
+            <v>Libya</v>
+          </cell>
+          <cell r="G89" t="str">
+            <v>Some data from proxy country: 818</v>
+          </cell>
+          <cell r="H89" t="str">
+            <v>Some data from proxy country: 818</v>
+          </cell>
+          <cell r="I89" t="str">
+            <v>Some data from proxy country: 818</v>
+          </cell>
+          <cell r="J89" t="str">
+            <v>Some data from proxy country: Egypt</v>
+          </cell>
+        </row>
+        <row r="90">
+          <cell r="A90">
+            <v>440</v>
+          </cell>
+          <cell r="B90" t="str">
+            <v>LTU</v>
+          </cell>
+          <cell r="C90" t="str">
+            <v>Lithuania</v>
+          </cell>
+          <cell r="G90" t="str">
+            <v>Some data from proxy country: 804</v>
+          </cell>
+          <cell r="H90" t="str">
+            <v>Some data from proxy country: 804</v>
+          </cell>
+          <cell r="I90" t="str">
+            <v>Some data from proxy country: 804</v>
+          </cell>
+          <cell r="J90" t="str">
+            <v>Some data from proxy country: Ukraine</v>
+          </cell>
+        </row>
+        <row r="91">
+          <cell r="A91">
+            <v>450</v>
+          </cell>
+          <cell r="B91" t="str">
+            <v>MDG</v>
+          </cell>
+          <cell r="C91" t="str">
+            <v>Madagascar</v>
+          </cell>
+          <cell r="D91" t="str">
+            <v>1992 DHS, 1997 DHS, 2000 MICS, 2003 DHS, 2008 DHS, 2018 MICS, 2021 DHS</v>
+          </cell>
+          <cell r="E91" t="str">
+            <v>1992 DHS, 1997 DHS, 2003 DHS, 2008 DHS, 2018 MICS, 2021 DHS</v>
+          </cell>
+          <cell r="F91" t="str">
+            <v>1992 DHS, 1997 DHS, 2003 DHS, 2008 DHS, 2018 MICS, 2021 DHS</v>
+          </cell>
+          <cell r="J91" t="str">
+            <v>1992 DHS, 1997 DHS, 2003 DHS, 2008 DHS, 2018 MICS, 2021 DHS</v>
+          </cell>
+        </row>
+        <row r="92">
+          <cell r="A92">
+            <v>454</v>
+          </cell>
+          <cell r="B92" t="str">
+            <v>MWI</v>
+          </cell>
+          <cell r="C92" t="str">
+            <v>Malawi</v>
+          </cell>
+          <cell r="D92" t="str">
+            <v>1992 DHS, 2000 DHS, 2004 DHS, 2006 MICS, 2010 DHS, 2013 MICS, 2015 DHS, 2019 MICS, 2024 DHS</v>
+          </cell>
+          <cell r="E92" t="str">
+            <v>1992 DHS, 2000 DHS, 2004 DHS, 2006 MICS, 2010 DHS, 2013 MICS, 2015 DHS, 2019 MICS, 2024 DHS</v>
+          </cell>
+          <cell r="F92" t="str">
+            <v>1992 DHS, 2000 DHS, 2004 DHS, 2006 MICS, 2010 DHS, 2013 MICS, 2015 DHS, 2019 MICS, 2024 DHS</v>
+          </cell>
+          <cell r="J92" t="str">
+            <v>1992 DHS, 2000 DHS, 2004 DHS, 2006 MICS, 2010 DHS, 2013 MICS, 2015 DHS, 2019 MICS, 2024 DHS</v>
+          </cell>
+        </row>
+        <row r="93">
+          <cell r="A93">
+            <v>458</v>
+          </cell>
+          <cell r="B93" t="str">
+            <v>MYS</v>
+          </cell>
+          <cell r="C93" t="str">
+            <v>Malaysia</v>
+          </cell>
+          <cell r="G93" t="str">
+            <v>Some data from proxy country: 764</v>
+          </cell>
+          <cell r="H93" t="str">
+            <v>Some data from proxy country: 704</v>
+          </cell>
+          <cell r="I93" t="str">
+            <v>Some data from proxy country: 764</v>
+          </cell>
+          <cell r="J93" t="str">
+            <v>Some data from proxy country: Thailand</v>
+          </cell>
+        </row>
+        <row r="94">
+          <cell r="A94">
+            <v>462</v>
+          </cell>
+          <cell r="B94" t="str">
+            <v>MDV</v>
+          </cell>
+          <cell r="C94" t="str">
+            <v>Maldives</v>
+          </cell>
+          <cell r="D94" t="str">
+            <v>2009 DHS, 2016 DHS</v>
+          </cell>
+          <cell r="E94" t="str">
+            <v>2009 DHS, 2016 DHS</v>
+          </cell>
+          <cell r="F94" t="str">
+            <v>2009 DHS, 2016 DHS</v>
+          </cell>
+          <cell r="J94" t="str">
+            <v>2009 DHS, 2016 DHS</v>
+          </cell>
+        </row>
+        <row r="95">
+          <cell r="A95">
+            <v>466</v>
+          </cell>
+          <cell r="B95" t="str">
+            <v>MLI</v>
+          </cell>
+          <cell r="C95" t="str">
+            <v>Mali</v>
+          </cell>
+          <cell r="D95" t="str">
+            <v>1995 DHS, 2001 DHS, 2006 DHS, 2012 DHS, 2015 MICS, 2018 DHS, 2023 DHS</v>
+          </cell>
+          <cell r="E95" t="str">
+            <v>1995 DHS, 2001 DHS, 2006 DHS, 2012 DHS, 2015 MICS, 2018 DHS, 2023 DHS</v>
+          </cell>
+          <cell r="F95" t="str">
+            <v>1995 DHS, 2001 DHS, 2006 DHS, 2012 DHS, 2015 MICS, 2018 DHS, 2023 DHS</v>
+          </cell>
+          <cell r="J95" t="str">
+            <v>1995 DHS, 2001 DHS, 2006 DHS, 2012 DHS, 2015 MICS, 2018 DHS, 2023 DHS</v>
+          </cell>
+        </row>
+        <row r="96">
+          <cell r="A96">
+            <v>474</v>
+          </cell>
+          <cell r="B96" t="str">
+            <v>MTQ</v>
+          </cell>
+          <cell r="C96" t="str">
+            <v>Martinique</v>
+          </cell>
+          <cell r="G96" t="str">
+            <v>Some data from proxy country: 214</v>
+          </cell>
+          <cell r="H96" t="str">
+            <v>Some data from proxy country: 214</v>
+          </cell>
+          <cell r="I96" t="str">
+            <v>Some data from proxy country: 214</v>
+          </cell>
+          <cell r="J96" t="str">
+            <v>Some data from proxy country: Dominican Republic</v>
+          </cell>
+        </row>
+        <row r="97">
+          <cell r="A97">
+            <v>478</v>
+          </cell>
+          <cell r="B97" t="str">
+            <v>MRT</v>
+          </cell>
+          <cell r="C97" t="str">
+            <v>Mauritania</v>
+          </cell>
+          <cell r="D97" t="str">
+            <v>2011 MICS, 2015 MICS, 2019 DHS</v>
+          </cell>
+          <cell r="E97" t="str">
+            <v>2011 MICS, 2015 MICS, 2019 DHS</v>
+          </cell>
+          <cell r="F97" t="str">
+            <v>2011 MICS, 2015 MICS, 2019 DHS</v>
+          </cell>
+          <cell r="J97" t="str">
+            <v>2011 MICS, 2015 MICS, 2019 DHS</v>
+          </cell>
+        </row>
+        <row r="98">
+          <cell r="A98">
+            <v>480</v>
+          </cell>
+          <cell r="B98" t="str">
+            <v>MUS</v>
+          </cell>
+          <cell r="C98" t="str">
+            <v>Mauritius</v>
+          </cell>
+          <cell r="G98" t="str">
+            <v>Some data from proxy country: 450</v>
+          </cell>
+          <cell r="H98" t="str">
+            <v>Some data from proxy country: 450</v>
+          </cell>
+          <cell r="I98" t="str">
+            <v>Some data from proxy country: 450</v>
+          </cell>
+          <cell r="J98" t="str">
+            <v>Some data from proxy country: Madagascar</v>
+          </cell>
+        </row>
+        <row r="99">
+          <cell r="A99">
+            <v>175</v>
+          </cell>
+          <cell r="B99" t="str">
+            <v>MYT</v>
+          </cell>
+          <cell r="C99" t="str">
+            <v>Mayotte</v>
+          </cell>
+          <cell r="G99" t="str">
+            <v>Some data from proxy country: 450</v>
+          </cell>
+          <cell r="H99" t="str">
+            <v>Some data from proxy country: 450</v>
+          </cell>
+          <cell r="I99" t="str">
+            <v>Some data from proxy country: 450</v>
+          </cell>
+          <cell r="J99" t="str">
+            <v>Some data from proxy country: Madagascar</v>
+          </cell>
+        </row>
+        <row r="100">
+          <cell r="A100">
+            <v>484</v>
+          </cell>
+          <cell r="B100" t="str">
+            <v>MEX</v>
+          </cell>
+          <cell r="C100" t="str">
+            <v>Mexico</v>
+          </cell>
+          <cell r="D100" t="str">
+            <v>2015 MICS</v>
+          </cell>
+          <cell r="E100" t="str">
+            <v>2015 MICS</v>
+          </cell>
+          <cell r="F100" t="str">
+            <v>2015 MICS</v>
+          </cell>
+          <cell r="G100" t="str">
+            <v>Some data from proxy country: 320</v>
+          </cell>
+          <cell r="H100" t="str">
+            <v>Some data from proxy country: 320</v>
+          </cell>
+          <cell r="I100" t="str">
+            <v>Some data from proxy country: 320</v>
+          </cell>
+          <cell r="J100" t="str">
+            <v>2015 MICS Some data from proxy country: Guatemala</v>
+          </cell>
+        </row>
+        <row r="101">
+          <cell r="A101">
+            <v>583</v>
+          </cell>
+          <cell r="B101" t="str">
+            <v>FSM</v>
+          </cell>
+          <cell r="C101" t="str">
+            <v>Micronesia (Fed. States of)</v>
+          </cell>
+          <cell r="G101" t="str">
+            <v>Some data from proxy country: 360</v>
+          </cell>
+          <cell r="H101" t="str">
+            <v>Some data from proxy country: 360</v>
+          </cell>
+          <cell r="I101" t="str">
+            <v>Some data from proxy country: 360</v>
+          </cell>
+          <cell r="J101" t="str">
+            <v>Some data from proxy country: Indonesia</v>
+          </cell>
+        </row>
+        <row r="102">
+          <cell r="A102">
+            <v>496</v>
+          </cell>
+          <cell r="B102" t="str">
+            <v>MNG</v>
+          </cell>
+          <cell r="C102" t="str">
+            <v>Mongolia</v>
+          </cell>
+          <cell r="D102" t="str">
+            <v>2000 MICS, 2005 MICS, 2010 MICS, 2013 MICS, 2018 MICS</v>
+          </cell>
+          <cell r="E102" t="str">
+            <v>2013 MICS, 2018 MICS</v>
+          </cell>
+          <cell r="F102" t="str">
+            <v>2000 MICS, 2005 MICS, 2010 MICS, 2013 MICS, 2018 MICS</v>
+          </cell>
+          <cell r="G102" t="str">
+            <v>Some data from proxy country: 804</v>
+          </cell>
+          <cell r="H102" t="str">
+            <v>Some data from proxy country: 804</v>
+          </cell>
+          <cell r="I102" t="str">
+            <v>Some data from proxy country: 804</v>
+          </cell>
+          <cell r="J102" t="str">
+            <v>2000 MICS, 2005 MICS, 2010 MICS, 2013 MICS, 2018 MICS Some data from proxy country: Ukraine</v>
+          </cell>
+        </row>
+        <row r="103">
+          <cell r="A103">
+            <v>499</v>
+          </cell>
+          <cell r="B103" t="str">
+            <v>MNE</v>
+          </cell>
+          <cell r="C103" t="str">
+            <v>Montenegro</v>
+          </cell>
+          <cell r="D103" t="str">
+            <v>2005 MICS, 2013 MICS, 2018 MICS</v>
+          </cell>
+          <cell r="E103" t="str">
+            <v>2013 MICS, 2018 MICS</v>
+          </cell>
+          <cell r="F103" t="str">
+            <v>2005 MICS, 2013 MICS, 2018 MICS</v>
+          </cell>
+          <cell r="G103" t="str">
+            <v>Some data from proxy country: 51</v>
+          </cell>
+          <cell r="H103" t="str">
+            <v>Some data from proxy country: 51</v>
+          </cell>
+          <cell r="I103" t="str">
+            <v>Some data from proxy country: 51</v>
+          </cell>
+          <cell r="J103" t="str">
+            <v>2005 MICS, 2013 MICS, 2018 MICS Some data from proxy country: Armenia</v>
+          </cell>
+        </row>
+        <row r="104">
+          <cell r="A104">
+            <v>504</v>
+          </cell>
+          <cell r="B104" t="str">
+            <v>MAR</v>
+          </cell>
+          <cell r="C104" t="str">
+            <v>Morocco</v>
+          </cell>
+          <cell r="D104" t="str">
+            <v>1992 DHS, 2003 DHS</v>
+          </cell>
+          <cell r="E104" t="str">
+            <v>1992 DHS, 2003 DHS</v>
+          </cell>
+          <cell r="F104" t="str">
+            <v>1992 DHS, 2003 DHS</v>
+          </cell>
+          <cell r="J104" t="str">
+            <v>1992 DHS, 2003 DHS</v>
+          </cell>
+        </row>
+        <row r="105">
+          <cell r="A105">
+            <v>508</v>
+          </cell>
+          <cell r="B105" t="str">
+            <v>MOZ</v>
+          </cell>
+          <cell r="C105" t="str">
+            <v>Mozambique</v>
+          </cell>
+          <cell r="D105" t="str">
+            <v>1997 DHS, 2003 DHS, 2008 MICS, 2011 DHS, 2015 DHS, 2022 DHS</v>
+          </cell>
+          <cell r="E105" t="str">
+            <v>1997 DHS, 2003 DHS, 2011 DHS, 2015 DHS, 2022 DHS</v>
+          </cell>
+          <cell r="F105" t="str">
+            <v>1997 DHS, 2003 DHS, 2008 MICS, 2011 DHS, 2015 DHS, 2022 DHS</v>
+          </cell>
+          <cell r="J105" t="str">
+            <v>1997 DHS, 2003 DHS, 2008 MICS, 2011 DHS, 2015 DHS, 2022 DHS</v>
+          </cell>
+        </row>
+        <row r="106">
+          <cell r="A106">
+            <v>104</v>
+          </cell>
+          <cell r="B106" t="str">
+            <v>MMR</v>
+          </cell>
+          <cell r="C106" t="str">
+            <v>Myanmar</v>
+          </cell>
+          <cell r="D106" t="str">
+            <v>2015 DHS</v>
+          </cell>
+          <cell r="E106" t="str">
+            <v>2015 DHS</v>
+          </cell>
+          <cell r="F106" t="str">
+            <v>2015 DHS</v>
+          </cell>
+          <cell r="J106" t="str">
+            <v>2015 DHS</v>
+          </cell>
+        </row>
+        <row r="107">
+          <cell r="A107">
+            <v>516</v>
+          </cell>
+          <cell r="B107" t="str">
+            <v>NAM</v>
+          </cell>
+          <cell r="C107" t="str">
+            <v>Namibia</v>
+          </cell>
+          <cell r="D107" t="str">
+            <v>1992 DHS, 2000 DHS, 2006 DHS, 2013 DHS</v>
+          </cell>
+          <cell r="E107" t="str">
+            <v>1992 DHS, 2000 DHS, 2006 DHS, 2013 DHS</v>
+          </cell>
+          <cell r="F107" t="str">
+            <v>1992 DHS, 2000 DHS, 2006 DHS, 2013 DHS</v>
+          </cell>
+          <cell r="J107" t="str">
+            <v>1992 DHS, 2000 DHS, 2006 DHS, 2013 DHS</v>
+          </cell>
+        </row>
+        <row r="108">
+          <cell r="A108">
+            <v>524</v>
+          </cell>
+          <cell r="B108" t="str">
+            <v>NPL</v>
+          </cell>
+          <cell r="C108" t="str">
+            <v>Nepal</v>
+          </cell>
+          <cell r="D108" t="str">
+            <v>1996 DHS, 2001 DHS, 2006 DHS, 2011 DHS, 2014 MICS, 2016 DHS, 2019 MICS, 2022 DHS, 2024 MICS</v>
+          </cell>
+          <cell r="E108" t="str">
+            <v>1996 DHS, 2001 DHS, 2006 DHS, 2011 DHS, 2014 MICS, 2016 DHS, 2019 MICS, 2022 DHS, 2024 MICS</v>
+          </cell>
+          <cell r="F108" t="str">
+            <v>1996 DHS, 2001 DHS, 2006 DHS, 2011 DHS, 2014 MICS, 2016 DHS, 2019 MICS, 2022 DHS, 2024 MICS</v>
+          </cell>
+          <cell r="J108" t="str">
+            <v>1996 DHS, 2001 DHS, 2006 DHS, 2011 DHS, 2014 MICS, 2016 DHS, 2019 MICS, 2022 DHS, 2024 MICS</v>
+          </cell>
+        </row>
+        <row r="109">
+          <cell r="A109">
+            <v>530</v>
+          </cell>
+          <cell r="B109" t="str">
+            <v>ANT</v>
+          </cell>
+          <cell r="C109" t="str">
+            <v>Netherlands Antilles</v>
+          </cell>
+          <cell r="G109" t="str">
+            <v>Some data from proxy country: 214</v>
+          </cell>
+          <cell r="H109" t="str">
+            <v>Some data from proxy country: 214</v>
+          </cell>
+          <cell r="I109" t="str">
+            <v>Some data from proxy country: 214</v>
+          </cell>
+          <cell r="J109" t="str">
+            <v>Some data from proxy country: Dominican Republic</v>
+          </cell>
+        </row>
+        <row r="110">
+          <cell r="A110">
+            <v>540</v>
+          </cell>
+          <cell r="B110" t="str">
+            <v>NCL</v>
+          </cell>
+          <cell r="C110" t="str">
+            <v>New Caledonia</v>
+          </cell>
+          <cell r="G110" t="str">
+            <v>Some data from proxy country: 360</v>
+          </cell>
+          <cell r="H110" t="str">
+            <v>Some data from proxy country: 360</v>
+          </cell>
+          <cell r="I110" t="str">
+            <v>Some data from proxy country: 360</v>
+          </cell>
+          <cell r="J110" t="str">
+            <v>Some data from proxy country: Indonesia</v>
+          </cell>
+        </row>
+        <row r="111">
+          <cell r="A111">
+            <v>558</v>
+          </cell>
+          <cell r="B111" t="str">
+            <v>NIC</v>
+          </cell>
+          <cell r="C111" t="str">
+            <v>Nicaragua</v>
+          </cell>
+          <cell r="D111" t="str">
+            <v>1998 DHS, 2001 DHS</v>
+          </cell>
+          <cell r="E111" t="str">
+            <v>1998 DHS, 2001 DHS</v>
+          </cell>
+          <cell r="F111" t="str">
+            <v>1998 DHS, 2001 DHS</v>
+          </cell>
+          <cell r="J111" t="str">
+            <v>1998 DHS, 2001 DHS</v>
+          </cell>
+        </row>
+        <row r="112">
+          <cell r="A112">
+            <v>562</v>
+          </cell>
+          <cell r="B112" t="str">
+            <v>NER</v>
+          </cell>
+          <cell r="C112" t="str">
+            <v>Niger</v>
+          </cell>
+          <cell r="D112" t="str">
+            <v>1992 DHS, 1998 DHS, 2000 MICS, 2006 DHS, 2012 DHS</v>
+          </cell>
+          <cell r="E112" t="str">
+            <v>1992 DHS, 1998 DHS, 2000 MICS, 2006 DHS, 2012 DHS</v>
+          </cell>
+          <cell r="F112" t="str">
+            <v>1992 DHS, 1998 DHS, 2000 MICS, 2006 DHS, 2012 DHS</v>
+          </cell>
+          <cell r="J112" t="str">
+            <v>1992 DHS, 1998 DHS, 2000 MICS, 2006 DHS, 2012 DHS</v>
+          </cell>
+        </row>
+        <row r="113">
+          <cell r="A113">
+            <v>566</v>
+          </cell>
+          <cell r="B113" t="str">
+            <v>NGA</v>
+          </cell>
+          <cell r="C113" t="str">
+            <v>Nigeria</v>
+          </cell>
+          <cell r="D113" t="str">
+            <v>1990 DHS, 2003 DHS, 2007 MICS, 2008 DHS, 2011 MICS, 2013 DHS, 2016 MICS, 2018 DHS, 2021 MICS, 2024 DHS</v>
+          </cell>
+          <cell r="E113" t="str">
+            <v>1990 DHS, 2003 DHS, 2008 DHS, 2011 MICS, 2013 DHS, 2016 MICS, 2018 DHS, 2021 MICS, 2024 DHS</v>
+          </cell>
+          <cell r="F113" t="str">
+            <v>1990 DHS, 2003 DHS, 2007 MICS, 2008 DHS, 2011 MICS, 2013 DHS, 2016 MICS, 2018 DHS, 2021 MICS, 2024 DHS</v>
+          </cell>
+          <cell r="J113" t="str">
+            <v>1990 DHS, 2003 DHS, 2007 MICS, 2008 DHS, 2011 MICS, 2013 DHS, 2016 MICS, 2018 DHS, 2021 MICS, 2024 DHS</v>
+          </cell>
+        </row>
+        <row r="114">
+          <cell r="A114">
+            <v>807</v>
+          </cell>
+          <cell r="B114" t="str">
+            <v>MKD</v>
+          </cell>
+          <cell r="C114" t="str">
+            <v>North Macedonia</v>
+          </cell>
+          <cell r="D114" t="str">
+            <v>2011 MICS, 2018 MICS</v>
+          </cell>
+          <cell r="F114" t="str">
+            <v>2011 MICS, 2018 MICS</v>
+          </cell>
+          <cell r="G114" t="str">
+            <v>Some data from proxy country: 498</v>
+          </cell>
+          <cell r="H114" t="str">
+            <v>Some data from proxy country: 498</v>
+          </cell>
+          <cell r="I114" t="str">
+            <v>Some data from proxy country: 498</v>
+          </cell>
+          <cell r="J114" t="str">
+            <v>2011 MICS, 2018 MICS Some data from proxy country: Moldova</v>
+          </cell>
+        </row>
+        <row r="115">
+          <cell r="A115">
+            <v>512</v>
+          </cell>
+          <cell r="B115" t="str">
+            <v>OMN</v>
+          </cell>
+          <cell r="C115" t="str">
+            <v>Oman</v>
+          </cell>
+          <cell r="G115" t="str">
+            <v>Some data from proxy country: 792</v>
+          </cell>
+          <cell r="H115" t="str">
+            <v>Some data from proxy country: 792</v>
+          </cell>
+          <cell r="I115" t="str">
+            <v>Some data from proxy country: 792</v>
+          </cell>
+          <cell r="J115" t="str">
+            <v>Some data from proxy country: Turkey</v>
+          </cell>
+        </row>
+        <row r="116">
+          <cell r="A116">
+            <v>586</v>
+          </cell>
+          <cell r="B116" t="str">
+            <v>PAK</v>
+          </cell>
+          <cell r="C116" t="str">
+            <v>Pakistan</v>
+          </cell>
+          <cell r="D116" t="str">
+            <v>1990 DHS, 2006 DHS, 2012 DHS, 2017 DHS</v>
+          </cell>
+          <cell r="E116" t="str">
+            <v>1990 DHS, 2006 DHS, 2012 DHS, 2017 DHS</v>
+          </cell>
+          <cell r="F116" t="str">
+            <v>1990 DHS, 2006 DHS, 2012 DHS, 2017 DHS</v>
+          </cell>
+          <cell r="J116" t="str">
+            <v>1990 DHS, 2006 DHS, 2012 DHS, 2017 DHS</v>
+          </cell>
+        </row>
+        <row r="117">
+          <cell r="A117">
+            <v>591</v>
+          </cell>
+          <cell r="B117" t="str">
+            <v>PAN</v>
+          </cell>
+          <cell r="C117" t="str">
+            <v>Panama</v>
+          </cell>
+          <cell r="D117" t="str">
+            <v>2013 MICS</v>
+          </cell>
+          <cell r="E117" t="str">
+            <v>2013 MICS</v>
+          </cell>
+          <cell r="F117" t="str">
+            <v>2013 MICS</v>
+          </cell>
+          <cell r="G117" t="str">
+            <v>Some data from proxy country: 320</v>
+          </cell>
+          <cell r="H117" t="str">
+            <v>Some data from proxy country: 320</v>
+          </cell>
+          <cell r="I117" t="str">
+            <v>Some data from proxy country: 320</v>
+          </cell>
+          <cell r="J117" t="str">
+            <v>2013 MICS Some data from proxy country: Guatemala</v>
+          </cell>
+        </row>
+        <row r="118">
+          <cell r="A118">
+            <v>598</v>
+          </cell>
+          <cell r="B118" t="str">
+            <v>PNG</v>
+          </cell>
+          <cell r="C118" t="str">
+            <v>Papua New Guinea</v>
+          </cell>
+          <cell r="D118" t="str">
+            <v>2016 DHS</v>
+          </cell>
+          <cell r="E118" t="str">
+            <v>2016 DHS</v>
+          </cell>
+          <cell r="F118" t="str">
+            <v>2016 DHS</v>
+          </cell>
+          <cell r="J118" t="str">
+            <v>2016 DHS</v>
+          </cell>
+        </row>
+        <row r="119">
+          <cell r="A119">
+            <v>600</v>
+          </cell>
+          <cell r="B119" t="str">
+            <v>PRY</v>
+          </cell>
+          <cell r="C119" t="str">
+            <v>Paraguay</v>
+          </cell>
+          <cell r="D119" t="str">
+            <v>1990 DHS, 2016 MICS</v>
+          </cell>
+          <cell r="E119" t="str">
+            <v>1990 DHS, 2016 MICS</v>
+          </cell>
+          <cell r="F119" t="str">
+            <v>1990 DHS, 2016 MICS</v>
+          </cell>
+          <cell r="J119" t="str">
+            <v>1990 DHS, 2016 MICS</v>
+          </cell>
+        </row>
+        <row r="120">
+          <cell r="A120">
+            <v>604</v>
+          </cell>
+          <cell r="B120" t="str">
+            <v>PER</v>
+          </cell>
+          <cell r="C120" t="str">
+            <v>Peru</v>
+          </cell>
+          <cell r="D120" t="str">
+            <v>1991 DHS, 1996 DHS, 2000 DHS, 2004 DHS, 2009 DHS, 2010 DHS, 2011 DHS, 2012 DHS</v>
+          </cell>
+          <cell r="E120" t="str">
+            <v>1991 DHS, 1996 DHS, 2000 DHS, 2004 DHS, 2009 DHS, 2010 DHS, 2011 DHS, 2012 DHS</v>
+          </cell>
+          <cell r="F120" t="str">
+            <v>1991 DHS, 1996 DHS, 2000 DHS, 2004 DHS, 2009 DHS, 2010 DHS, 2011 DHS, 2012 DHS</v>
+          </cell>
+          <cell r="J120" t="str">
+            <v>1991 DHS, 1996 DHS, 2000 DHS, 2004 DHS, 2009 DHS, 2010 DHS, 2011 DHS, 2012 DHS</v>
+          </cell>
+        </row>
+        <row r="121">
+          <cell r="A121">
+            <v>608</v>
+          </cell>
+          <cell r="B121" t="str">
+            <v>PHL</v>
+          </cell>
+          <cell r="C121" t="str">
+            <v>Philippines</v>
+          </cell>
+          <cell r="D121" t="str">
+            <v>1993 DHS, 1998 DHS, 2003 DHS, 2008 DHS, 2013 DHS, 2017 DHS, 2022 DHS</v>
+          </cell>
+          <cell r="E121" t="str">
+            <v>1993 DHS, 1998 DHS, 2003 DHS, 2008 DHS, 2013 DHS, 2017 DHS, 2022 DHS</v>
+          </cell>
+          <cell r="F121" t="str">
+            <v>1993 DHS, 1998 DHS, 2003 DHS, 2008 DHS, 2013 DHS, 2017 DHS, 2022 DHS</v>
+          </cell>
+          <cell r="J121" t="str">
+            <v>1993 DHS, 1998 DHS, 2003 DHS, 2008 DHS, 2013 DHS, 2017 DHS, 2022 DHS</v>
+          </cell>
+        </row>
+        <row r="122">
+          <cell r="A122">
+            <v>616</v>
+          </cell>
+          <cell r="B122" t="str">
+            <v>POL</v>
+          </cell>
+          <cell r="C122" t="str">
+            <v>Poland</v>
+          </cell>
+          <cell r="G122" t="str">
+            <v>Some data from proxy country: 804</v>
+          </cell>
+          <cell r="H122" t="str">
+            <v>Some data from proxy country: 804</v>
+          </cell>
+          <cell r="I122" t="str">
+            <v>Some data from proxy country: 804</v>
+          </cell>
+          <cell r="J122" t="str">
+            <v>Some data from proxy country: Ukraine</v>
+          </cell>
+        </row>
+        <row r="123">
+          <cell r="A123">
+            <v>957</v>
+          </cell>
+          <cell r="B123" t="str">
+            <v/>
+          </cell>
+          <cell r="C123" t="str">
+            <v>Polynesia</v>
+          </cell>
+          <cell r="G123" t="str">
+            <v>Some data from proxy country: 360</v>
+          </cell>
+          <cell r="H123" t="str">
+            <v>Some data from proxy country: 360</v>
+          </cell>
+          <cell r="I123" t="str">
+            <v>Some data from proxy country: 360</v>
+          </cell>
+          <cell r="J123" t="str">
+            <v>Some data from proxy country: Indonesia</v>
+          </cell>
+        </row>
+        <row r="124">
+          <cell r="A124">
+            <v>630</v>
+          </cell>
+          <cell r="B124" t="str">
+            <v>PRI</v>
+          </cell>
+          <cell r="C124" t="str">
+            <v>Puerto Rico</v>
+          </cell>
+          <cell r="G124" t="str">
+            <v>Some data from proxy country: 214</v>
+          </cell>
+          <cell r="H124" t="str">
+            <v>Some data from proxy country: 214</v>
+          </cell>
+          <cell r="I124" t="str">
+            <v>Some data from proxy country: 214</v>
+          </cell>
+          <cell r="J124" t="str">
+            <v>Some data from proxy country: Dominican Republic</v>
+          </cell>
+        </row>
+        <row r="125">
+          <cell r="A125">
+            <v>634</v>
+          </cell>
+          <cell r="B125" t="str">
+            <v>QAT</v>
+          </cell>
+          <cell r="C125" t="str">
+            <v>Qatar</v>
+          </cell>
+          <cell r="D125" t="str">
+            <v>2012 MICS</v>
+          </cell>
+          <cell r="E125" t="str">
+            <v>2012 MICS</v>
+          </cell>
+          <cell r="F125" t="str">
+            <v>2012 MICS</v>
+          </cell>
+          <cell r="G125" t="str">
+            <v>Some data from proxy country: 792</v>
+          </cell>
+          <cell r="H125" t="str">
+            <v>Some data from proxy country: 792</v>
+          </cell>
+          <cell r="I125" t="str">
+            <v>Some data from proxy country: 792</v>
+          </cell>
+          <cell r="J125" t="str">
+            <v>2012 MICS Some data from proxy country: Turkey</v>
+          </cell>
+        </row>
+        <row r="126">
+          <cell r="A126">
+            <v>410</v>
+          </cell>
+          <cell r="B126" t="str">
+            <v>KOR</v>
+          </cell>
+          <cell r="C126" t="str">
+            <v>Republic of Korea</v>
+          </cell>
+          <cell r="G126" t="str">
+            <v>Some data from proxy country: 360</v>
+          </cell>
+          <cell r="H126" t="str">
+            <v>Some data from proxy country: 360</v>
+          </cell>
+          <cell r="I126" t="str">
+            <v>Some data from proxy country: 360</v>
+          </cell>
+          <cell r="J126" t="str">
+            <v>Some data from proxy country: Indonesia</v>
+          </cell>
+        </row>
+        <row r="127">
+          <cell r="A127">
+            <v>498</v>
+          </cell>
+          <cell r="B127" t="str">
+            <v>MDA</v>
+          </cell>
+          <cell r="C127" t="str">
+            <v>Republic of Moldova</v>
+          </cell>
+          <cell r="D127" t="str">
+            <v>2000 MICS, 2005 DHS, 2012 MICS</v>
+          </cell>
+          <cell r="E127" t="str">
+            <v>2005 DHS, 2012 MICS</v>
+          </cell>
+          <cell r="F127" t="str">
+            <v>2005 DHS, 2012 MICS</v>
+          </cell>
+          <cell r="J127" t="str">
+            <v>2005 DHS, 2012 MICS</v>
+          </cell>
+        </row>
+        <row r="128">
+          <cell r="A128">
+            <v>638</v>
+          </cell>
+          <cell r="B128" t="str">
+            <v>REU</v>
+          </cell>
+          <cell r="C128" t="str">
+            <v>Reunion</v>
+          </cell>
+          <cell r="G128" t="str">
+            <v>Some data from proxy country: 450</v>
+          </cell>
+          <cell r="H128" t="str">
+            <v>Some data from proxy country: 450</v>
+          </cell>
+          <cell r="I128" t="str">
+            <v>Some data from proxy country: 450</v>
+          </cell>
+          <cell r="J128" t="str">
+            <v>Some data from proxy country: Madagascar</v>
+          </cell>
+        </row>
+        <row r="129">
+          <cell r="A129">
+            <v>642</v>
+          </cell>
+          <cell r="B129" t="str">
+            <v>ROU</v>
+          </cell>
+          <cell r="C129" t="str">
+            <v>Romania</v>
+          </cell>
+          <cell r="G129" t="str">
+            <v>Some data from proxy country: 804</v>
+          </cell>
+          <cell r="H129" t="str">
+            <v>Some data from proxy country: 804</v>
+          </cell>
+          <cell r="I129" t="str">
+            <v>Some data from proxy country: 804</v>
+          </cell>
+          <cell r="J129" t="str">
+            <v>Some data from proxy country: Ukraine</v>
+          </cell>
+        </row>
+        <row r="130">
+          <cell r="A130">
+            <v>643</v>
+          </cell>
+          <cell r="B130" t="str">
+            <v>RUS</v>
+          </cell>
+          <cell r="C130" t="str">
+            <v>Russian Federation</v>
+          </cell>
+          <cell r="G130" t="str">
+            <v>Some data from proxy country: 804</v>
+          </cell>
+          <cell r="H130" t="str">
+            <v>Some data from proxy country: 804</v>
+          </cell>
+          <cell r="I130" t="str">
+            <v>Some data from proxy country: 804</v>
+          </cell>
+          <cell r="J130" t="str">
+            <v>Some data from proxy country: Ukraine</v>
+          </cell>
+        </row>
+        <row r="131">
+          <cell r="A131">
+            <v>646</v>
+          </cell>
+          <cell r="B131" t="str">
+            <v>RWA</v>
+          </cell>
+          <cell r="C131" t="str">
+            <v>Rwanda</v>
+          </cell>
+          <cell r="D131" t="str">
+            <v>1992 DHS, 2000 DHS, 2005 DHS, 2010 DHS, 2014 DHS, 2019 DHS</v>
+          </cell>
+          <cell r="E131" t="str">
+            <v>1992 DHS, 2000 DHS, 2005 DHS, 2010 DHS, 2014 DHS, 2019 DHS</v>
+          </cell>
+          <cell r="F131" t="str">
+            <v>1992 DHS, 2000 DHS, 2005 DHS, 2010 DHS, 2014 DHS, 2019 DHS</v>
+          </cell>
+          <cell r="J131" t="str">
+            <v>1992 DHS, 2000 DHS, 2005 DHS, 2010 DHS, 2014 DHS, 2019 DHS</v>
+          </cell>
+        </row>
+        <row r="132">
+          <cell r="A132">
+            <v>662</v>
+          </cell>
+          <cell r="B132" t="str">
+            <v>LCA</v>
+          </cell>
+          <cell r="C132" t="str">
+            <v>Saint Lucia</v>
+          </cell>
+          <cell r="D132" t="str">
+            <v>2012 MICS</v>
+          </cell>
+          <cell r="E132" t="str">
+            <v>2012 MICS</v>
+          </cell>
+          <cell r="F132" t="str">
+            <v>2012 MICS</v>
+          </cell>
+          <cell r="G132" t="str">
+            <v>Some data from proxy country: 214</v>
+          </cell>
+          <cell r="H132" t="str">
+            <v>Some data from proxy country: 214</v>
+          </cell>
+          <cell r="I132" t="str">
+            <v>Some data from proxy country: 214</v>
+          </cell>
+          <cell r="J132" t="str">
+            <v>2012 MICS Some data from proxy country: Dominican Republic</v>
+          </cell>
+        </row>
+        <row r="133">
+          <cell r="A133">
+            <v>670</v>
+          </cell>
+          <cell r="B133" t="str">
+            <v>VCT</v>
+          </cell>
+          <cell r="C133" t="str">
+            <v>Saint Vincent and the Grenadines</v>
+          </cell>
+          <cell r="G133" t="str">
+            <v>Some data from proxy country: 214</v>
+          </cell>
+          <cell r="H133" t="str">
+            <v>Some data from proxy country: 214</v>
+          </cell>
+          <cell r="I133" t="str">
+            <v>Some data from proxy country: 214</v>
+          </cell>
+          <cell r="J133" t="str">
+            <v>Some data from proxy country: Dominican Republic</v>
+          </cell>
+        </row>
+        <row r="134">
+          <cell r="A134">
+            <v>882</v>
+          </cell>
+          <cell r="B134" t="str">
+            <v>WSM</v>
+          </cell>
+          <cell r="C134" t="str">
+            <v>Samoa</v>
+          </cell>
+          <cell r="D134" t="str">
+            <v>2019 MICS</v>
+          </cell>
+          <cell r="E134" t="str">
+            <v>2019 MICS</v>
+          </cell>
+          <cell r="F134" t="str">
+            <v>2019 MICS</v>
+          </cell>
+          <cell r="G134" t="str">
+            <v>Some data from proxy country: 360</v>
+          </cell>
+          <cell r="H134" t="str">
+            <v>Some data from proxy country: 360</v>
+          </cell>
+          <cell r="I134" t="str">
+            <v>Some data from proxy country: 360</v>
+          </cell>
+          <cell r="J134" t="str">
+            <v>2019 MICS Some data from proxy country: Indonesia</v>
+          </cell>
+        </row>
+        <row r="135">
+          <cell r="A135">
+            <v>678</v>
+          </cell>
+          <cell r="B135" t="str">
+            <v>STP</v>
+          </cell>
+          <cell r="C135" t="str">
+            <v>Sao Tome and Principe</v>
+          </cell>
+          <cell r="D135" t="str">
+            <v>2000 MICS, 2008 DHS, 2014 MICS, 2019 MICS</v>
+          </cell>
+          <cell r="E135" t="str">
+            <v>2008 DHS, 2014 MICS, 2019 MICS</v>
+          </cell>
+          <cell r="F135" t="str">
+            <v>2008 DHS, 2014 MICS, 2019 MICS</v>
+          </cell>
+          <cell r="J135" t="str">
+            <v>2008 DHS, 2014 MICS, 2019 MICS</v>
+          </cell>
+        </row>
+        <row r="136">
+          <cell r="A136">
+            <v>682</v>
+          </cell>
+          <cell r="B136" t="str">
+            <v>SAU</v>
+          </cell>
+          <cell r="C136" t="str">
+            <v>Saudi Arabia</v>
+          </cell>
+          <cell r="G136" t="str">
+            <v>Some data from proxy country: 792</v>
+          </cell>
+          <cell r="H136" t="str">
+            <v>Some data from proxy country: 792</v>
+          </cell>
+          <cell r="I136" t="str">
+            <v>Some data from proxy country: 792</v>
+          </cell>
+          <cell r="J136" t="str">
+            <v>Some data from proxy country: Turkey</v>
+          </cell>
+        </row>
+        <row r="137">
+          <cell r="A137">
+            <v>686</v>
+          </cell>
+          <cell r="B137" t="str">
+            <v>SEN</v>
+          </cell>
+          <cell r="C137" t="str">
+            <v>Senegal</v>
+          </cell>
+          <cell r="D137" t="str">
+            <v>1992 DHS, 1997 DHS, 2005 DHS, 2010 DHS, 2012 DHS, 2014 DHS, 2015 DHS, 2016 DHS, 2017 DHS, 2018 DHS, 2019 DHS, 2023 DHS</v>
+          </cell>
+          <cell r="E137" t="str">
+            <v>1992 DHS, 1997 DHS, 2005 DHS, 2010 DHS, 2012 DHS, 2014 DHS, 2015 DHS, 2016 DHS, 2017 DHS, 2018 DHS, 2019 DHS, 2023 DHS</v>
+          </cell>
+          <cell r="F137" t="str">
+            <v>1992 DHS, 1997 DHS, 2005 DHS, 2010 DHS, 2012 DHS, 2014 DHS, 2015 DHS, 2016 DHS, 2017 DHS, 2018 DHS, 2019 DHS, 2023 DHS</v>
+          </cell>
+          <cell r="J137" t="str">
+            <v>1992 DHS, 1997 DHS, 2005 DHS, 2010 DHS, 2012 DHS, 2014 DHS, 2015 DHS, 2016 DHS, 2017 DHS, 2018 DHS, 2019 DHS, 2023 DHS</v>
+          </cell>
+        </row>
+        <row r="138">
+          <cell r="A138">
+            <v>688</v>
+          </cell>
+          <cell r="B138" t="str">
+            <v>SRB</v>
+          </cell>
+          <cell r="C138" t="str">
+            <v>Serbia</v>
+          </cell>
+          <cell r="D138" t="str">
+            <v>2005 MICS, 2010 MICS, 2014 MICS, 2019 MICS</v>
+          </cell>
+          <cell r="E138" t="str">
+            <v>2010 MICS, 2019 MICS</v>
+          </cell>
+          <cell r="F138" t="str">
+            <v>2010 MICS, 2014 MICS, 2019 MICS</v>
+          </cell>
+          <cell r="G138" t="str">
+            <v>Some data from proxy country: 498</v>
+          </cell>
+          <cell r="H138" t="str">
+            <v>Some data from proxy country: 498</v>
+          </cell>
+          <cell r="I138" t="str">
+            <v>Some data from proxy country: 498</v>
+          </cell>
+          <cell r="J138" t="str">
+            <v>2010 MICS, 2014 MICS, 2019 MICS Some data from proxy country: Moldova</v>
+          </cell>
+        </row>
+        <row r="139">
+          <cell r="A139">
+            <v>690</v>
+          </cell>
+          <cell r="B139" t="str">
+            <v>SYC</v>
+          </cell>
+          <cell r="C139" t="str">
+            <v>Seychelles</v>
+          </cell>
+          <cell r="G139" t="str">
+            <v>Some data from proxy country: 450</v>
+          </cell>
+          <cell r="H139" t="str">
+            <v>Some data from proxy country: 450</v>
+          </cell>
+          <cell r="I139" t="str">
+            <v>Some data from proxy country: 450</v>
+          </cell>
+          <cell r="J139" t="str">
+            <v>Some data from proxy country: Madagascar</v>
+          </cell>
+        </row>
+        <row r="140">
+          <cell r="A140">
+            <v>694</v>
+          </cell>
+          <cell r="B140" t="str">
+            <v>SLE</v>
+          </cell>
+          <cell r="C140" t="str">
+            <v>Sierra Leone</v>
+          </cell>
+          <cell r="D140" t="str">
+            <v>2000 MICS, 2005 MICS, 2008 DHS, 2010 MICS, 2013 DHS, 2017 MICS, 2019 DHS</v>
+          </cell>
+          <cell r="E140" t="str">
+            <v>2008 DHS, 2010 MICS, 2013 DHS, 2017 MICS, 2019 DHS</v>
+          </cell>
+          <cell r="F140" t="str">
+            <v>2000 MICS, 2005 MICS, 2008 DHS, 2010 MICS, 2013 DHS, 2017 MICS, 2019 DHS</v>
+          </cell>
+          <cell r="J140" t="str">
+            <v>2000 MICS, 2005 MICS, 2008 DHS, 2010 MICS, 2013 DHS, 2017 MICS, 2019 DHS</v>
+          </cell>
+        </row>
+        <row r="141">
+          <cell r="A141">
+            <v>702</v>
+          </cell>
+          <cell r="B141" t="str">
+            <v>SGP</v>
+          </cell>
+          <cell r="C141" t="str">
+            <v>Singapore</v>
+          </cell>
+          <cell r="G141" t="str">
+            <v>Some data from proxy country: 764</v>
+          </cell>
+          <cell r="H141" t="str">
+            <v>Some data from proxy country: 704</v>
+          </cell>
+          <cell r="I141" t="str">
+            <v>Some data from proxy country: 764</v>
+          </cell>
+          <cell r="J141" t="str">
+            <v>Some data from proxy country: Thailand</v>
+          </cell>
+        </row>
+        <row r="142">
+          <cell r="A142">
+            <v>703</v>
+          </cell>
+          <cell r="B142" t="str">
+            <v>SVK</v>
+          </cell>
+          <cell r="C142" t="str">
+            <v>Slovakia</v>
+          </cell>
+          <cell r="G142" t="str">
+            <v>Some data from proxy country: 804</v>
+          </cell>
+          <cell r="H142" t="str">
+            <v>Some data from proxy country: 804</v>
+          </cell>
+          <cell r="I142" t="str">
+            <v>Some data from proxy country: 804</v>
+          </cell>
+          <cell r="J142" t="str">
+            <v>Some data from proxy country: Ukraine</v>
+          </cell>
+        </row>
+        <row r="143">
+          <cell r="A143">
+            <v>705</v>
+          </cell>
+          <cell r="B143" t="str">
+            <v>SVN</v>
+          </cell>
+          <cell r="C143" t="str">
+            <v>Slovenia</v>
+          </cell>
+          <cell r="G143" t="str">
+            <v>Some data from proxy country: 498</v>
+          </cell>
+          <cell r="H143" t="str">
+            <v>Some data from proxy country: 498</v>
+          </cell>
+          <cell r="I143" t="str">
+            <v>Some data from proxy country: 498</v>
+          </cell>
+          <cell r="J143" t="str">
+            <v>Some data from proxy country: Moldova</v>
+          </cell>
+        </row>
+        <row r="144">
+          <cell r="A144">
+            <v>90</v>
+          </cell>
+          <cell r="B144" t="str">
+            <v>SLB</v>
+          </cell>
+          <cell r="C144" t="str">
+            <v>Solomon Islands</v>
+          </cell>
+          <cell r="G144" t="str">
+            <v>Some data from proxy country: 360</v>
+          </cell>
+          <cell r="H144" t="str">
+            <v>Some data from proxy country: 360</v>
+          </cell>
+          <cell r="I144" t="str">
+            <v>Some data from proxy country: 360</v>
+          </cell>
+          <cell r="J144" t="str">
+            <v>Some data from proxy country: Indonesia</v>
+          </cell>
+        </row>
+        <row r="145">
+          <cell r="A145">
+            <v>706</v>
+          </cell>
+          <cell r="B145" t="str">
+            <v>SOM</v>
+          </cell>
+          <cell r="C145" t="str">
+            <v>Somalia</v>
+          </cell>
+          <cell r="D145" t="str">
+            <v>2006 MICS</v>
+          </cell>
+          <cell r="E145" t="str">
+            <v>2006 MICS</v>
+          </cell>
+          <cell r="F145" t="str">
+            <v>2006 MICS</v>
+          </cell>
+          <cell r="G145" t="str">
+            <v>Some data from proxy country: 231</v>
+          </cell>
+          <cell r="H145" t="str">
+            <v>Some data from proxy country: 231</v>
+          </cell>
+          <cell r="I145" t="str">
+            <v>Some data from proxy country: 231</v>
+          </cell>
+          <cell r="J145" t="str">
+            <v>2006 MICS Some data from proxy country: Ethiopia</v>
+          </cell>
+        </row>
+        <row r="146">
+          <cell r="A146">
+            <v>710</v>
+          </cell>
+          <cell r="B146" t="str">
+            <v>ZAF</v>
+          </cell>
+          <cell r="C146" t="str">
+            <v>South Africa</v>
+          </cell>
+          <cell r="D146" t="str">
+            <v>1998 DHS, 2016 DHS</v>
+          </cell>
+          <cell r="E146" t="str">
+            <v>1998 DHS, 2016 DHS</v>
+          </cell>
+          <cell r="F146" t="str">
+            <v>1998 DHS, 2016 DHS</v>
+          </cell>
+          <cell r="J146" t="str">
+            <v>1998 DHS, 2016 DHS</v>
+          </cell>
+        </row>
+        <row r="147">
+          <cell r="A147">
+            <v>728</v>
+          </cell>
+          <cell r="B147" t="str">
+            <v>SSD</v>
+          </cell>
+          <cell r="C147" t="str">
+            <v>South Sudan</v>
+          </cell>
+          <cell r="D147" t="str">
+            <v>2010 MICS</v>
+          </cell>
+          <cell r="E147" t="str">
+            <v>2010 MICS</v>
+          </cell>
+          <cell r="F147" t="str">
+            <v>2010 MICS</v>
+          </cell>
+          <cell r="G147" t="str">
+            <v>Some data from proxy country: 800</v>
+          </cell>
+          <cell r="H147" t="str">
+            <v>Some data from proxy country: 800</v>
+          </cell>
+          <cell r="I147" t="str">
+            <v>Some data from proxy country: 800</v>
+          </cell>
+          <cell r="J147" t="str">
+            <v>2010 MICS Some data from proxy country: Uganda</v>
+          </cell>
+        </row>
+        <row r="148">
+          <cell r="A148">
+            <v>144</v>
+          </cell>
+          <cell r="B148" t="str">
+            <v>LKA</v>
+          </cell>
+          <cell r="C148" t="str">
+            <v>Sri Lanka</v>
+          </cell>
+          <cell r="G148" t="str">
+            <v>Some data from proxy country: 356</v>
+          </cell>
+          <cell r="H148" t="str">
+            <v>Some data from proxy country: 356</v>
+          </cell>
+          <cell r="I148" t="str">
+            <v>Some data from proxy country: 356</v>
+          </cell>
+          <cell r="J148" t="str">
+            <v>Some data from proxy country: India</v>
+          </cell>
+        </row>
+        <row r="149">
+          <cell r="A149">
+            <v>275</v>
+          </cell>
+          <cell r="B149" t="str">
+            <v>PSE</v>
+          </cell>
+          <cell r="C149" t="str">
+            <v>State of Palestine</v>
+          </cell>
+          <cell r="D149" t="str">
+            <v>2010 MICS, 2014 MICS, 2019 MICS</v>
+          </cell>
+          <cell r="E149" t="str">
+            <v>2010 MICS, 2014 MICS, 2019 MICS</v>
+          </cell>
+          <cell r="F149" t="str">
+            <v>2014 MICS, 2019 MICS</v>
+          </cell>
+          <cell r="G149" t="str">
+            <v>Some data from proxy country: 400</v>
+          </cell>
+          <cell r="H149" t="str">
+            <v>Some data from proxy country: 400</v>
+          </cell>
+          <cell r="I149" t="str">
+            <v>Some data from proxy country: 400</v>
+          </cell>
+          <cell r="J149" t="str">
+            <v>2014 MICS, 2019 MICS Some data from proxy country: Jordan</v>
+          </cell>
+        </row>
+        <row r="150">
+          <cell r="A150">
+            <v>729</v>
+          </cell>
+          <cell r="B150" t="str">
+            <v>SDN</v>
+          </cell>
+          <cell r="C150" t="str">
+            <v>Sudan</v>
+          </cell>
+          <cell r="D150" t="str">
+            <v>2014 MICS</v>
+          </cell>
+          <cell r="E150" t="str">
+            <v>2014 MICS</v>
+          </cell>
+          <cell r="F150" t="str">
+            <v>2014 MICS</v>
+          </cell>
+          <cell r="G150" t="str">
+            <v>Some data from proxy country: 800</v>
+          </cell>
+          <cell r="H150" t="str">
+            <v>Some data from proxy country: 800</v>
+          </cell>
+          <cell r="I150" t="str">
+            <v>Some data from proxy country: 800</v>
+          </cell>
+          <cell r="J150" t="str">
+            <v>2014 MICS Some data from proxy country: Uganda</v>
+          </cell>
+        </row>
+        <row r="151">
+          <cell r="A151">
+            <v>740</v>
+          </cell>
+          <cell r="B151" t="str">
+            <v>SUR</v>
+          </cell>
+          <cell r="C151" t="str">
+            <v>Suriname</v>
+          </cell>
+          <cell r="D151" t="str">
+            <v>1999 MICS, 2006 MICS, 2010 MICS, 2018 MICS</v>
+          </cell>
+          <cell r="E151" t="str">
+            <v>2010 MICS, 2018 MICS</v>
+          </cell>
+          <cell r="F151" t="str">
+            <v>1999 MICS, 2006 MICS, 2010 MICS, 2018 MICS</v>
+          </cell>
+          <cell r="G151" t="str">
+            <v>Some data from proxy country: 76</v>
+          </cell>
+          <cell r="H151" t="str">
+            <v>Some data from proxy country: 76</v>
+          </cell>
+          <cell r="I151" t="str">
+            <v>Some data from proxy country: 76</v>
+          </cell>
+          <cell r="J151" t="str">
+            <v>1999 MICS, 2006 MICS, 2010 MICS, 2018 MICS Some data from proxy country: Brazil</v>
+          </cell>
+        </row>
+        <row r="152">
+          <cell r="A152">
+            <v>760</v>
+          </cell>
+          <cell r="B152" t="str">
+            <v>SYR</v>
+          </cell>
+          <cell r="C152" t="str">
+            <v>Syrian Arab Republic</v>
+          </cell>
+          <cell r="D152" t="str">
+            <v>2006 MICS</v>
+          </cell>
+          <cell r="E152" t="str">
+            <v>2006 MICS</v>
+          </cell>
+          <cell r="F152" t="str">
+            <v>2006 MICS</v>
+          </cell>
+          <cell r="G152" t="str">
+            <v>Some data from proxy country: 792</v>
+          </cell>
+          <cell r="H152" t="str">
+            <v>Some data from proxy country: 792</v>
+          </cell>
+          <cell r="I152" t="str">
+            <v>Some data from proxy country: 792</v>
+          </cell>
+          <cell r="J152" t="str">
+            <v>2006 MICS Some data from proxy country: Turkey</v>
+          </cell>
+        </row>
+        <row r="153">
+          <cell r="A153">
+            <v>762</v>
+          </cell>
+          <cell r="B153" t="str">
+            <v>TJK</v>
+          </cell>
+          <cell r="C153" t="str">
+            <v>Tajikistan</v>
+          </cell>
+          <cell r="D153" t="str">
+            <v>2005 MICS, 2012 DHS, 2017 DHS, 2023 DHS</v>
+          </cell>
+          <cell r="E153" t="str">
+            <v>2005 MICS, 2012 DHS, 2017 DHS, 2023 DHS</v>
+          </cell>
+          <cell r="F153" t="str">
+            <v>2005 MICS, 2012 DHS, 2017 DHS, 2023 DHS</v>
+          </cell>
+          <cell r="J153" t="str">
+            <v>2005 MICS, 2012 DHS, 2017 DHS, 2023 DHS</v>
+          </cell>
+        </row>
+        <row r="154">
+          <cell r="A154">
+            <v>764</v>
+          </cell>
+          <cell r="B154" t="str">
+            <v>THA</v>
+          </cell>
+          <cell r="C154" t="str">
+            <v>Thailand</v>
+          </cell>
+          <cell r="D154" t="str">
+            <v>2005 MICS, 2012 MICS, 2015 MICS, 2019 MICS, 2022 MICS</v>
+          </cell>
+          <cell r="F154" t="str">
+            <v>2012 MICS, 2015 MICS, 2019 MICS, 2022 MICS</v>
+          </cell>
+          <cell r="G154" t="str">
+            <v>Some data from proxy country: 704</v>
+          </cell>
+          <cell r="H154" t="str">
+            <v>Some data from proxy country: 704</v>
+          </cell>
+          <cell r="I154" t="str">
+            <v>Some data from proxy country: 704</v>
+          </cell>
+          <cell r="J154" t="str">
+            <v>2012 MICS, 2015 MICS, 2019 MICS, 2022 MICS Some data from proxy country: Viet Nam</v>
+          </cell>
+        </row>
+        <row r="155">
+          <cell r="A155">
+            <v>626</v>
+          </cell>
+          <cell r="B155" t="str">
+            <v>TLS</v>
+          </cell>
+          <cell r="C155" t="str">
+            <v>Timor-Leste</v>
+          </cell>
+          <cell r="D155" t="str">
+            <v>2009 DHS, 2016 DHS</v>
+          </cell>
+          <cell r="E155" t="str">
+            <v>2009 DHS, 2016 DHS</v>
+          </cell>
+          <cell r="F155" t="str">
+            <v>2009 DHS, 2016 DHS</v>
+          </cell>
+          <cell r="J155" t="str">
+            <v>2009 DHS, 2016 DHS</v>
+          </cell>
+        </row>
+        <row r="156">
+          <cell r="A156">
+            <v>768</v>
+          </cell>
+          <cell r="B156" t="str">
+            <v>TGO</v>
+          </cell>
+          <cell r="C156" t="str">
+            <v>Togo</v>
+          </cell>
+          <cell r="D156" t="str">
+            <v>1998 DHS, 2000 MICS, 2006 MICS, 2010 MICS, 2013 DHS, 2017 MICS</v>
+          </cell>
+          <cell r="E156" t="str">
+            <v>1998 DHS, 2010 MICS, 2013 DHS, 2017 MICS</v>
+          </cell>
+          <cell r="F156" t="str">
+            <v>1998 DHS, 2006 MICS, 2010 MICS, 2013 DHS, 2017 MICS</v>
+          </cell>
+          <cell r="J156" t="str">
+            <v>1998 DHS, 2006 MICS, 2010 MICS, 2013 DHS, 2017 MICS</v>
+          </cell>
+        </row>
+        <row r="157">
+          <cell r="A157">
+            <v>776</v>
+          </cell>
+          <cell r="B157" t="str">
+            <v>TON</v>
+          </cell>
+          <cell r="C157" t="str">
+            <v>Tonga</v>
+          </cell>
+          <cell r="D157" t="str">
+            <v>2019 MICS</v>
+          </cell>
+          <cell r="E157" t="str">
+            <v>2019 MICS</v>
+          </cell>
+          <cell r="F157" t="str">
+            <v>2019 MICS</v>
+          </cell>
+          <cell r="G157" t="str">
+            <v>Some data from proxy country: 360</v>
+          </cell>
+          <cell r="H157" t="str">
+            <v>Some data from proxy country: 360</v>
+          </cell>
+          <cell r="I157" t="str">
+            <v>Some data from proxy country: 360</v>
+          </cell>
+          <cell r="J157" t="str">
+            <v>2019 MICS Some data from proxy country: Indonesia</v>
+          </cell>
+        </row>
+        <row r="158">
+          <cell r="A158">
+            <v>780</v>
+          </cell>
+          <cell r="B158" t="str">
+            <v>TTO</v>
+          </cell>
+          <cell r="C158" t="str">
+            <v>Trinidad and Tobago</v>
+          </cell>
+          <cell r="D158" t="str">
+            <v>2000 MICS, 2006 MICS, 2011 MICS, 2022 MICS</v>
+          </cell>
+          <cell r="E158" t="str">
+            <v>2011 MICS, 2022 MICS</v>
+          </cell>
+          <cell r="F158" t="str">
+            <v>2000 MICS, 2006 MICS, 2011 MICS, 2022 MICS</v>
+          </cell>
+          <cell r="G158" t="str">
+            <v>Some data from proxy country: 214</v>
+          </cell>
+          <cell r="H158" t="str">
+            <v>Some data from proxy country: 214</v>
+          </cell>
+          <cell r="I158" t="str">
+            <v>Some data from proxy country: 214</v>
+          </cell>
+          <cell r="J158" t="str">
+            <v>2000 MICS, 2006 MICS, 2011 MICS, 2022 MICS Some data from proxy country: Dominican Republic</v>
+          </cell>
+        </row>
+        <row r="159">
+          <cell r="A159">
+            <v>788</v>
+          </cell>
+          <cell r="B159" t="str">
+            <v>TUN</v>
+          </cell>
+          <cell r="C159" t="str">
+            <v>Tunisia</v>
+          </cell>
+          <cell r="D159" t="str">
+            <v>2011 MICS, 2018 MICS, 2023 MICS</v>
+          </cell>
+          <cell r="E159" t="str">
+            <v>2011 MICS, 2018 MICS, 2023 MICS</v>
+          </cell>
+          <cell r="F159" t="str">
+            <v>2011 MICS, 2018 MICS, 2023 MICS</v>
+          </cell>
+          <cell r="G159" t="str">
+            <v>Some data from proxy country: 504</v>
+          </cell>
+          <cell r="H159" t="str">
+            <v>Some data from proxy country: 504</v>
+          </cell>
+          <cell r="I159" t="str">
+            <v>Some data from proxy country: 504</v>
+          </cell>
+          <cell r="J159" t="str">
+            <v>2011 MICS, 2018 MICS, 2023 MICS Some data from proxy country: Morocco</v>
+          </cell>
+        </row>
+        <row r="160">
+          <cell r="A160">
+            <v>792</v>
+          </cell>
+          <cell r="B160" t="str">
+            <v>TUR</v>
+          </cell>
+          <cell r="C160" t="str">
+            <v>Turkey</v>
+          </cell>
+          <cell r="D160" t="str">
+            <v>1993 DHS, 1998 DHS, 2003 DHS, 2013 DHS</v>
+          </cell>
+          <cell r="E160" t="str">
+            <v>1993 DHS, 1998 DHS, 2003 DHS, 2013 DHS</v>
+          </cell>
+          <cell r="F160" t="str">
+            <v>1993 DHS, 1998 DHS, 2003 DHS, 2013 DHS</v>
+          </cell>
+          <cell r="J160" t="str">
+            <v>1993 DHS, 1998 DHS, 2003 DHS, 2013 DHS</v>
+          </cell>
+        </row>
+        <row r="161">
+          <cell r="A161">
+            <v>795</v>
+          </cell>
+          <cell r="B161" t="str">
+            <v>TKM</v>
+          </cell>
+          <cell r="C161" t="str">
+            <v>Turkmenistan</v>
+          </cell>
+          <cell r="D161" t="str">
+            <v>2006 MICS, 2015 MICS, 2019 MICS, 2024 MICS</v>
+          </cell>
+          <cell r="E161" t="str">
+            <v>2006 MICS, 2015 MICS, 2019 MICS, 2024 MICS</v>
+          </cell>
+          <cell r="F161" t="str">
+            <v>2006 MICS, 2015 MICS, 2019 MICS, 2024 MICS</v>
+          </cell>
+          <cell r="G161" t="str">
+            <v>Some data from proxy country: 398</v>
+          </cell>
+          <cell r="H161" t="str">
+            <v>Some data from proxy country: 398</v>
+          </cell>
+          <cell r="I161" t="str">
+            <v>Some data from proxy country: 398</v>
+          </cell>
+          <cell r="J161" t="str">
+            <v>2006 MICS, 2015 MICS, 2019 MICS, 2024 MICS Some data from proxy country: Kazakhstan</v>
+          </cell>
+        </row>
+        <row r="162">
+          <cell r="A162">
+            <v>800</v>
+          </cell>
+          <cell r="B162" t="str">
+            <v>UGA</v>
+          </cell>
+          <cell r="C162" t="str">
+            <v>Uganda</v>
+          </cell>
+          <cell r="D162" t="str">
+            <v>1995 DHS, 2000 DHS, 2006 DHS, 2011 DHS, 2016 DHS</v>
+          </cell>
+          <cell r="E162" t="str">
+            <v>1995 DHS, 2000 DHS, 2006 DHS, 2011 DHS, 2016 DHS</v>
+          </cell>
+          <cell r="F162" t="str">
+            <v>1995 DHS, 2000 DHS, 2006 DHS, 2011 DHS, 2016 DHS</v>
+          </cell>
+          <cell r="J162" t="str">
+            <v>1995 DHS, 2000 DHS, 2006 DHS, 2011 DHS, 2016 DHS</v>
+          </cell>
+        </row>
+        <row r="163">
+          <cell r="A163">
+            <v>804</v>
+          </cell>
+          <cell r="B163" t="str">
+            <v>UKR</v>
+          </cell>
+          <cell r="C163" t="str">
+            <v>Ukraine</v>
+          </cell>
+          <cell r="D163" t="str">
+            <v>2005 MICS, 2007 DHS, 2012 MICS</v>
+          </cell>
+          <cell r="E163" t="str">
+            <v>2007 DHS, 2012 MICS</v>
+          </cell>
+          <cell r="F163" t="str">
+            <v>2005 MICS, 2007 DHS, 2012 MICS</v>
+          </cell>
+          <cell r="J163" t="str">
+            <v>2005 MICS, 2007 DHS, 2012 MICS</v>
+          </cell>
+        </row>
+        <row r="164">
+          <cell r="A164">
+            <v>784</v>
+          </cell>
+          <cell r="B164" t="str">
+            <v>ARE</v>
+          </cell>
+          <cell r="C164" t="str">
+            <v>United Arab Emirates</v>
+          </cell>
+          <cell r="G164" t="str">
+            <v>Some data from proxy country: 792</v>
+          </cell>
+          <cell r="H164" t="str">
+            <v>Some data from proxy country: 792</v>
+          </cell>
+          <cell r="I164" t="str">
+            <v>Some data from proxy country: 792</v>
+          </cell>
+          <cell r="J164" t="str">
+            <v>Some data from proxy country: Turkey</v>
+          </cell>
+        </row>
+        <row r="165">
+          <cell r="A165">
+            <v>834</v>
+          </cell>
+          <cell r="B165" t="str">
+            <v>TZA</v>
+          </cell>
+          <cell r="C165" t="str">
+            <v>United Republic of Tanzania</v>
+          </cell>
+          <cell r="D165" t="str">
+            <v>1991 DHS, 1996 DHS, 1999 DHS, 2004 DHS, 2010 DHS, 2015 DHS, 2022 DHS</v>
+          </cell>
+          <cell r="E165" t="str">
+            <v>1991 DHS, 1996 DHS, 1999 DHS, 2004 DHS, 2010 DHS, 2015 DHS, 2022 DHS</v>
+          </cell>
+          <cell r="F165" t="str">
+            <v>1991 DHS, 1996 DHS, 1999 DHS, 2004 DHS, 2010 DHS, 2015 DHS, 2022 DHS</v>
+          </cell>
+          <cell r="J165" t="str">
+            <v>1991 DHS, 1996 DHS, 1999 DHS, 2004 DHS, 2010 DHS, 2015 DHS, 2022 DHS</v>
+          </cell>
+        </row>
+        <row r="166">
+          <cell r="A166">
+            <v>850</v>
+          </cell>
+          <cell r="B166" t="str">
+            <v>VIR</v>
+          </cell>
+          <cell r="C166" t="str">
+            <v>United States Virgin Islands</v>
+          </cell>
+          <cell r="G166" t="str">
+            <v>Some data from proxy country: 214</v>
+          </cell>
+          <cell r="H166" t="str">
+            <v>Some data from proxy country: 214</v>
+          </cell>
+          <cell r="I166" t="str">
+            <v>Some data from proxy country: 214</v>
+          </cell>
+          <cell r="J166" t="str">
+            <v>Some data from proxy country: Dominican Republic</v>
+          </cell>
+        </row>
+        <row r="167">
+          <cell r="A167">
+            <v>858</v>
+          </cell>
+          <cell r="B167" t="str">
+            <v>URY</v>
+          </cell>
+          <cell r="C167" t="str">
+            <v>Uruguay</v>
+          </cell>
+          <cell r="G167" t="str">
+            <v>Some data from proxy country: 76</v>
+          </cell>
+          <cell r="H167" t="str">
+            <v>Some data from proxy country: 76</v>
+          </cell>
+          <cell r="I167" t="str">
+            <v>Some data from proxy country: 76</v>
+          </cell>
+          <cell r="J167" t="str">
+            <v>Some data from proxy country: Brazil</v>
+          </cell>
+        </row>
+        <row r="168">
+          <cell r="A168">
+            <v>860</v>
+          </cell>
+          <cell r="B168" t="str">
+            <v>UZB</v>
+          </cell>
+          <cell r="C168" t="str">
+            <v>Uzbekistan</v>
+          </cell>
+          <cell r="D168" t="str">
+            <v>1996 DHS, 2000 MICS, 2006 MICS, 2021 MICS</v>
+          </cell>
+          <cell r="E168" t="str">
+            <v>1996 DHS, 2000 MICS, 2006 MICS, 2021 MICS</v>
+          </cell>
+          <cell r="F168" t="str">
+            <v>1996 DHS, 2000 MICS, 2006 MICS, 2021 MICS</v>
+          </cell>
+          <cell r="J168" t="str">
+            <v>1996 DHS, 2000 MICS, 2006 MICS, 2021 MICS</v>
+          </cell>
+        </row>
+        <row r="169">
+          <cell r="A169">
+            <v>548</v>
+          </cell>
+          <cell r="B169" t="str">
+            <v>VUT</v>
+          </cell>
+          <cell r="C169" t="str">
+            <v>Vanuatu</v>
+          </cell>
+          <cell r="D169" t="str">
+            <v>2007 MICS, 2023 MICS</v>
+          </cell>
+          <cell r="E169" t="str">
+            <v>2023 MICS</v>
+          </cell>
+          <cell r="F169" t="str">
+            <v>2007 MICS, 2023 MICS</v>
+          </cell>
+          <cell r="G169" t="str">
+            <v>Some data from proxy country: 360</v>
+          </cell>
+          <cell r="H169" t="str">
+            <v>Some data from proxy country: 360</v>
+          </cell>
+          <cell r="I169" t="str">
+            <v>Some data from proxy country: 360</v>
+          </cell>
+          <cell r="J169" t="str">
+            <v>2007 MICS, 2023 MICS Some data from proxy country: Indonesia</v>
+          </cell>
+        </row>
+        <row r="170">
+          <cell r="A170">
+            <v>862</v>
+          </cell>
+          <cell r="B170" t="str">
+            <v>VEN</v>
+          </cell>
+          <cell r="C170" t="str">
+            <v>Venezuela (Bolivarian Republic of)</v>
+          </cell>
+          <cell r="G170" t="str">
+            <v>Some data from proxy country: 76</v>
+          </cell>
+          <cell r="H170" t="str">
+            <v>Some data from proxy country: 76</v>
+          </cell>
+          <cell r="I170" t="str">
+            <v>Some data from proxy country: 76</v>
+          </cell>
+          <cell r="J170" t="str">
+            <v>Some data from proxy country: Brazil</v>
+          </cell>
+        </row>
+        <row r="171">
+          <cell r="A171">
+            <v>704</v>
+          </cell>
+          <cell r="B171" t="str">
+            <v>VNM</v>
+          </cell>
+          <cell r="C171" t="str">
+            <v>Viet Nam</v>
+          </cell>
+          <cell r="D171" t="str">
+            <v>1997 DHS, 2000 MICS, 2002 DHS, 2006 MICS, 2010 MICS, 2013 MICS, 2020 MICS</v>
+          </cell>
+          <cell r="E171" t="str">
+            <v>1997 DHS, 2000 MICS, 2002 DHS, 2006 MICS, 2010 MICS, 2013 MICS, 2020 MICS</v>
+          </cell>
+          <cell r="F171" t="str">
+            <v>1997 DHS, 2000 MICS, 2002 DHS, 2006 MICS, 2010 MICS, 2013 MICS, 2020 MICS</v>
+          </cell>
+          <cell r="J171" t="str">
+            <v>1997 DHS, 2000 MICS, 2002 DHS, 2006 MICS, 2010 MICS, 2013 MICS, 2020 MICS</v>
+          </cell>
+        </row>
+        <row r="172">
+          <cell r="A172">
+            <v>732</v>
+          </cell>
+          <cell r="B172" t="str">
+            <v>ESH</v>
+          </cell>
+          <cell r="C172" t="str">
+            <v>Western Sahara</v>
+          </cell>
+          <cell r="G172" t="str">
+            <v>Some data from proxy country: 504</v>
+          </cell>
+          <cell r="H172" t="str">
+            <v>Some data from proxy country: 504</v>
+          </cell>
+          <cell r="I172" t="str">
+            <v>Some data from proxy country: 504</v>
+          </cell>
+          <cell r="J172" t="str">
+            <v>Some data from proxy country: Morocco</v>
+          </cell>
+        </row>
+        <row r="173">
+          <cell r="A173">
+            <v>887</v>
+          </cell>
+          <cell r="B173" t="str">
+            <v>YEM</v>
+          </cell>
+          <cell r="C173" t="str">
+            <v>Yemen</v>
+          </cell>
+          <cell r="D173" t="str">
+            <v>1991 DHS, 2006 MICS, 2013 DHS</v>
+          </cell>
+          <cell r="E173" t="str">
+            <v>1991 DHS, 2006 MICS, 2013 DHS</v>
+          </cell>
+          <cell r="F173" t="str">
+            <v>1991 DHS, 2013 DHS</v>
+          </cell>
+          <cell r="J173" t="str">
+            <v>1991 DHS, 2013 DHS</v>
+          </cell>
+        </row>
+        <row r="174">
+          <cell r="A174">
+            <v>894</v>
+          </cell>
+          <cell r="B174" t="str">
+            <v>ZMB</v>
+          </cell>
+          <cell r="C174" t="str">
+            <v>Zambia</v>
+          </cell>
+          <cell r="D174" t="str">
+            <v>1992 DHS, 1996 DHS, 1999 MICS, 2001 DHS, 2007 DHS, 2013 DHS, 2018 DHS, 2024 DHS</v>
+          </cell>
+          <cell r="E174" t="str">
+            <v>1992 DHS, 1996 DHS, 2001 DHS, 2007 DHS, 2013 DHS, 2018 DHS, 2024 DHS</v>
+          </cell>
+          <cell r="F174" t="str">
+            <v>1992 DHS, 1996 DHS, 1999 MICS, 2001 DHS, 2007 DHS, 2013 DHS, 2018 DHS, 2024 DHS</v>
+          </cell>
+          <cell r="J174" t="str">
+            <v>1992 DHS, 1996 DHS, 1999 MICS, 2001 DHS, 2007 DHS, 2013 DHS, 2018 DHS, 2024 DHS</v>
+          </cell>
+        </row>
+        <row r="175">
+          <cell r="A175">
+            <v>716</v>
+          </cell>
+          <cell r="B175" t="str">
+            <v>ZWE</v>
+          </cell>
+          <cell r="C175" t="str">
+            <v>Zimbabwe</v>
+          </cell>
+          <cell r="D175" t="str">
+            <v>1994 DHS, 1999 DHS, 2005 DHS, 2009 MICS, 2010 DHS, 2014 MICS, 2015 DHS</v>
+          </cell>
+          <cell r="E175" t="str">
+            <v>1994 DHS, 1999 DHS, 2005 DHS, 2010 DHS, 2014 MICS, 2015 DHS</v>
+          </cell>
+          <cell r="F175" t="str">
+            <v>1994 DHS, 1999 DHS, 2005 DHS, 2009 MICS, 2010 DHS, 2014 MICS, 2015 DHS</v>
+          </cell>
+          <cell r="J175" t="str">
+            <v>1994 DHS, 1999 DHS, 2005 DHS, 2009 MICS, 2010 DHS, 2014 MICS, 2015 DHS</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -13933,7 +18345,7 @@
         <v>1104</v>
       </c>
       <c r="W113" t="s">
-        <v>1376</v>
+        <v>1495</v>
       </c>
       <c r="X113" t="s">
         <v>1426</v>
@@ -36884,6 +41296,5011 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D4FE8C6-E11B-420F-807C-E2A4CD41A6AC}">
+  <dimension ref="A1:C416"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" t="str">
+        <f>VLOOKUP(A2,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2010 MICS, 2015 DHS</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" t="str">
+        <f>VLOOKUP(A3,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2005 MICS, 2008 DHS, 2017 DHS</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" t="str">
+        <f>VLOOKUP(A4,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2012 MICS, 2018 MICS Some data from proxy country: Egypt</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>24</v>
+      </c>
+      <c r="B5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" t="str">
+        <f>VLOOKUP(A5,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2001 MICS, 2015 DHS, 2023 DHS</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>28</v>
+      </c>
+      <c r="B6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" t="str">
+        <f>VLOOKUP(A6,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>Some data from proxy country: Dominican Republic</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>32</v>
+      </c>
+      <c r="B7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C7" t="str">
+        <f>VLOOKUP(A7,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2011 MICS, 2019 MICS Some data from proxy country: Brazil</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>51</v>
+      </c>
+      <c r="B8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C8" t="str">
+        <f>VLOOKUP(A8,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2000 DHS, 2005 DHS, 2010 DHS, 2015 DHS</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>533</v>
+      </c>
+      <c r="B9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C9" t="str">
+        <f>VLOOKUP(A9,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>Some data from proxy country: Dominican Republic</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>62</v>
+      </c>
+      <c r="C10" t="e">
+        <f>VLOOKUP(A10,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>40</v>
+      </c>
+      <c r="B11" t="s">
+        <v>68</v>
+      </c>
+      <c r="C11" t="e">
+        <f>VLOOKUP(A11,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>31</v>
+      </c>
+      <c r="B12" t="s">
+        <v>72</v>
+      </c>
+      <c r="C12" t="str">
+        <f>VLOOKUP(A12,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2000 MICS, 2006 DHS, 2023 MICS</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>44</v>
+      </c>
+      <c r="B13" t="s">
+        <v>75</v>
+      </c>
+      <c r="C13" t="str">
+        <f>VLOOKUP(A13,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>Some data from proxy country: Dominican Republic</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>48</v>
+      </c>
+      <c r="B14" t="s">
+        <v>79</v>
+      </c>
+      <c r="C14" t="str">
+        <f>VLOOKUP(A14,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>Some data from proxy country: Thailand</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>50</v>
+      </c>
+      <c r="B15" t="s">
+        <v>82</v>
+      </c>
+      <c r="C15" t="str">
+        <f>VLOOKUP(A15,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1993 DHS, 1996 DHS, 1999 DHS, 2004 DHS, 2007 DHS, 2011 DHS, 2012 MICS, 2014 DHS, 2017 DHS, 2019 MICS, 2022 DHS</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>52</v>
+      </c>
+      <c r="B16" t="s">
+        <v>85</v>
+      </c>
+      <c r="C16" t="str">
+        <f>VLOOKUP(A16,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2012 MICS Some data from proxy country: Dominican Republic</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>112</v>
+      </c>
+      <c r="B17" t="s">
+        <v>88</v>
+      </c>
+      <c r="C17" t="str">
+        <f>VLOOKUP(A17,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2005 MICS, 2012 MICS, 2019 MICS Some data from proxy country: Ukraine</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>56</v>
+      </c>
+      <c r="B18" t="s">
+        <v>92</v>
+      </c>
+      <c r="C18" t="e">
+        <f>VLOOKUP(A18,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>84</v>
+      </c>
+      <c r="B19" t="s">
+        <v>94</v>
+      </c>
+      <c r="C19" t="str">
+        <f>VLOOKUP(A19,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2006 MICS, 2011 MICS, 2015 MICS Some data from proxy country: Guatemala</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>204</v>
+      </c>
+      <c r="B20" t="s">
+        <v>97</v>
+      </c>
+      <c r="C20" t="str">
+        <f>VLOOKUP(A20,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1996 DHS, 2001 DHS, 2006 DHS, 2011 DHS, 2014 MICS, 2017 DHS, 2021 MICS</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="3">
+        <v>204</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C21" t="str">
+        <f>VLOOKUP(A21,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1996 DHS, 2001 DHS, 2006 DHS, 2011 DHS, 2014 MICS, 2017 DHS, 2021 MICS</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="3">
+        <v>204</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C22" t="str">
+        <f>VLOOKUP(A22,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1996 DHS, 2001 DHS, 2006 DHS, 2011 DHS, 2014 MICS, 2017 DHS, 2021 MICS</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="3">
+        <v>204</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C23" t="str">
+        <f>VLOOKUP(A23,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1996 DHS, 2001 DHS, 2006 DHS, 2011 DHS, 2014 MICS, 2017 DHS, 2021 MICS</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="3">
+        <v>204</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C24" t="str">
+        <f>VLOOKUP(A24,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1996 DHS, 2001 DHS, 2006 DHS, 2011 DHS, 2014 MICS, 2017 DHS, 2021 MICS</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="3">
+        <v>204</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C25" t="str">
+        <f>VLOOKUP(A25,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1996 DHS, 2001 DHS, 2006 DHS, 2011 DHS, 2014 MICS, 2017 DHS, 2021 MICS</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="3">
+        <v>204</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C26" t="str">
+        <f>VLOOKUP(A26,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1996 DHS, 2001 DHS, 2006 DHS, 2011 DHS, 2014 MICS, 2017 DHS, 2021 MICS</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="3">
+        <v>204</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C27" t="str">
+        <f>VLOOKUP(A27,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1996 DHS, 2001 DHS, 2006 DHS, 2011 DHS, 2014 MICS, 2017 DHS, 2021 MICS</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="3">
+        <v>204</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C28" t="str">
+        <f>VLOOKUP(A28,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1996 DHS, 2001 DHS, 2006 DHS, 2011 DHS, 2014 MICS, 2017 DHS, 2021 MICS</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="3">
+        <v>204</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C29" t="str">
+        <f>VLOOKUP(A29,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1996 DHS, 2001 DHS, 2006 DHS, 2011 DHS, 2014 MICS, 2017 DHS, 2021 MICS</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="3">
+        <v>204</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C30" t="str">
+        <f>VLOOKUP(A30,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1996 DHS, 2001 DHS, 2006 DHS, 2011 DHS, 2014 MICS, 2017 DHS, 2021 MICS</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="3">
+        <v>204</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C31" t="str">
+        <f>VLOOKUP(A31,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1996 DHS, 2001 DHS, 2006 DHS, 2011 DHS, 2014 MICS, 2017 DHS, 2021 MICS</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="3">
+        <v>204</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C32" t="str">
+        <f>VLOOKUP(A32,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1996 DHS, 2001 DHS, 2006 DHS, 2011 DHS, 2014 MICS, 2017 DHS, 2021 MICS</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>64</v>
+      </c>
+      <c r="B33" t="s">
+        <v>102</v>
+      </c>
+      <c r="C33" t="str">
+        <f>VLOOKUP(A33,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2010 MICS Some data from proxy country: Nepal</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>68</v>
+      </c>
+      <c r="B34" t="s">
+        <v>104</v>
+      </c>
+      <c r="C34" t="str">
+        <f>VLOOKUP(A34,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1994 DHS, 1998 DHS, 2003 DHS, 2008 DHS</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>70</v>
+      </c>
+      <c r="B35" t="s">
+        <v>108</v>
+      </c>
+      <c r="C35" t="str">
+        <f>VLOOKUP(A35,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2006 MICS, 2011 MICS Some data from proxy country: Moldova</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>72</v>
+      </c>
+      <c r="B36" t="s">
+        <v>111</v>
+      </c>
+      <c r="C36" t="str">
+        <f>VLOOKUP(A36,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>Some data from proxy country: Namibia</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>76</v>
+      </c>
+      <c r="B37" t="s">
+        <v>116</v>
+      </c>
+      <c r="C37" t="str">
+        <f>VLOOKUP(A37,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1991 DHS, 1996 DHS</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>96</v>
+      </c>
+      <c r="B38" t="s">
+        <v>120</v>
+      </c>
+      <c r="C38" t="str">
+        <f>VLOOKUP(A38,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>Some data from proxy country: Indonesia</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>100</v>
+      </c>
+      <c r="B39" t="s">
+        <v>124</v>
+      </c>
+      <c r="C39" t="str">
+        <f>VLOOKUP(A39,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>Some data from proxy country: Ukraine</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>854</v>
+      </c>
+      <c r="B40" t="s">
+        <v>127</v>
+      </c>
+      <c r="C40" t="str">
+        <f>VLOOKUP(A40,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1993 DHS, 1998 DHS, 2003 DHS, 2006 MICS, 2010 DHS, 2021 DHS</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>108</v>
+      </c>
+      <c r="B41" t="s">
+        <v>129</v>
+      </c>
+      <c r="C41" t="str">
+        <f>VLOOKUP(A41,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2005 MICS, 2010 DHS, 2016 DHS</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>116</v>
+      </c>
+      <c r="B42" t="s">
+        <v>133</v>
+      </c>
+      <c r="C42" t="str">
+        <f>VLOOKUP(A42,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2000 DHS, 2005 DHS, 2010 DHS, 2014 DHS, 2021 DHS</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>120</v>
+      </c>
+      <c r="B43" t="s">
+        <v>137</v>
+      </c>
+      <c r="C43" t="str">
+        <f>VLOOKUP(A43,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1991 DHS, 1998 DHS, 2004 DHS, 2006 MICS, 2011 DHS, 2014 MICS, 2018 DHS</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>124</v>
+      </c>
+      <c r="B44" t="s">
+        <v>140</v>
+      </c>
+      <c r="C44" t="e">
+        <f>VLOOKUP(A44,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>132</v>
+      </c>
+      <c r="B45" t="s">
+        <v>144</v>
+      </c>
+      <c r="C45" t="str">
+        <f>VLOOKUP(A45,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>Some data from proxy country: Morocco</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>140</v>
+      </c>
+      <c r="B46" t="s">
+        <v>147</v>
+      </c>
+      <c r="C46" t="str">
+        <f>VLOOKUP(A46,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1994 DHS, 2010 MICS, 2018 MICS</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>148</v>
+      </c>
+      <c r="B47" t="s">
+        <v>151</v>
+      </c>
+      <c r="C47" t="str">
+        <f>VLOOKUP(A47,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1996 DHS, 2004 DHS, 2010 MICS, 2014 DHS, 2019 MICS</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>830</v>
+      </c>
+      <c r="B48" t="s">
+        <v>153</v>
+      </c>
+      <c r="C48" t="e">
+        <f>VLOOKUP(A48,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>152</v>
+      </c>
+      <c r="B49" t="s">
+        <v>155</v>
+      </c>
+      <c r="C49" t="str">
+        <f>VLOOKUP(A49,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>Some data from proxy country: Brazil</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>156</v>
+      </c>
+      <c r="B50" t="s">
+        <v>159</v>
+      </c>
+      <c r="C50" t="str">
+        <f>VLOOKUP(A50,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>Some data from proxy country: Viet Nam</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>344</v>
+      </c>
+      <c r="B51" t="s">
+        <v>163</v>
+      </c>
+      <c r="C51" t="e">
+        <f>VLOOKUP(A51,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>446</v>
+      </c>
+      <c r="B52" t="s">
+        <v>166</v>
+      </c>
+      <c r="C52" t="e">
+        <f>VLOOKUP(A52,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>158</v>
+      </c>
+      <c r="B53" t="s">
+        <v>169</v>
+      </c>
+      <c r="C53" t="e">
+        <f>VLOOKUP(A53,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>170</v>
+      </c>
+      <c r="B54" t="s">
+        <v>172</v>
+      </c>
+      <c r="C54" t="str">
+        <f>VLOOKUP(A54,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1990 DHS, 1995 DHS, 2000 DHS, 2005 DHS, 2010 DHS, 2015 DHS</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>174</v>
+      </c>
+      <c r="B55" t="s">
+        <v>176</v>
+      </c>
+      <c r="C55" t="str">
+        <f>VLOOKUP(A55,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1996 DHS, 2000 MICS, 2012 DHS, 2022 MICS</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>178</v>
+      </c>
+      <c r="B56" t="s">
+        <v>179</v>
+      </c>
+      <c r="C56" t="str">
+        <f>VLOOKUP(A56,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2005 DHS, 2011 DHS, 2014 MICS</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>184</v>
+      </c>
+      <c r="B57" t="s">
+        <v>1352</v>
+      </c>
+      <c r="C57" t="e">
+        <f>VLOOKUP(A57,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>188</v>
+      </c>
+      <c r="B58" t="s">
+        <v>182</v>
+      </c>
+      <c r="C58" t="str">
+        <f>VLOOKUP(A58,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2011 MICS, 2018 MICS Some data from proxy country: Guatemala</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>384</v>
+      </c>
+      <c r="B59" t="s">
+        <v>185</v>
+      </c>
+      <c r="C59" t="str">
+        <f>VLOOKUP(A59,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1994 DHS, 1998 DHS, 2006 MICS, 2011 DHS, 2016 MICS, 2021 DHS</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="3">
+        <v>384</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C60" t="str">
+        <f>VLOOKUP(A60,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1994 DHS, 1998 DHS, 2006 MICS, 2011 DHS, 2016 MICS, 2021 DHS</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="3">
+        <v>384</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C61" t="str">
+        <f>VLOOKUP(A61,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1994 DHS, 1998 DHS, 2006 MICS, 2011 DHS, 2016 MICS, 2021 DHS</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="3">
+        <v>384</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C62" t="str">
+        <f>VLOOKUP(A62,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1994 DHS, 1998 DHS, 2006 MICS, 2011 DHS, 2016 MICS, 2021 DHS</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="3">
+        <v>384</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C63" t="str">
+        <f>VLOOKUP(A63,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1994 DHS, 1998 DHS, 2006 MICS, 2011 DHS, 2016 MICS, 2021 DHS</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="3">
+        <v>384</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C64" t="str">
+        <f>VLOOKUP(A64,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1994 DHS, 1998 DHS, 2006 MICS, 2011 DHS, 2016 MICS, 2021 DHS</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="3">
+        <v>384</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C65" t="str">
+        <f>VLOOKUP(A65,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1994 DHS, 1998 DHS, 2006 MICS, 2011 DHS, 2016 MICS, 2021 DHS</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="3">
+        <v>384</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C66" t="str">
+        <f>VLOOKUP(A66,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1994 DHS, 1998 DHS, 2006 MICS, 2011 DHS, 2016 MICS, 2021 DHS</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="3">
+        <v>384</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C67" t="str">
+        <f>VLOOKUP(A67,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1994 DHS, 1998 DHS, 2006 MICS, 2011 DHS, 2016 MICS, 2021 DHS</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="3">
+        <v>384</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C68" t="str">
+        <f>VLOOKUP(A68,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1994 DHS, 1998 DHS, 2006 MICS, 2011 DHS, 2016 MICS, 2021 DHS</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="3">
+        <v>384</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C69" t="str">
+        <f>VLOOKUP(A69,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1994 DHS, 1998 DHS, 2006 MICS, 2011 DHS, 2016 MICS, 2021 DHS</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="3">
+        <v>384</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C70" t="str">
+        <f>VLOOKUP(A70,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1994 DHS, 1998 DHS, 2006 MICS, 2011 DHS, 2016 MICS, 2021 DHS</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>191</v>
+      </c>
+      <c r="B71" t="s">
+        <v>187</v>
+      </c>
+      <c r="C71" t="str">
+        <f>VLOOKUP(A71,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>Some data from proxy country: Moldova</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>192</v>
+      </c>
+      <c r="B72" t="s">
+        <v>190</v>
+      </c>
+      <c r="C72" t="str">
+        <f>VLOOKUP(A72,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2011 MICS, 2014 MICS, 2019 MICS Some data from proxy country: Dominican Republic</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>531</v>
+      </c>
+      <c r="B73" t="s">
+        <v>193</v>
+      </c>
+      <c r="C73" t="str">
+        <f>VLOOKUP(A73,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>Some data from proxy country: Dominican Republic</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>196</v>
+      </c>
+      <c r="B74" t="s">
+        <v>196</v>
+      </c>
+      <c r="C74" t="str">
+        <f>VLOOKUP(A74,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>Some data from proxy country: Jordan</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>203</v>
+      </c>
+      <c r="B75" t="s">
+        <v>198</v>
+      </c>
+      <c r="C75" t="str">
+        <f>VLOOKUP(A75,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>Some data from proxy country: Ukraine</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>408</v>
+      </c>
+      <c r="B76" t="s">
+        <v>201</v>
+      </c>
+      <c r="C76" t="str">
+        <f>VLOOKUP(A76,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>Some data from proxy country: Myanmar</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>180</v>
+      </c>
+      <c r="B77" t="s">
+        <v>204</v>
+      </c>
+      <c r="C77" t="str">
+        <f>VLOOKUP(A77,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2001 MICS, 2007 DHS, 2010 MICS, 2013 DHS, 2017 MICS, 2023 DHS</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>208</v>
+      </c>
+      <c r="B78" t="s">
+        <v>207</v>
+      </c>
+      <c r="C78" t="e">
+        <f>VLOOKUP(A78,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>262</v>
+      </c>
+      <c r="B79" t="s">
+        <v>210</v>
+      </c>
+      <c r="C79" t="str">
+        <f>VLOOKUP(A79,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2006 MICS Some data from proxy country: Ethiopia</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>212</v>
+      </c>
+      <c r="B80" t="s">
+        <v>213</v>
+      </c>
+      <c r="C80" t="e">
+        <f>VLOOKUP(A80,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>214</v>
+      </c>
+      <c r="B81" t="s">
+        <v>215</v>
+      </c>
+      <c r="C81" t="str">
+        <f>VLOOKUP(A81,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1991 DHS, 1996 DHS, 1999 DHS, 2002 DHS, 2007 DHS, 2013 DHS, 2014 MICS, 2019 MICS</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>218</v>
+      </c>
+      <c r="B82" t="s">
+        <v>220</v>
+      </c>
+      <c r="C82" t="str">
+        <f>VLOOKUP(A82,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>Some data from proxy country: Colombia</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>818</v>
+      </c>
+      <c r="B83" t="s">
+        <v>223</v>
+      </c>
+      <c r="C83" t="str">
+        <f>VLOOKUP(A83,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1992 DHS, 1995 DHS, 2000 DHS, 2003 DHS, 2005 DHS, 2008 DHS, 2014 DHS</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>222</v>
+      </c>
+      <c r="B84" t="s">
+        <v>226</v>
+      </c>
+      <c r="C84" t="str">
+        <f>VLOOKUP(A84,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2014 MICS Some data from proxy country: Guatemala</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>226</v>
+      </c>
+      <c r="B85" t="s">
+        <v>229</v>
+      </c>
+      <c r="C85" t="str">
+        <f>VLOOKUP(A85,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>Some data from proxy country: Guinea</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>232</v>
+      </c>
+      <c r="B86" t="s">
+        <v>231</v>
+      </c>
+      <c r="C86" t="str">
+        <f>VLOOKUP(A86,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>Some data from proxy country: Uganda</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>233</v>
+      </c>
+      <c r="B87" t="s">
+        <v>234</v>
+      </c>
+      <c r="C87" t="str">
+        <f>VLOOKUP(A87,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>Some data from proxy country: Ukraine</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>231</v>
+      </c>
+      <c r="B88" t="s">
+        <v>237</v>
+      </c>
+      <c r="C88" t="str">
+        <f>VLOOKUP(A88,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2000 DHS, 2005 DHS, 2011 DHS, 2016 DHS</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" s="3">
+        <v>231</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C89" t="str">
+        <f>VLOOKUP(A89,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2000 DHS, 2005 DHS, 2011 DHS, 2016 DHS</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" s="3">
+        <v>231</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C90" t="str">
+        <f>VLOOKUP(A90,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2000 DHS, 2005 DHS, 2011 DHS, 2016 DHS</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" s="3">
+        <v>231</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C91" t="str">
+        <f>VLOOKUP(A91,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2000 DHS, 2005 DHS, 2011 DHS, 2016 DHS</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" s="3">
+        <v>231</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C92" t="str">
+        <f>VLOOKUP(A92,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2000 DHS, 2005 DHS, 2011 DHS, 2016 DHS</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" s="3">
+        <v>231</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C93" t="str">
+        <f>VLOOKUP(A93,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2000 DHS, 2005 DHS, 2011 DHS, 2016 DHS</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" s="3">
+        <v>231</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C94" t="str">
+        <f>VLOOKUP(A94,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2000 DHS, 2005 DHS, 2011 DHS, 2016 DHS</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" s="3">
+        <v>231</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C95" t="str">
+        <f>VLOOKUP(A95,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2000 DHS, 2005 DHS, 2011 DHS, 2016 DHS</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" s="3">
+        <v>231</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C96" t="str">
+        <f>VLOOKUP(A96,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2000 DHS, 2005 DHS, 2011 DHS, 2016 DHS</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" s="3">
+        <v>231</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C97" t="str">
+        <f>VLOOKUP(A97,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2000 DHS, 2005 DHS, 2011 DHS, 2016 DHS</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" s="3">
+        <v>231</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C98" t="str">
+        <f>VLOOKUP(A98,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2000 DHS, 2005 DHS, 2011 DHS, 2016 DHS</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" s="3">
+        <v>231</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C99" t="str">
+        <f>VLOOKUP(A99,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2000 DHS, 2005 DHS, 2011 DHS, 2016 DHS</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" s="3">
+        <v>231</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C100" t="str">
+        <f>VLOOKUP(A100,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2000 DHS, 2005 DHS, 2011 DHS, 2016 DHS</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" s="3">
+        <v>231</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C101" t="str">
+        <f>VLOOKUP(A101,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2000 DHS, 2005 DHS, 2011 DHS, 2016 DHS</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" s="3">
+        <v>231</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C102" t="str">
+        <f>VLOOKUP(A102,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2000 DHS, 2005 DHS, 2011 DHS, 2016 DHS</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" s="3">
+        <v>231</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C103" t="str">
+        <f>VLOOKUP(A103,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2000 DHS, 2005 DHS, 2011 DHS, 2016 DHS</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>242</v>
+      </c>
+      <c r="B104" t="s">
+        <v>241</v>
+      </c>
+      <c r="C104" t="str">
+        <f>VLOOKUP(A104,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2021 MICS Some data from proxy country: Indonesia</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>246</v>
+      </c>
+      <c r="B105" t="s">
+        <v>245</v>
+      </c>
+      <c r="C105" t="e">
+        <f>VLOOKUP(A105,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>250</v>
+      </c>
+      <c r="B106" t="s">
+        <v>247</v>
+      </c>
+      <c r="C106" t="e">
+        <f>VLOOKUP(A106,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>254</v>
+      </c>
+      <c r="B107" t="s">
+        <v>249</v>
+      </c>
+      <c r="C107" t="str">
+        <f>VLOOKUP(A107,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>Some data from proxy country: Brazil</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108">
+        <v>258</v>
+      </c>
+      <c r="B108" t="s">
+        <v>251</v>
+      </c>
+      <c r="C108" t="str">
+        <f>VLOOKUP(A108,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>Some data from proxy country: Indonesia</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109">
+        <v>266</v>
+      </c>
+      <c r="B109" t="s">
+        <v>254</v>
+      </c>
+      <c r="C109" t="str">
+        <f>VLOOKUP(A109,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2000 DHS, 2012 DHS, 2019 DHS</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <v>270</v>
+      </c>
+      <c r="B110" t="s">
+        <v>256</v>
+      </c>
+      <c r="C110" t="str">
+        <f>VLOOKUP(A110,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2010 MICS, 2013 DHS, 2018 MICS, 2019 DHS</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111">
+        <v>268</v>
+      </c>
+      <c r="B111" t="s">
+        <v>259</v>
+      </c>
+      <c r="C111" t="str">
+        <f>VLOOKUP(A111,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2018 MICS Some data from proxy country: Armenia</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112">
+        <v>276</v>
+      </c>
+      <c r="B112" t="s">
+        <v>262</v>
+      </c>
+      <c r="C112" t="e">
+        <f>VLOOKUP(A112,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113">
+        <v>288</v>
+      </c>
+      <c r="B113" t="s">
+        <v>264</v>
+      </c>
+      <c r="C113" t="str">
+        <f>VLOOKUP(A113,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1993 DHS, 1998 DHS, 2003 DHS, 2006 MICS, 2008 DHS, 2011 MICS, 2014 DHS, 2017 MICS, 2022 DHS</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114">
+        <v>300</v>
+      </c>
+      <c r="B114" t="s">
+        <v>268</v>
+      </c>
+      <c r="C114" t="e">
+        <f>VLOOKUP(A114,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115">
+        <v>308</v>
+      </c>
+      <c r="B115" t="s">
+        <v>270</v>
+      </c>
+      <c r="C115" t="str">
+        <f>VLOOKUP(A115,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>Some data from proxy country: Dominican Republic</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116">
+        <v>312</v>
+      </c>
+      <c r="B116" t="s">
+        <v>272</v>
+      </c>
+      <c r="C116" t="str">
+        <f>VLOOKUP(A116,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>Some data from proxy country: Dominican Republic</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117">
+        <v>316</v>
+      </c>
+      <c r="B117" t="s">
+        <v>274</v>
+      </c>
+      <c r="C117" t="str">
+        <f>VLOOKUP(A117,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>Some data from proxy country: Indonesia</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118">
+        <v>320</v>
+      </c>
+      <c r="B118" t="s">
+        <v>277</v>
+      </c>
+      <c r="C118" t="str">
+        <f>VLOOKUP(A118,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1995 DHS, 2014 DHS</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119">
+        <v>324</v>
+      </c>
+      <c r="B119" t="s">
+        <v>280</v>
+      </c>
+      <c r="C119" t="str">
+        <f>VLOOKUP(A119,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1999 DHS, 2005 DHS, 2012 DHS, 2016 MICS, 2018 DHS</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120">
+        <v>624</v>
+      </c>
+      <c r="B120" t="s">
+        <v>283</v>
+      </c>
+      <c r="C120" t="str">
+        <f>VLOOKUP(A120,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2000 MICS, 2006 MICS, 2014 MICS, 2018 MICS Some data from proxy country: Guinea</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121">
+        <v>328</v>
+      </c>
+      <c r="B121" t="s">
+        <v>285</v>
+      </c>
+      <c r="C121" t="str">
+        <f>VLOOKUP(A121,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2006 MICS, 2009 DHS, 2014 MICS, 2019 MICS</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122">
+        <v>332</v>
+      </c>
+      <c r="B122" t="s">
+        <v>288</v>
+      </c>
+      <c r="C122" t="str">
+        <f>VLOOKUP(A122,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1994 DHS, 2000 DHS, 2005 DHS, 2012 DHS, 2016 DHS</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" s="3">
+        <v>332</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="C123" t="str">
+        <f>VLOOKUP(A123,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1994 DHS, 2000 DHS, 2005 DHS, 2012 DHS, 2016 DHS</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" s="3">
+        <v>332</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="C124" t="str">
+        <f>VLOOKUP(A124,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1994 DHS, 2000 DHS, 2005 DHS, 2012 DHS, 2016 DHS</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" s="3">
+        <v>332</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="C125" t="str">
+        <f>VLOOKUP(A125,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1994 DHS, 2000 DHS, 2005 DHS, 2012 DHS, 2016 DHS</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" s="3">
+        <v>332</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="C126" t="str">
+        <f>VLOOKUP(A126,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1994 DHS, 2000 DHS, 2005 DHS, 2012 DHS, 2016 DHS</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" s="3">
+        <v>332</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="C127" t="str">
+        <f>VLOOKUP(A127,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1994 DHS, 2000 DHS, 2005 DHS, 2012 DHS, 2016 DHS</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" s="3">
+        <v>332</v>
+      </c>
+      <c r="B128" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="C128" t="str">
+        <f>VLOOKUP(A128,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1994 DHS, 2000 DHS, 2005 DHS, 2012 DHS, 2016 DHS</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" s="3">
+        <v>332</v>
+      </c>
+      <c r="B129" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="C129" t="str">
+        <f>VLOOKUP(A129,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1994 DHS, 2000 DHS, 2005 DHS, 2012 DHS, 2016 DHS</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" s="3">
+        <v>332</v>
+      </c>
+      <c r="B130" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="C130" t="str">
+        <f>VLOOKUP(A130,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1994 DHS, 2000 DHS, 2005 DHS, 2012 DHS, 2016 DHS</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" s="3">
+        <v>332</v>
+      </c>
+      <c r="B131" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="C131" t="str">
+        <f>VLOOKUP(A131,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1994 DHS, 2000 DHS, 2005 DHS, 2012 DHS, 2016 DHS</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132" s="3">
+        <v>332</v>
+      </c>
+      <c r="B132" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="C132" t="str">
+        <f>VLOOKUP(A132,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1994 DHS, 2000 DHS, 2005 DHS, 2012 DHS, 2016 DHS</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133">
+        <v>340</v>
+      </c>
+      <c r="B133" t="s">
+        <v>292</v>
+      </c>
+      <c r="C133" t="str">
+        <f>VLOOKUP(A133,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2005 DHS, 2011 DHS, 2019 MICS</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134">
+        <v>348</v>
+      </c>
+      <c r="B134" t="s">
+        <v>295</v>
+      </c>
+      <c r="C134" t="str">
+        <f>VLOOKUP(A134,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>Some data from proxy country: Ukraine</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135">
+        <v>352</v>
+      </c>
+      <c r="B135" t="s">
+        <v>298</v>
+      </c>
+      <c r="C135" t="e">
+        <f>VLOOKUP(A135,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136">
+        <v>356</v>
+      </c>
+      <c r="B136" t="s">
+        <v>301</v>
+      </c>
+      <c r="C136" t="str">
+        <f>VLOOKUP(A136,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1992 DHS, 1998 DHS, 2005 DHS, 2015 DHS, 2019 DHS</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137">
+        <v>356</v>
+      </c>
+      <c r="B137" t="s">
+        <v>301</v>
+      </c>
+      <c r="C137" t="str">
+        <f>VLOOKUP(A137,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1992 DHS, 1998 DHS, 2005 DHS, 2015 DHS, 2019 DHS</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138">
+        <v>356</v>
+      </c>
+      <c r="B138" t="s">
+        <v>301</v>
+      </c>
+      <c r="C138" t="str">
+        <f>VLOOKUP(A138,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1992 DHS, 1998 DHS, 2005 DHS, 2015 DHS, 2019 DHS</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139">
+        <v>356</v>
+      </c>
+      <c r="B139" t="s">
+        <v>301</v>
+      </c>
+      <c r="C139" t="str">
+        <f>VLOOKUP(A139,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1992 DHS, 1998 DHS, 2005 DHS, 2015 DHS, 2019 DHS</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140">
+        <v>356</v>
+      </c>
+      <c r="B140" t="s">
+        <v>301</v>
+      </c>
+      <c r="C140" t="str">
+        <f>VLOOKUP(A140,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1992 DHS, 1998 DHS, 2005 DHS, 2015 DHS, 2019 DHS</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141">
+        <v>356</v>
+      </c>
+      <c r="B141" t="s">
+        <v>301</v>
+      </c>
+      <c r="C141" t="str">
+        <f>VLOOKUP(A141,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1992 DHS, 1998 DHS, 2005 DHS, 2015 DHS, 2019 DHS</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142">
+        <v>356</v>
+      </c>
+      <c r="B142" t="s">
+        <v>301</v>
+      </c>
+      <c r="C142" t="str">
+        <f>VLOOKUP(A142,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1992 DHS, 1998 DHS, 2005 DHS, 2015 DHS, 2019 DHS</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143">
+        <v>356</v>
+      </c>
+      <c r="B143" t="s">
+        <v>301</v>
+      </c>
+      <c r="C143" t="str">
+        <f>VLOOKUP(A143,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1992 DHS, 1998 DHS, 2005 DHS, 2015 DHS, 2019 DHS</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144">
+        <v>356</v>
+      </c>
+      <c r="B144" t="s">
+        <v>301</v>
+      </c>
+      <c r="C144" t="str">
+        <f>VLOOKUP(A144,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1992 DHS, 1998 DHS, 2005 DHS, 2015 DHS, 2019 DHS</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145">
+        <v>356</v>
+      </c>
+      <c r="B145" t="s">
+        <v>301</v>
+      </c>
+      <c r="C145" t="str">
+        <f>VLOOKUP(A145,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1992 DHS, 1998 DHS, 2005 DHS, 2015 DHS, 2019 DHS</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146">
+        <v>356</v>
+      </c>
+      <c r="B146" t="s">
+        <v>301</v>
+      </c>
+      <c r="C146" t="str">
+        <f>VLOOKUP(A146,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1992 DHS, 1998 DHS, 2005 DHS, 2015 DHS, 2019 DHS</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A147">
+        <v>356</v>
+      </c>
+      <c r="B147" t="s">
+        <v>301</v>
+      </c>
+      <c r="C147" t="str">
+        <f>VLOOKUP(A147,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1992 DHS, 1998 DHS, 2005 DHS, 2015 DHS, 2019 DHS</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148">
+        <v>356</v>
+      </c>
+      <c r="B148" t="s">
+        <v>301</v>
+      </c>
+      <c r="C148" t="str">
+        <f>VLOOKUP(A148,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1992 DHS, 1998 DHS, 2005 DHS, 2015 DHS, 2019 DHS</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149">
+        <v>356</v>
+      </c>
+      <c r="B149" t="s">
+        <v>301</v>
+      </c>
+      <c r="C149" t="str">
+        <f>VLOOKUP(A149,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1992 DHS, 1998 DHS, 2005 DHS, 2015 DHS, 2019 DHS</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A150">
+        <v>356</v>
+      </c>
+      <c r="B150" t="s">
+        <v>301</v>
+      </c>
+      <c r="C150" t="str">
+        <f>VLOOKUP(A150,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1992 DHS, 1998 DHS, 2005 DHS, 2015 DHS, 2019 DHS</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151">
+        <v>356</v>
+      </c>
+      <c r="B151" t="s">
+        <v>301</v>
+      </c>
+      <c r="C151" t="str">
+        <f>VLOOKUP(A151,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1992 DHS, 1998 DHS, 2005 DHS, 2015 DHS, 2019 DHS</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152">
+        <v>356</v>
+      </c>
+      <c r="B152" t="s">
+        <v>301</v>
+      </c>
+      <c r="C152" t="str">
+        <f>VLOOKUP(A152,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1992 DHS, 1998 DHS, 2005 DHS, 2015 DHS, 2019 DHS</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153">
+        <v>356</v>
+      </c>
+      <c r="B153" t="s">
+        <v>301</v>
+      </c>
+      <c r="C153" t="str">
+        <f>VLOOKUP(A153,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1992 DHS, 1998 DHS, 2005 DHS, 2015 DHS, 2019 DHS</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154">
+        <v>356</v>
+      </c>
+      <c r="B154" t="s">
+        <v>301</v>
+      </c>
+      <c r="C154" t="str">
+        <f>VLOOKUP(A154,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1992 DHS, 1998 DHS, 2005 DHS, 2015 DHS, 2019 DHS</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155">
+        <v>356</v>
+      </c>
+      <c r="B155" t="s">
+        <v>301</v>
+      </c>
+      <c r="C155" t="str">
+        <f>VLOOKUP(A155,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1992 DHS, 1998 DHS, 2005 DHS, 2015 DHS, 2019 DHS</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A156">
+        <v>356</v>
+      </c>
+      <c r="B156" t="s">
+        <v>301</v>
+      </c>
+      <c r="C156" t="str">
+        <f>VLOOKUP(A156,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1992 DHS, 1998 DHS, 2005 DHS, 2015 DHS, 2019 DHS</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157">
+        <v>356</v>
+      </c>
+      <c r="B157" t="s">
+        <v>301</v>
+      </c>
+      <c r="C157" t="str">
+        <f>VLOOKUP(A157,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1992 DHS, 1998 DHS, 2005 DHS, 2015 DHS, 2019 DHS</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158">
+        <v>356</v>
+      </c>
+      <c r="B158" t="s">
+        <v>301</v>
+      </c>
+      <c r="C158" t="str">
+        <f>VLOOKUP(A158,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1992 DHS, 1998 DHS, 2005 DHS, 2015 DHS, 2019 DHS</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A159">
+        <v>356</v>
+      </c>
+      <c r="B159" t="s">
+        <v>301</v>
+      </c>
+      <c r="C159" t="str">
+        <f>VLOOKUP(A159,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1992 DHS, 1998 DHS, 2005 DHS, 2015 DHS, 2019 DHS</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A160">
+        <v>356</v>
+      </c>
+      <c r="B160" t="s">
+        <v>301</v>
+      </c>
+      <c r="C160" t="str">
+        <f>VLOOKUP(A160,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1992 DHS, 1998 DHS, 2005 DHS, 2015 DHS, 2019 DHS</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161">
+        <v>356</v>
+      </c>
+      <c r="B161" t="s">
+        <v>301</v>
+      </c>
+      <c r="C161" t="str">
+        <f>VLOOKUP(A161,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1992 DHS, 1998 DHS, 2005 DHS, 2015 DHS, 2019 DHS</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A162">
+        <v>356</v>
+      </c>
+      <c r="B162" t="s">
+        <v>301</v>
+      </c>
+      <c r="C162" t="str">
+        <f>VLOOKUP(A162,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1992 DHS, 1998 DHS, 2005 DHS, 2015 DHS, 2019 DHS</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163">
+        <v>356</v>
+      </c>
+      <c r="B163" t="s">
+        <v>301</v>
+      </c>
+      <c r="C163" t="str">
+        <f>VLOOKUP(A163,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1992 DHS, 1998 DHS, 2005 DHS, 2015 DHS, 2019 DHS</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A164">
+        <v>356</v>
+      </c>
+      <c r="B164" t="s">
+        <v>301</v>
+      </c>
+      <c r="C164" t="str">
+        <f>VLOOKUP(A164,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1992 DHS, 1998 DHS, 2005 DHS, 2015 DHS, 2019 DHS</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A165">
+        <v>356</v>
+      </c>
+      <c r="B165" t="s">
+        <v>301</v>
+      </c>
+      <c r="C165" t="str">
+        <f>VLOOKUP(A165,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1992 DHS, 1998 DHS, 2005 DHS, 2015 DHS, 2019 DHS</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166">
+        <v>356</v>
+      </c>
+      <c r="B166" t="s">
+        <v>301</v>
+      </c>
+      <c r="C166" t="str">
+        <f>VLOOKUP(A166,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1992 DHS, 1998 DHS, 2005 DHS, 2015 DHS, 2019 DHS</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A167">
+        <v>356</v>
+      </c>
+      <c r="B167" t="s">
+        <v>301</v>
+      </c>
+      <c r="C167" t="str">
+        <f>VLOOKUP(A167,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1992 DHS, 1998 DHS, 2005 DHS, 2015 DHS, 2019 DHS</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A168">
+        <v>356</v>
+      </c>
+      <c r="B168" t="s">
+        <v>301</v>
+      </c>
+      <c r="C168" t="str">
+        <f>VLOOKUP(A168,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1992 DHS, 1998 DHS, 2005 DHS, 2015 DHS, 2019 DHS</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A169">
+        <v>356</v>
+      </c>
+      <c r="B169" t="s">
+        <v>301</v>
+      </c>
+      <c r="C169" t="str">
+        <f>VLOOKUP(A169,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1992 DHS, 1998 DHS, 2005 DHS, 2015 DHS, 2019 DHS</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A170">
+        <v>356</v>
+      </c>
+      <c r="B170" t="s">
+        <v>301</v>
+      </c>
+      <c r="C170" t="str">
+        <f>VLOOKUP(A170,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1992 DHS, 1998 DHS, 2005 DHS, 2015 DHS, 2019 DHS</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A171">
+        <v>356</v>
+      </c>
+      <c r="B171" t="s">
+        <v>301</v>
+      </c>
+      <c r="C171" t="str">
+        <f>VLOOKUP(A171,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1992 DHS, 1998 DHS, 2005 DHS, 2015 DHS, 2019 DHS</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A172">
+        <v>360</v>
+      </c>
+      <c r="B172" t="s">
+        <v>304</v>
+      </c>
+      <c r="C172" t="str">
+        <f>VLOOKUP(A172,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1991 DHS, 1994 DHS, 1997 DHS, 2002 DHS, 2007 DHS, 2012 DHS, 2017 DHS</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A173">
+        <v>364</v>
+      </c>
+      <c r="B173" t="s">
+        <v>307</v>
+      </c>
+      <c r="C173" t="str">
+        <f>VLOOKUP(A173,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>Some data from proxy country: Jordan</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A174">
+        <v>368</v>
+      </c>
+      <c r="B174" t="s">
+        <v>310</v>
+      </c>
+      <c r="C174" t="str">
+        <f>VLOOKUP(A174,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2000 MICS, 2006 MICS, 2011 MICS, 2018 MICS Some data from proxy country: Turkey</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A175">
+        <v>372</v>
+      </c>
+      <c r="B175" t="s">
+        <v>313</v>
+      </c>
+      <c r="C175" t="e">
+        <f>VLOOKUP(A175,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A176">
+        <v>376</v>
+      </c>
+      <c r="B176" t="s">
+        <v>315</v>
+      </c>
+      <c r="C176" t="e">
+        <f>VLOOKUP(A176,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A177">
+        <v>380</v>
+      </c>
+      <c r="B177" t="s">
+        <v>318</v>
+      </c>
+      <c r="C177" t="e">
+        <f>VLOOKUP(A177,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A178">
+        <v>388</v>
+      </c>
+      <c r="B178" t="s">
+        <v>320</v>
+      </c>
+      <c r="C178" t="str">
+        <f>VLOOKUP(A178,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>Some data from proxy country: Dominican Republic</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A179">
+        <v>392</v>
+      </c>
+      <c r="B179" t="s">
+        <v>323</v>
+      </c>
+      <c r="C179" t="e">
+        <f>VLOOKUP(A179,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A180">
+        <v>400</v>
+      </c>
+      <c r="B180" t="s">
+        <v>326</v>
+      </c>
+      <c r="C180" t="str">
+        <f>VLOOKUP(A180,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1990 DHS, 1997 DHS, 2002 DHS, 2007 DHS, 2012 DHS, 2017 DHS, 2023 DHS</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A181">
+        <v>398</v>
+      </c>
+      <c r="B181" t="s">
+        <v>329</v>
+      </c>
+      <c r="C181" t="str">
+        <f>VLOOKUP(A181,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1995 DHS, 1999 DHS, 2006 MICS, 2010 MICS, 2015 MICS, 2024 MICS</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A182">
+        <v>404</v>
+      </c>
+      <c r="B182" t="s">
+        <v>332</v>
+      </c>
+      <c r="C182" t="str">
+        <f>VLOOKUP(A182,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1993 DHS, 1998 DHS, 2003 DHS, 2008 DHS, 2014 DHS, 2022 DHS</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A183" s="3">
+        <v>404</v>
+      </c>
+      <c r="B183" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="C183" t="str">
+        <f>VLOOKUP(A183,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1993 DHS, 1998 DHS, 2003 DHS, 2008 DHS, 2014 DHS, 2022 DHS</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A184" s="3">
+        <v>404</v>
+      </c>
+      <c r="B184" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="C184" t="str">
+        <f>VLOOKUP(A184,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1993 DHS, 1998 DHS, 2003 DHS, 2008 DHS, 2014 DHS, 2022 DHS</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A185" s="3">
+        <v>404</v>
+      </c>
+      <c r="B185" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="C185" t="str">
+        <f>VLOOKUP(A185,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1993 DHS, 1998 DHS, 2003 DHS, 2008 DHS, 2014 DHS, 2022 DHS</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A186" s="3">
+        <v>404</v>
+      </c>
+      <c r="B186" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="C186" t="str">
+        <f>VLOOKUP(A186,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1993 DHS, 1998 DHS, 2003 DHS, 2008 DHS, 2014 DHS, 2022 DHS</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A187" s="3">
+        <v>404</v>
+      </c>
+      <c r="B187" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="C187" t="str">
+        <f>VLOOKUP(A187,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1993 DHS, 1998 DHS, 2003 DHS, 2008 DHS, 2014 DHS, 2022 DHS</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A188" s="3">
+        <v>404</v>
+      </c>
+      <c r="B188" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="C188" t="str">
+        <f>VLOOKUP(A188,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1993 DHS, 1998 DHS, 2003 DHS, 2008 DHS, 2014 DHS, 2022 DHS</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A189" s="3">
+        <v>404</v>
+      </c>
+      <c r="B189" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="C189" t="str">
+        <f>VLOOKUP(A189,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1993 DHS, 1998 DHS, 2003 DHS, 2008 DHS, 2014 DHS, 2022 DHS</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A190" s="3">
+        <v>404</v>
+      </c>
+      <c r="B190" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="C190" t="str">
+        <f>VLOOKUP(A190,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1993 DHS, 1998 DHS, 2003 DHS, 2008 DHS, 2014 DHS, 2022 DHS</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A191">
+        <v>296</v>
+      </c>
+      <c r="B191" t="s">
+        <v>336</v>
+      </c>
+      <c r="C191" t="str">
+        <f>VLOOKUP(A191,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2018 MICS Some data from proxy country: Indonesia</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A192" s="5">
+        <v>412</v>
+      </c>
+      <c r="B192" s="5" t="s">
+        <v>984</v>
+      </c>
+      <c r="C192" t="e">
+        <f>VLOOKUP(A192,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A193">
+        <v>414</v>
+      </c>
+      <c r="B193" t="s">
+        <v>338</v>
+      </c>
+      <c r="C193" t="str">
+        <f>VLOOKUP(A193,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>Some data from proxy country: Turkey</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A194">
+        <v>417</v>
+      </c>
+      <c r="B194" t="s">
+        <v>341</v>
+      </c>
+      <c r="C194" t="str">
+        <f>VLOOKUP(A194,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1997 DHS, 2005 MICS, 2012 DHS, 2014 MICS, 2018 MICS, 2023 MICS</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A195">
+        <v>418</v>
+      </c>
+      <c r="B195" t="s">
+        <v>344</v>
+      </c>
+      <c r="C195" t="str">
+        <f>VLOOKUP(A195,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2011 MICS, 2017 MICS, 2023 MICS Some data from proxy country: Cambodia</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A196">
+        <v>428</v>
+      </c>
+      <c r="B196" t="s">
+        <v>348</v>
+      </c>
+      <c r="C196" t="str">
+        <f>VLOOKUP(A196,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>Some data from proxy country: Ukraine</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A197">
+        <v>422</v>
+      </c>
+      <c r="B197" t="s">
+        <v>352</v>
+      </c>
+      <c r="C197" t="str">
+        <f>VLOOKUP(A197,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>Some data from proxy country: Turkey</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A198">
+        <v>426</v>
+      </c>
+      <c r="B198" t="s">
+        <v>355</v>
+      </c>
+      <c r="C198" t="str">
+        <f>VLOOKUP(A198,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2004 DHS, 2009 DHS, 2014 DHS, 2018 MICS, 2023 DHS</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A199">
+        <v>430</v>
+      </c>
+      <c r="B199" t="s">
+        <v>362</v>
+      </c>
+      <c r="C199" t="str">
+        <f>VLOOKUP(A199,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2007 DHS, 2013 DHS, 2019 DHS</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A200">
+        <v>434</v>
+      </c>
+      <c r="B200" t="s">
+        <v>365</v>
+      </c>
+      <c r="C200" t="str">
+        <f>VLOOKUP(A200,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>Some data from proxy country: Egypt</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A201">
+        <v>440</v>
+      </c>
+      <c r="B201" t="s">
+        <v>368</v>
+      </c>
+      <c r="C201" t="str">
+        <f>VLOOKUP(A201,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>Some data from proxy country: Ukraine</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A202">
+        <v>442</v>
+      </c>
+      <c r="B202" t="s">
+        <v>373</v>
+      </c>
+      <c r="C202" t="e">
+        <f>VLOOKUP(A202,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A203">
+        <v>450</v>
+      </c>
+      <c r="B203" t="s">
+        <v>375</v>
+      </c>
+      <c r="C203" t="str">
+        <f>VLOOKUP(A203,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1992 DHS, 1997 DHS, 2003 DHS, 2008 DHS, 2018 MICS, 2021 DHS</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A204">
+        <v>454</v>
+      </c>
+      <c r="B204" t="s">
+        <v>379</v>
+      </c>
+      <c r="C204" t="str">
+        <f>VLOOKUP(A204,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1992 DHS, 2000 DHS, 2004 DHS, 2006 MICS, 2010 DHS, 2013 MICS, 2015 DHS, 2019 MICS, 2024 DHS</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A205">
+        <v>458</v>
+      </c>
+      <c r="B205" t="s">
+        <v>383</v>
+      </c>
+      <c r="C205" t="str">
+        <f>VLOOKUP(A205,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>Some data from proxy country: Thailand</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A206">
+        <v>462</v>
+      </c>
+      <c r="B206" t="s">
+        <v>386</v>
+      </c>
+      <c r="C206" t="str">
+        <f>VLOOKUP(A206,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2009 DHS, 2016 DHS</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A207">
+        <v>466</v>
+      </c>
+      <c r="B207" t="s">
+        <v>389</v>
+      </c>
+      <c r="C207" t="str">
+        <f>VLOOKUP(A207,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1995 DHS, 2001 DHS, 2006 DHS, 2012 DHS, 2015 MICS, 2018 DHS, 2023 DHS</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A208">
+        <v>470</v>
+      </c>
+      <c r="B208" t="s">
+        <v>391</v>
+      </c>
+      <c r="C208" t="e">
+        <f>VLOOKUP(A208,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A209">
+        <v>584</v>
+      </c>
+      <c r="B209" t="s">
+        <v>1354</v>
+      </c>
+      <c r="C209" t="e">
+        <f>VLOOKUP(A209,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A210">
+        <v>474</v>
+      </c>
+      <c r="B210" t="s">
+        <v>393</v>
+      </c>
+      <c r="C210" t="str">
+        <f>VLOOKUP(A210,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>Some data from proxy country: Dominican Republic</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A211">
+        <v>478</v>
+      </c>
+      <c r="B211" t="s">
+        <v>395</v>
+      </c>
+      <c r="C211" t="str">
+        <f>VLOOKUP(A211,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2011 MICS, 2015 MICS, 2019 DHS</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A212">
+        <v>480</v>
+      </c>
+      <c r="B212" t="s">
+        <v>398</v>
+      </c>
+      <c r="C212" t="str">
+        <f>VLOOKUP(A212,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>Some data from proxy country: Madagascar</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A213">
+        <v>175</v>
+      </c>
+      <c r="B213" t="s">
+        <v>401</v>
+      </c>
+      <c r="C213" t="str">
+        <f>VLOOKUP(A213,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>Some data from proxy country: Madagascar</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A214">
+        <v>484</v>
+      </c>
+      <c r="B214" t="s">
+        <v>404</v>
+      </c>
+      <c r="C214" t="str">
+        <f>VLOOKUP(A214,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2015 MICS Some data from proxy country: Guatemala</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A215">
+        <v>583</v>
+      </c>
+      <c r="B215" t="s">
+        <v>409</v>
+      </c>
+      <c r="C215" t="str">
+        <f>VLOOKUP(A215,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>Some data from proxy country: Indonesia</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A216">
+        <v>496</v>
+      </c>
+      <c r="B216" t="s">
+        <v>413</v>
+      </c>
+      <c r="C216" t="str">
+        <f>VLOOKUP(A216,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2000 MICS, 2005 MICS, 2010 MICS, 2013 MICS, 2018 MICS Some data from proxy country: Ukraine</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A217">
+        <v>499</v>
+      </c>
+      <c r="B217" t="s">
+        <v>416</v>
+      </c>
+      <c r="C217" t="str">
+        <f>VLOOKUP(A217,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2005 MICS, 2013 MICS, 2018 MICS Some data from proxy country: Armenia</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A218">
+        <v>504</v>
+      </c>
+      <c r="B218" t="s">
+        <v>419</v>
+      </c>
+      <c r="C218" t="str">
+        <f>VLOOKUP(A218,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1992 DHS, 2003 DHS</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A219">
+        <v>508</v>
+      </c>
+      <c r="B219" t="s">
+        <v>422</v>
+      </c>
+      <c r="C219" t="str">
+        <f>VLOOKUP(A219,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1997 DHS, 2003 DHS, 2008 MICS, 2011 DHS, 2015 DHS, 2022 DHS</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A220" s="3">
+        <v>508</v>
+      </c>
+      <c r="B220" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="C220" t="str">
+        <f>VLOOKUP(A220,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1997 DHS, 2003 DHS, 2008 MICS, 2011 DHS, 2015 DHS, 2022 DHS</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A221" s="3">
+        <v>508</v>
+      </c>
+      <c r="B221" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="C221" t="str">
+        <f>VLOOKUP(A221,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1997 DHS, 2003 DHS, 2008 MICS, 2011 DHS, 2015 DHS, 2022 DHS</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A222" s="3">
+        <v>508</v>
+      </c>
+      <c r="B222" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="C222" t="str">
+        <f>VLOOKUP(A222,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1997 DHS, 2003 DHS, 2008 MICS, 2011 DHS, 2015 DHS, 2022 DHS</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A223" s="3">
+        <v>508</v>
+      </c>
+      <c r="B223" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="C223" t="str">
+        <f>VLOOKUP(A223,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1997 DHS, 2003 DHS, 2008 MICS, 2011 DHS, 2015 DHS, 2022 DHS</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A224" s="3">
+        <v>508</v>
+      </c>
+      <c r="B224" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="C224" t="str">
+        <f>VLOOKUP(A224,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1997 DHS, 2003 DHS, 2008 MICS, 2011 DHS, 2015 DHS, 2022 DHS</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A225" s="3">
+        <v>508</v>
+      </c>
+      <c r="B225" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="C225" t="str">
+        <f>VLOOKUP(A225,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1997 DHS, 2003 DHS, 2008 MICS, 2011 DHS, 2015 DHS, 2022 DHS</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A226" s="3">
+        <v>508</v>
+      </c>
+      <c r="B226" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="C226" t="str">
+        <f>VLOOKUP(A226,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1997 DHS, 2003 DHS, 2008 MICS, 2011 DHS, 2015 DHS, 2022 DHS</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A227" s="3">
+        <v>508</v>
+      </c>
+      <c r="B227" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="C227" t="str">
+        <f>VLOOKUP(A227,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1997 DHS, 2003 DHS, 2008 MICS, 2011 DHS, 2015 DHS, 2022 DHS</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A228" s="3">
+        <v>508</v>
+      </c>
+      <c r="B228" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="C228" t="str">
+        <f>VLOOKUP(A228,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1997 DHS, 2003 DHS, 2008 MICS, 2011 DHS, 2015 DHS, 2022 DHS</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A229" s="3">
+        <v>508</v>
+      </c>
+      <c r="B229" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="C229" t="str">
+        <f>VLOOKUP(A229,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1997 DHS, 2003 DHS, 2008 MICS, 2011 DHS, 2015 DHS, 2022 DHS</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A230" s="3">
+        <v>508</v>
+      </c>
+      <c r="B230" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="C230" t="str">
+        <f>VLOOKUP(A230,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1997 DHS, 2003 DHS, 2008 MICS, 2011 DHS, 2015 DHS, 2022 DHS</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A231">
+        <v>104</v>
+      </c>
+      <c r="B231" t="s">
+        <v>425</v>
+      </c>
+      <c r="C231" t="str">
+        <f>VLOOKUP(A231,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2015 DHS</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A232">
+        <v>516</v>
+      </c>
+      <c r="B232" t="s">
+        <v>429</v>
+      </c>
+      <c r="C232" t="str">
+        <f>VLOOKUP(A232,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1992 DHS, 2000 DHS, 2006 DHS, 2013 DHS</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A233">
+        <v>520</v>
+      </c>
+      <c r="B233" t="s">
+        <v>1356</v>
+      </c>
+      <c r="C233" t="e">
+        <f>VLOOKUP(A233,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A234">
+        <v>524</v>
+      </c>
+      <c r="B234" t="s">
+        <v>432</v>
+      </c>
+      <c r="C234" t="str">
+        <f>VLOOKUP(A234,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1996 DHS, 2001 DHS, 2006 DHS, 2011 DHS, 2014 MICS, 2016 DHS, 2019 MICS, 2022 DHS, 2024 MICS</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A235">
+        <v>528</v>
+      </c>
+      <c r="B235" t="s">
+        <v>435</v>
+      </c>
+      <c r="C235" t="e">
+        <f>VLOOKUP(A235,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A236">
+        <v>540</v>
+      </c>
+      <c r="B236" t="s">
+        <v>437</v>
+      </c>
+      <c r="C236" t="str">
+        <f>VLOOKUP(A236,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>Some data from proxy country: Indonesia</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A237">
+        <v>554</v>
+      </c>
+      <c r="B237" t="s">
+        <v>439</v>
+      </c>
+      <c r="C237" t="e">
+        <f>VLOOKUP(A237,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A238">
+        <v>558</v>
+      </c>
+      <c r="B238" t="s">
+        <v>441</v>
+      </c>
+      <c r="C238" t="str">
+        <f>VLOOKUP(A238,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1998 DHS, 2001 DHS</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A239">
+        <v>562</v>
+      </c>
+      <c r="B239" t="s">
+        <v>444</v>
+      </c>
+      <c r="C239" t="str">
+        <f>VLOOKUP(A239,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1992 DHS, 1998 DHS, 2000 MICS, 2006 DHS, 2012 DHS</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A240">
+        <v>566</v>
+      </c>
+      <c r="B240" t="s">
+        <v>446</v>
+      </c>
+      <c r="C240" t="str">
+        <f>VLOOKUP(A240,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1990 DHS, 2003 DHS, 2007 MICS, 2008 DHS, 2011 MICS, 2013 DHS, 2016 MICS, 2018 DHS, 2021 MICS, 2024 DHS</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A241" s="3">
+        <v>566</v>
+      </c>
+      <c r="B241" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="C241" t="str">
+        <f>VLOOKUP(A241,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1990 DHS, 2003 DHS, 2007 MICS, 2008 DHS, 2011 MICS, 2013 DHS, 2016 MICS, 2018 DHS, 2021 MICS, 2024 DHS</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A242" s="3">
+        <v>566</v>
+      </c>
+      <c r="B242" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="C242" t="str">
+        <f>VLOOKUP(A242,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1990 DHS, 2003 DHS, 2007 MICS, 2008 DHS, 2011 MICS, 2013 DHS, 2016 MICS, 2018 DHS, 2021 MICS, 2024 DHS</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A243" s="3">
+        <v>566</v>
+      </c>
+      <c r="B243" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="C243" t="str">
+        <f>VLOOKUP(A243,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1990 DHS, 2003 DHS, 2007 MICS, 2008 DHS, 2011 MICS, 2013 DHS, 2016 MICS, 2018 DHS, 2021 MICS, 2024 DHS</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A244" s="3">
+        <v>566</v>
+      </c>
+      <c r="B244" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="C244" t="str">
+        <f>VLOOKUP(A244,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1990 DHS, 2003 DHS, 2007 MICS, 2008 DHS, 2011 MICS, 2013 DHS, 2016 MICS, 2018 DHS, 2021 MICS, 2024 DHS</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A245" s="3">
+        <v>566</v>
+      </c>
+      <c r="B245" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="C245" t="str">
+        <f>VLOOKUP(A245,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1990 DHS, 2003 DHS, 2007 MICS, 2008 DHS, 2011 MICS, 2013 DHS, 2016 MICS, 2018 DHS, 2021 MICS, 2024 DHS</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A246" s="3">
+        <v>566</v>
+      </c>
+      <c r="B246" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="C246" t="str">
+        <f>VLOOKUP(A246,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1990 DHS, 2003 DHS, 2007 MICS, 2008 DHS, 2011 MICS, 2013 DHS, 2016 MICS, 2018 DHS, 2021 MICS, 2024 DHS</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A247" s="3">
+        <v>566</v>
+      </c>
+      <c r="B247" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="C247" t="str">
+        <f>VLOOKUP(A247,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1990 DHS, 2003 DHS, 2007 MICS, 2008 DHS, 2011 MICS, 2013 DHS, 2016 MICS, 2018 DHS, 2021 MICS, 2024 DHS</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A248" s="3">
+        <v>566</v>
+      </c>
+      <c r="B248" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="C248" t="str">
+        <f>VLOOKUP(A248,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1990 DHS, 2003 DHS, 2007 MICS, 2008 DHS, 2011 MICS, 2013 DHS, 2016 MICS, 2018 DHS, 2021 MICS, 2024 DHS</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A249" s="3">
+        <v>566</v>
+      </c>
+      <c r="B249" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="C249" t="str">
+        <f>VLOOKUP(A249,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1990 DHS, 2003 DHS, 2007 MICS, 2008 DHS, 2011 MICS, 2013 DHS, 2016 MICS, 2018 DHS, 2021 MICS, 2024 DHS</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A250" s="3">
+        <v>566</v>
+      </c>
+      <c r="B250" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="C250" t="str">
+        <f>VLOOKUP(A250,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1990 DHS, 2003 DHS, 2007 MICS, 2008 DHS, 2011 MICS, 2013 DHS, 2016 MICS, 2018 DHS, 2021 MICS, 2024 DHS</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A251" s="3">
+        <v>566</v>
+      </c>
+      <c r="B251" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="C251" t="str">
+        <f>VLOOKUP(A251,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1990 DHS, 2003 DHS, 2007 MICS, 2008 DHS, 2011 MICS, 2013 DHS, 2016 MICS, 2018 DHS, 2021 MICS, 2024 DHS</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A252" s="3">
+        <v>566</v>
+      </c>
+      <c r="B252" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="C252" t="str">
+        <f>VLOOKUP(A252,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1990 DHS, 2003 DHS, 2007 MICS, 2008 DHS, 2011 MICS, 2013 DHS, 2016 MICS, 2018 DHS, 2021 MICS, 2024 DHS</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A253" s="3">
+        <v>566</v>
+      </c>
+      <c r="B253" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="C253" t="str">
+        <f>VLOOKUP(A253,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1990 DHS, 2003 DHS, 2007 MICS, 2008 DHS, 2011 MICS, 2013 DHS, 2016 MICS, 2018 DHS, 2021 MICS, 2024 DHS</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A254" s="3">
+        <v>566</v>
+      </c>
+      <c r="B254" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="C254" t="str">
+        <f>VLOOKUP(A254,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1990 DHS, 2003 DHS, 2007 MICS, 2008 DHS, 2011 MICS, 2013 DHS, 2016 MICS, 2018 DHS, 2021 MICS, 2024 DHS</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A255" s="3">
+        <v>566</v>
+      </c>
+      <c r="B255" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="C255" t="str">
+        <f>VLOOKUP(A255,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1990 DHS, 2003 DHS, 2007 MICS, 2008 DHS, 2011 MICS, 2013 DHS, 2016 MICS, 2018 DHS, 2021 MICS, 2024 DHS</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A256" s="3">
+        <v>566</v>
+      </c>
+      <c r="B256" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="C256" t="str">
+        <f>VLOOKUP(A256,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1990 DHS, 2003 DHS, 2007 MICS, 2008 DHS, 2011 MICS, 2013 DHS, 2016 MICS, 2018 DHS, 2021 MICS, 2024 DHS</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A257" s="3">
+        <v>566</v>
+      </c>
+      <c r="B257" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="C257" t="str">
+        <f>VLOOKUP(A257,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1990 DHS, 2003 DHS, 2007 MICS, 2008 DHS, 2011 MICS, 2013 DHS, 2016 MICS, 2018 DHS, 2021 MICS, 2024 DHS</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A258" s="3">
+        <v>566</v>
+      </c>
+      <c r="B258" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="C258" t="str">
+        <f>VLOOKUP(A258,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1990 DHS, 2003 DHS, 2007 MICS, 2008 DHS, 2011 MICS, 2013 DHS, 2016 MICS, 2018 DHS, 2021 MICS, 2024 DHS</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A259" s="3">
+        <v>566</v>
+      </c>
+      <c r="B259" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="C259" t="str">
+        <f>VLOOKUP(A259,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1990 DHS, 2003 DHS, 2007 MICS, 2008 DHS, 2011 MICS, 2013 DHS, 2016 MICS, 2018 DHS, 2021 MICS, 2024 DHS</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A260" s="3">
+        <v>566</v>
+      </c>
+      <c r="B260" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="C260" t="str">
+        <f>VLOOKUP(A260,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1990 DHS, 2003 DHS, 2007 MICS, 2008 DHS, 2011 MICS, 2013 DHS, 2016 MICS, 2018 DHS, 2021 MICS, 2024 DHS</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A261" s="3">
+        <v>566</v>
+      </c>
+      <c r="B261" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="C261" t="str">
+        <f>VLOOKUP(A261,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1990 DHS, 2003 DHS, 2007 MICS, 2008 DHS, 2011 MICS, 2013 DHS, 2016 MICS, 2018 DHS, 2021 MICS, 2024 DHS</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A262" s="3">
+        <v>566</v>
+      </c>
+      <c r="B262" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="C262" t="str">
+        <f>VLOOKUP(A262,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1990 DHS, 2003 DHS, 2007 MICS, 2008 DHS, 2011 MICS, 2013 DHS, 2016 MICS, 2018 DHS, 2021 MICS, 2024 DHS</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A263" s="3">
+        <v>566</v>
+      </c>
+      <c r="B263" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="C263" t="str">
+        <f>VLOOKUP(A263,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1990 DHS, 2003 DHS, 2007 MICS, 2008 DHS, 2011 MICS, 2013 DHS, 2016 MICS, 2018 DHS, 2021 MICS, 2024 DHS</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A264" s="3">
+        <v>566</v>
+      </c>
+      <c r="B264" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="C264" t="str">
+        <f>VLOOKUP(A264,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1990 DHS, 2003 DHS, 2007 MICS, 2008 DHS, 2011 MICS, 2013 DHS, 2016 MICS, 2018 DHS, 2021 MICS, 2024 DHS</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A265" s="3">
+        <v>566</v>
+      </c>
+      <c r="B265" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="C265" t="str">
+        <f>VLOOKUP(A265,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1990 DHS, 2003 DHS, 2007 MICS, 2008 DHS, 2011 MICS, 2013 DHS, 2016 MICS, 2018 DHS, 2021 MICS, 2024 DHS</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A266" s="3">
+        <v>566</v>
+      </c>
+      <c r="B266" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="C266" t="str">
+        <f>VLOOKUP(A266,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1990 DHS, 2003 DHS, 2007 MICS, 2008 DHS, 2011 MICS, 2013 DHS, 2016 MICS, 2018 DHS, 2021 MICS, 2024 DHS</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A267" s="3">
+        <v>566</v>
+      </c>
+      <c r="B267" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="C267" t="str">
+        <f>VLOOKUP(A267,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1990 DHS, 2003 DHS, 2007 MICS, 2008 DHS, 2011 MICS, 2013 DHS, 2016 MICS, 2018 DHS, 2021 MICS, 2024 DHS</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A268" s="3">
+        <v>566</v>
+      </c>
+      <c r="B268" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="C268" t="str">
+        <f>VLOOKUP(A268,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1990 DHS, 2003 DHS, 2007 MICS, 2008 DHS, 2011 MICS, 2013 DHS, 2016 MICS, 2018 DHS, 2021 MICS, 2024 DHS</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A269" s="3">
+        <v>566</v>
+      </c>
+      <c r="B269" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="C269" t="str">
+        <f>VLOOKUP(A269,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1990 DHS, 2003 DHS, 2007 MICS, 2008 DHS, 2011 MICS, 2013 DHS, 2016 MICS, 2018 DHS, 2021 MICS, 2024 DHS</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A270" s="3">
+        <v>566</v>
+      </c>
+      <c r="B270" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="C270" t="str">
+        <f>VLOOKUP(A270,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1990 DHS, 2003 DHS, 2007 MICS, 2008 DHS, 2011 MICS, 2013 DHS, 2016 MICS, 2018 DHS, 2021 MICS, 2024 DHS</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A271" s="3">
+        <v>566</v>
+      </c>
+      <c r="B271" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="C271" t="str">
+        <f>VLOOKUP(A271,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1990 DHS, 2003 DHS, 2007 MICS, 2008 DHS, 2011 MICS, 2013 DHS, 2016 MICS, 2018 DHS, 2021 MICS, 2024 DHS</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A272" s="3">
+        <v>566</v>
+      </c>
+      <c r="B272" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="C272" t="str">
+        <f>VLOOKUP(A272,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1990 DHS, 2003 DHS, 2007 MICS, 2008 DHS, 2011 MICS, 2013 DHS, 2016 MICS, 2018 DHS, 2021 MICS, 2024 DHS</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A273" s="3">
+        <v>566</v>
+      </c>
+      <c r="B273" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="C273" t="str">
+        <f>VLOOKUP(A273,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1990 DHS, 2003 DHS, 2007 MICS, 2008 DHS, 2011 MICS, 2013 DHS, 2016 MICS, 2018 DHS, 2021 MICS, 2024 DHS</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A274" s="3">
+        <v>566</v>
+      </c>
+      <c r="B274" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="C274" t="str">
+        <f>VLOOKUP(A274,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1990 DHS, 2003 DHS, 2007 MICS, 2008 DHS, 2011 MICS, 2013 DHS, 2016 MICS, 2018 DHS, 2021 MICS, 2024 DHS</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A275" s="3">
+        <v>566</v>
+      </c>
+      <c r="B275" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="C275" t="str">
+        <f>VLOOKUP(A275,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1990 DHS, 2003 DHS, 2007 MICS, 2008 DHS, 2011 MICS, 2013 DHS, 2016 MICS, 2018 DHS, 2021 MICS, 2024 DHS</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A276" s="3">
+        <v>566</v>
+      </c>
+      <c r="B276" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="C276" t="str">
+        <f>VLOOKUP(A276,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1990 DHS, 2003 DHS, 2007 MICS, 2008 DHS, 2011 MICS, 2013 DHS, 2016 MICS, 2018 DHS, 2021 MICS, 2024 DHS</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A277" s="3">
+        <v>566</v>
+      </c>
+      <c r="B277" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="C277" t="str">
+        <f>VLOOKUP(A277,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1990 DHS, 2003 DHS, 2007 MICS, 2008 DHS, 2011 MICS, 2013 DHS, 2016 MICS, 2018 DHS, 2021 MICS, 2024 DHS</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A278">
+        <v>570</v>
+      </c>
+      <c r="B278" t="s">
+        <v>1358</v>
+      </c>
+      <c r="C278" t="e">
+        <f>VLOOKUP(A278,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A279">
+        <v>578</v>
+      </c>
+      <c r="B279" t="s">
+        <v>453</v>
+      </c>
+      <c r="C279" t="e">
+        <f>VLOOKUP(A279,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A280">
+        <v>275</v>
+      </c>
+      <c r="B280" t="s">
+        <v>456</v>
+      </c>
+      <c r="C280" t="str">
+        <f>VLOOKUP(A280,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2014 MICS, 2019 MICS Some data from proxy country: Jordan</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A281">
+        <v>512</v>
+      </c>
+      <c r="B281" t="s">
+        <v>458</v>
+      </c>
+      <c r="C281" t="str">
+        <f>VLOOKUP(A281,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>Some data from proxy country: Turkey</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A282">
+        <v>586</v>
+      </c>
+      <c r="B282" t="s">
+        <v>461</v>
+      </c>
+      <c r="C282" t="str">
+        <f>VLOOKUP(A282,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1990 DHS, 2006 DHS, 2012 DHS, 2017 DHS</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A283">
+        <v>585</v>
+      </c>
+      <c r="B283" t="s">
+        <v>1360</v>
+      </c>
+      <c r="C283" t="e">
+        <f>VLOOKUP(A283,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A284">
+        <v>591</v>
+      </c>
+      <c r="B284" t="s">
+        <v>465</v>
+      </c>
+      <c r="C284" t="str">
+        <f>VLOOKUP(A284,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2013 MICS Some data from proxy country: Guatemala</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A285">
+        <v>598</v>
+      </c>
+      <c r="B285" t="s">
+        <v>469</v>
+      </c>
+      <c r="C285" t="str">
+        <f>VLOOKUP(A285,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2016 DHS</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A286">
+        <v>600</v>
+      </c>
+      <c r="B286" t="s">
+        <v>472</v>
+      </c>
+      <c r="C286" t="str">
+        <f>VLOOKUP(A286,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1990 DHS, 2016 MICS</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A287">
+        <v>604</v>
+      </c>
+      <c r="B287" t="s">
+        <v>476</v>
+      </c>
+      <c r="C287" t="str">
+        <f>VLOOKUP(A287,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1991 DHS, 1996 DHS, 2000 DHS, 2004 DHS, 2009 DHS, 2010 DHS, 2011 DHS, 2012 DHS</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A288">
+        <v>608</v>
+      </c>
+      <c r="B288" t="s">
+        <v>479</v>
+      </c>
+      <c r="C288" t="str">
+        <f>VLOOKUP(A288,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1993 DHS, 1998 DHS, 2003 DHS, 2008 DHS, 2013 DHS, 2017 DHS, 2022 DHS</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A289">
+        <v>616</v>
+      </c>
+      <c r="B289" t="s">
+        <v>482</v>
+      </c>
+      <c r="C289" t="str">
+        <f>VLOOKUP(A289,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>Some data from proxy country: Ukraine</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A290">
+        <v>620</v>
+      </c>
+      <c r="B290" t="s">
+        <v>486</v>
+      </c>
+      <c r="C290" t="e">
+        <f>VLOOKUP(A290,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A291">
+        <v>630</v>
+      </c>
+      <c r="B291" t="s">
+        <v>488</v>
+      </c>
+      <c r="C291" t="str">
+        <f>VLOOKUP(A291,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>Some data from proxy country: Dominican Republic</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A292">
+        <v>634</v>
+      </c>
+      <c r="B292" t="s">
+        <v>490</v>
+      </c>
+      <c r="C292" t="str">
+        <f>VLOOKUP(A292,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2012 MICS Some data from proxy country: Turkey</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A293">
+        <v>410</v>
+      </c>
+      <c r="B293" t="s">
+        <v>493</v>
+      </c>
+      <c r="C293" t="str">
+        <f>VLOOKUP(A293,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>Some data from proxy country: Indonesia</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A294">
+        <v>498</v>
+      </c>
+      <c r="B294" t="s">
+        <v>496</v>
+      </c>
+      <c r="C294" t="str">
+        <f>VLOOKUP(A294,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2005 DHS, 2012 MICS</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A295" s="3">
+        <v>498</v>
+      </c>
+      <c r="B295" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="C295" t="str">
+        <f>VLOOKUP(A295,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2005 DHS, 2012 MICS</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A296" s="3">
+        <v>498</v>
+      </c>
+      <c r="B296" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="C296" t="str">
+        <f>VLOOKUP(A296,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2005 DHS, 2012 MICS</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A297">
+        <v>638</v>
+      </c>
+      <c r="B297" t="s">
+        <v>499</v>
+      </c>
+      <c r="C297" t="str">
+        <f>VLOOKUP(A297,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>Some data from proxy country: Madagascar</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A298">
+        <v>642</v>
+      </c>
+      <c r="B298" t="s">
+        <v>501</v>
+      </c>
+      <c r="C298" t="str">
+        <f>VLOOKUP(A298,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>Some data from proxy country: Ukraine</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A299">
+        <v>643</v>
+      </c>
+      <c r="B299" t="s">
+        <v>504</v>
+      </c>
+      <c r="C299" t="str">
+        <f>VLOOKUP(A299,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>Some data from proxy country: Ukraine</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A300">
+        <v>646</v>
+      </c>
+      <c r="B300" t="s">
+        <v>507</v>
+      </c>
+      <c r="C300" t="str">
+        <f>VLOOKUP(A300,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1992 DHS, 2000 DHS, 2005 DHS, 2010 DHS, 2014 DHS, 2019 DHS</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A301">
+        <v>659</v>
+      </c>
+      <c r="B301" t="s">
+        <v>510</v>
+      </c>
+      <c r="C301" t="e">
+        <f>VLOOKUP(A301,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A302">
+        <v>662</v>
+      </c>
+      <c r="B302" t="s">
+        <v>512</v>
+      </c>
+      <c r="C302" t="str">
+        <f>VLOOKUP(A302,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2012 MICS Some data from proxy country: Dominican Republic</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A303">
+        <v>670</v>
+      </c>
+      <c r="B303" t="s">
+        <v>514</v>
+      </c>
+      <c r="C303" t="str">
+        <f>VLOOKUP(A303,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>Some data from proxy country: Dominican Republic</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A304">
+        <v>882</v>
+      </c>
+      <c r="B304" t="s">
+        <v>516</v>
+      </c>
+      <c r="C304" t="str">
+        <f>VLOOKUP(A304,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2019 MICS Some data from proxy country: Indonesia</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A305">
+        <v>5733</v>
+      </c>
+      <c r="B305" t="s">
+        <v>519</v>
+      </c>
+      <c r="C305" t="e">
+        <f>VLOOKUP(A305,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A306">
+        <v>678</v>
+      </c>
+      <c r="B306" t="s">
+        <v>520</v>
+      </c>
+      <c r="C306" t="str">
+        <f>VLOOKUP(A306,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2008 DHS, 2014 MICS, 2019 MICS</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A307">
+        <v>682</v>
+      </c>
+      <c r="B307" t="s">
+        <v>523</v>
+      </c>
+      <c r="C307" t="str">
+        <f>VLOOKUP(A307,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>Some data from proxy country: Turkey</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A308">
+        <v>686</v>
+      </c>
+      <c r="B308" t="s">
+        <v>526</v>
+      </c>
+      <c r="C308" t="str">
+        <f>VLOOKUP(A308,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1992 DHS, 1997 DHS, 2005 DHS, 2010 DHS, 2012 DHS, 2014 DHS, 2015 DHS, 2016 DHS, 2017 DHS, 2018 DHS, 2019 DHS, 2023 DHS</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A309">
+        <v>688</v>
+      </c>
+      <c r="B309" t="s">
+        <v>528</v>
+      </c>
+      <c r="C309" t="str">
+        <f>VLOOKUP(A309,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2010 MICS, 2014 MICS, 2019 MICS Some data from proxy country: Moldova</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A310">
+        <v>690</v>
+      </c>
+      <c r="B310" t="s">
+        <v>531</v>
+      </c>
+      <c r="C310" t="str">
+        <f>VLOOKUP(A310,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>Some data from proxy country: Madagascar</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A311">
+        <v>694</v>
+      </c>
+      <c r="B311" t="s">
+        <v>534</v>
+      </c>
+      <c r="C311" t="str">
+        <f>VLOOKUP(A311,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2000 MICS, 2005 MICS, 2008 DHS, 2010 MICS, 2013 DHS, 2017 MICS, 2019 DHS</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A312">
+        <v>702</v>
+      </c>
+      <c r="B312" t="s">
+        <v>538</v>
+      </c>
+      <c r="C312" t="str">
+        <f>VLOOKUP(A312,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>Some data from proxy country: Thailand</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A313">
+        <v>703</v>
+      </c>
+      <c r="B313" t="s">
+        <v>541</v>
+      </c>
+      <c r="C313" t="str">
+        <f>VLOOKUP(A313,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>Some data from proxy country: Ukraine</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A314">
+        <v>705</v>
+      </c>
+      <c r="B314" t="s">
+        <v>544</v>
+      </c>
+      <c r="C314" t="str">
+        <f>VLOOKUP(A314,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>Some data from proxy country: Moldova</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A315">
+        <v>90</v>
+      </c>
+      <c r="B315" t="s">
+        <v>547</v>
+      </c>
+      <c r="C315" t="str">
+        <f>VLOOKUP(A315,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>Some data from proxy country: Indonesia</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A316">
+        <v>706</v>
+      </c>
+      <c r="B316" t="s">
+        <v>550</v>
+      </c>
+      <c r="C316" t="str">
+        <f>VLOOKUP(A316,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2006 MICS Some data from proxy country: Ethiopia</v>
+      </c>
+    </row>
+    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A317">
+        <v>710</v>
+      </c>
+      <c r="B317" t="s">
+        <v>553</v>
+      </c>
+      <c r="C317" t="str">
+        <f>VLOOKUP(A317,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1998 DHS, 2016 DHS</v>
+      </c>
+    </row>
+    <row r="318" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A318">
+        <v>728</v>
+      </c>
+      <c r="B318" t="s">
+        <v>559</v>
+      </c>
+      <c r="C318" t="str">
+        <f>VLOOKUP(A318,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2010 MICS Some data from proxy country: Uganda</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A319">
+        <v>724</v>
+      </c>
+      <c r="B319" t="s">
+        <v>566</v>
+      </c>
+      <c r="C319" t="e">
+        <f>VLOOKUP(A319,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A320">
+        <v>144</v>
+      </c>
+      <c r="B320" t="s">
+        <v>568</v>
+      </c>
+      <c r="C320" t="str">
+        <f>VLOOKUP(A320,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>Some data from proxy country: India</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A321">
+        <v>729</v>
+      </c>
+      <c r="B321" t="s">
+        <v>572</v>
+      </c>
+      <c r="C321" t="str">
+        <f>VLOOKUP(A321,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2014 MICS Some data from proxy country: Uganda</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A322">
+        <v>740</v>
+      </c>
+      <c r="B322" t="s">
+        <v>574</v>
+      </c>
+      <c r="C322" t="str">
+        <f>VLOOKUP(A322,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1999 MICS, 2006 MICS, 2010 MICS, 2018 MICS Some data from proxy country: Brazil</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A323">
+        <v>748</v>
+      </c>
+      <c r="B323" t="s">
+        <v>983</v>
+      </c>
+      <c r="C323" t="str">
+        <f>VLOOKUP(A323,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2006 DHS, 2010 MICS, 2014 MICS, 2021 MICS</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A324">
+        <v>752</v>
+      </c>
+      <c r="B324" t="s">
+        <v>579</v>
+      </c>
+      <c r="C324" t="e">
+        <f>VLOOKUP(A324,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A325">
+        <v>756</v>
+      </c>
+      <c r="B325" t="s">
+        <v>582</v>
+      </c>
+      <c r="C325" t="e">
+        <f>VLOOKUP(A325,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A326">
+        <v>760</v>
+      </c>
+      <c r="B326" t="s">
+        <v>585</v>
+      </c>
+      <c r="C326" t="str">
+        <f>VLOOKUP(A326,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2006 MICS Some data from proxy country: Turkey</v>
+      </c>
+    </row>
+    <row r="327" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A327">
+        <v>762</v>
+      </c>
+      <c r="B327" t="s">
+        <v>588</v>
+      </c>
+      <c r="C327" t="str">
+        <f>VLOOKUP(A327,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2005 MICS, 2012 DHS, 2017 DHS, 2023 DHS</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A328">
+        <v>807</v>
+      </c>
+      <c r="B328" t="s">
+        <v>959</v>
+      </c>
+      <c r="C328" t="str">
+        <f>VLOOKUP(A328,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2011 MICS, 2018 MICS Some data from proxy country: Moldova</v>
+      </c>
+    </row>
+    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A329">
+        <v>764</v>
+      </c>
+      <c r="B329" t="s">
+        <v>592</v>
+      </c>
+      <c r="C329" t="str">
+        <f>VLOOKUP(A329,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2012 MICS, 2015 MICS, 2019 MICS, 2022 MICS Some data from proxy country: Viet Nam</v>
+      </c>
+    </row>
+    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A330">
+        <v>626</v>
+      </c>
+      <c r="B330" t="s">
+        <v>596</v>
+      </c>
+      <c r="C330" t="str">
+        <f>VLOOKUP(A330,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2009 DHS, 2016 DHS</v>
+      </c>
+    </row>
+    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A331">
+        <v>768</v>
+      </c>
+      <c r="B331" t="s">
+        <v>598</v>
+      </c>
+      <c r="C331" t="str">
+        <f>VLOOKUP(A331,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1998 DHS, 2006 MICS, 2010 MICS, 2013 DHS, 2017 MICS</v>
+      </c>
+    </row>
+    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A332" s="3">
+        <v>768</v>
+      </c>
+      <c r="B332" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="C332" t="str">
+        <f>VLOOKUP(A332,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1998 DHS, 2006 MICS, 2010 MICS, 2013 DHS, 2017 MICS</v>
+      </c>
+    </row>
+    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A333" s="3">
+        <v>768</v>
+      </c>
+      <c r="B333" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="C333" t="str">
+        <f>VLOOKUP(A333,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1998 DHS, 2006 MICS, 2010 MICS, 2013 DHS, 2017 MICS</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A334" s="3">
+        <v>768</v>
+      </c>
+      <c r="B334" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="C334" t="str">
+        <f>VLOOKUP(A334,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1998 DHS, 2006 MICS, 2010 MICS, 2013 DHS, 2017 MICS</v>
+      </c>
+    </row>
+    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A335" s="3">
+        <v>768</v>
+      </c>
+      <c r="B335" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="C335" t="str">
+        <f>VLOOKUP(A335,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1998 DHS, 2006 MICS, 2010 MICS, 2013 DHS, 2017 MICS</v>
+      </c>
+    </row>
+    <row r="336" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A336" s="3">
+        <v>768</v>
+      </c>
+      <c r="B336" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="C336" t="str">
+        <f>VLOOKUP(A336,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1998 DHS, 2006 MICS, 2010 MICS, 2013 DHS, 2017 MICS</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A337" s="3">
+        <v>768</v>
+      </c>
+      <c r="B337" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="C337" t="str">
+        <f>VLOOKUP(A337,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1998 DHS, 2006 MICS, 2010 MICS, 2013 DHS, 2017 MICS</v>
+      </c>
+    </row>
+    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A338">
+        <v>772</v>
+      </c>
+      <c r="B338" t="s">
+        <v>1362</v>
+      </c>
+      <c r="C338" t="e">
+        <f>VLOOKUP(A338,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A339">
+        <v>776</v>
+      </c>
+      <c r="B339" t="s">
+        <v>600</v>
+      </c>
+      <c r="C339" t="str">
+        <f>VLOOKUP(A339,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2019 MICS Some data from proxy country: Indonesia</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A340">
+        <v>780</v>
+      </c>
+      <c r="B340" t="s">
+        <v>603</v>
+      </c>
+      <c r="C340" t="str">
+        <f>VLOOKUP(A340,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2000 MICS, 2006 MICS, 2011 MICS, 2022 MICS Some data from proxy country: Dominican Republic</v>
+      </c>
+    </row>
+    <row r="341" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A341">
+        <v>788</v>
+      </c>
+      <c r="B341" t="s">
+        <v>606</v>
+      </c>
+      <c r="C341" t="str">
+        <f>VLOOKUP(A341,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2011 MICS, 2018 MICS, 2023 MICS Some data from proxy country: Morocco</v>
+      </c>
+    </row>
+    <row r="342" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A342">
+        <v>792</v>
+      </c>
+      <c r="B342" t="s">
+        <v>609</v>
+      </c>
+      <c r="C342" t="str">
+        <f>VLOOKUP(A342,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1993 DHS, 1998 DHS, 2003 DHS, 2013 DHS</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A343">
+        <v>795</v>
+      </c>
+      <c r="B343" t="s">
+        <v>612</v>
+      </c>
+      <c r="C343" t="str">
+        <f>VLOOKUP(A343,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2006 MICS, 2015 MICS, 2019 MICS, 2024 MICS Some data from proxy country: Kazakhstan</v>
+      </c>
+    </row>
+    <row r="344" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A344">
+        <v>798</v>
+      </c>
+      <c r="B344" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C344" t="e">
+        <f>VLOOKUP(A344,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="345" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A345">
+        <v>800</v>
+      </c>
+      <c r="B345" t="s">
+        <v>615</v>
+      </c>
+      <c r="C345" t="str">
+        <f>VLOOKUP(A345,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1995 DHS, 2000 DHS, 2006 DHS, 2011 DHS, 2016 DHS</v>
+      </c>
+    </row>
+    <row r="346" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A346" s="3">
+        <v>800</v>
+      </c>
+      <c r="B346" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="C346" t="str">
+        <f>VLOOKUP(A346,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1995 DHS, 2000 DHS, 2006 DHS, 2011 DHS, 2016 DHS</v>
+      </c>
+    </row>
+    <row r="347" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A347" s="3">
+        <v>800</v>
+      </c>
+      <c r="B347" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="C347" t="str">
+        <f>VLOOKUP(A347,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1995 DHS, 2000 DHS, 2006 DHS, 2011 DHS, 2016 DHS</v>
+      </c>
+    </row>
+    <row r="348" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A348" s="3">
+        <v>800</v>
+      </c>
+      <c r="B348" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="C348" t="str">
+        <f>VLOOKUP(A348,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1995 DHS, 2000 DHS, 2006 DHS, 2011 DHS, 2016 DHS</v>
+      </c>
+    </row>
+    <row r="349" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A349" s="3">
+        <v>800</v>
+      </c>
+      <c r="B349" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="C349" t="str">
+        <f>VLOOKUP(A349,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1995 DHS, 2000 DHS, 2006 DHS, 2011 DHS, 2016 DHS</v>
+      </c>
+    </row>
+    <row r="350" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A350" s="3">
+        <v>800</v>
+      </c>
+      <c r="B350" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="C350" t="str">
+        <f>VLOOKUP(A350,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1995 DHS, 2000 DHS, 2006 DHS, 2011 DHS, 2016 DHS</v>
+      </c>
+    </row>
+    <row r="351" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A351" s="3">
+        <v>800</v>
+      </c>
+      <c r="B351" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="C351" t="str">
+        <f>VLOOKUP(A351,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1995 DHS, 2000 DHS, 2006 DHS, 2011 DHS, 2016 DHS</v>
+      </c>
+    </row>
+    <row r="352" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A352" s="3">
+        <v>800</v>
+      </c>
+      <c r="B352" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="C352" t="str">
+        <f>VLOOKUP(A352,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1995 DHS, 2000 DHS, 2006 DHS, 2011 DHS, 2016 DHS</v>
+      </c>
+    </row>
+    <row r="353" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A353" s="3">
+        <v>800</v>
+      </c>
+      <c r="B353" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="C353" t="str">
+        <f>VLOOKUP(A353,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1995 DHS, 2000 DHS, 2006 DHS, 2011 DHS, 2016 DHS</v>
+      </c>
+    </row>
+    <row r="354" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A354" s="3">
+        <v>800</v>
+      </c>
+      <c r="B354" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="C354" t="str">
+        <f>VLOOKUP(A354,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1995 DHS, 2000 DHS, 2006 DHS, 2011 DHS, 2016 DHS</v>
+      </c>
+    </row>
+    <row r="355" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A355">
+        <v>804</v>
+      </c>
+      <c r="B355" t="s">
+        <v>619</v>
+      </c>
+      <c r="C355" t="str">
+        <f>VLOOKUP(A355,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2005 MICS, 2007 DHS, 2012 MICS</v>
+      </c>
+    </row>
+    <row r="356" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A356">
+        <v>784</v>
+      </c>
+      <c r="B356" t="s">
+        <v>622</v>
+      </c>
+      <c r="C356" t="str">
+        <f>VLOOKUP(A356,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>Some data from proxy country: Turkey</v>
+      </c>
+    </row>
+    <row r="357" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A357">
+        <v>826</v>
+      </c>
+      <c r="B357" t="s">
+        <v>625</v>
+      </c>
+      <c r="C357" t="e">
+        <f>VLOOKUP(A357,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="358" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A358">
+        <v>834</v>
+      </c>
+      <c r="B358" t="s">
+        <v>627</v>
+      </c>
+      <c r="C358" t="str">
+        <f>VLOOKUP(A358,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1991 DHS, 1996 DHS, 1999 DHS, 2004 DHS, 2010 DHS, 2015 DHS, 2022 DHS</v>
+      </c>
+    </row>
+    <row r="359" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A359" s="3">
+        <v>834</v>
+      </c>
+      <c r="B359" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="C359" t="str">
+        <f>VLOOKUP(A359,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1991 DHS, 1996 DHS, 1999 DHS, 2004 DHS, 2010 DHS, 2015 DHS, 2022 DHS</v>
+      </c>
+    </row>
+    <row r="360" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A360" s="3">
+        <v>834</v>
+      </c>
+      <c r="B360" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="C360" t="str">
+        <f>VLOOKUP(A360,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1991 DHS, 1996 DHS, 1999 DHS, 2004 DHS, 2010 DHS, 2015 DHS, 2022 DHS</v>
+      </c>
+    </row>
+    <row r="361" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A361" s="3">
+        <v>834</v>
+      </c>
+      <c r="B361" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="C361" t="str">
+        <f>VLOOKUP(A361,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1991 DHS, 1996 DHS, 1999 DHS, 2004 DHS, 2010 DHS, 2015 DHS, 2022 DHS</v>
+      </c>
+    </row>
+    <row r="362" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A362" s="3">
+        <v>834</v>
+      </c>
+      <c r="B362" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="C362" t="str">
+        <f>VLOOKUP(A362,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1991 DHS, 1996 DHS, 1999 DHS, 2004 DHS, 2010 DHS, 2015 DHS, 2022 DHS</v>
+      </c>
+    </row>
+    <row r="363" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A363" s="3">
+        <v>834</v>
+      </c>
+      <c r="B363" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="C363" t="str">
+        <f>VLOOKUP(A363,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1991 DHS, 1996 DHS, 1999 DHS, 2004 DHS, 2010 DHS, 2015 DHS, 2022 DHS</v>
+      </c>
+    </row>
+    <row r="364" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A364" s="3">
+        <v>834</v>
+      </c>
+      <c r="B364" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="C364" t="str">
+        <f>VLOOKUP(A364,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1991 DHS, 1996 DHS, 1999 DHS, 2004 DHS, 2010 DHS, 2015 DHS, 2022 DHS</v>
+      </c>
+    </row>
+    <row r="365" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A365" s="3">
+        <v>834</v>
+      </c>
+      <c r="B365" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="C365" t="str">
+        <f>VLOOKUP(A365,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1991 DHS, 1996 DHS, 1999 DHS, 2004 DHS, 2010 DHS, 2015 DHS, 2022 DHS</v>
+      </c>
+    </row>
+    <row r="366" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A366" s="3">
+        <v>834</v>
+      </c>
+      <c r="B366" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="C366" t="str">
+        <f>VLOOKUP(A366,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1991 DHS, 1996 DHS, 1999 DHS, 2004 DHS, 2010 DHS, 2015 DHS, 2022 DHS</v>
+      </c>
+    </row>
+    <row r="367" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A367" s="3">
+        <v>834</v>
+      </c>
+      <c r="B367" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="C367" t="str">
+        <f>VLOOKUP(A367,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1991 DHS, 1996 DHS, 1999 DHS, 2004 DHS, 2010 DHS, 2015 DHS, 2022 DHS</v>
+      </c>
+    </row>
+    <row r="368" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A368" s="3">
+        <v>834</v>
+      </c>
+      <c r="B368" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="C368" t="str">
+        <f>VLOOKUP(A368,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1991 DHS, 1996 DHS, 1999 DHS, 2004 DHS, 2010 DHS, 2015 DHS, 2022 DHS</v>
+      </c>
+    </row>
+    <row r="369" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A369" s="3">
+        <v>834</v>
+      </c>
+      <c r="B369" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="C369" t="str">
+        <f>VLOOKUP(A369,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1991 DHS, 1996 DHS, 1999 DHS, 2004 DHS, 2010 DHS, 2015 DHS, 2022 DHS</v>
+      </c>
+    </row>
+    <row r="370" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A370" s="3">
+        <v>834</v>
+      </c>
+      <c r="B370" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="C370" t="str">
+        <f>VLOOKUP(A370,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1991 DHS, 1996 DHS, 1999 DHS, 2004 DHS, 2010 DHS, 2015 DHS, 2022 DHS</v>
+      </c>
+    </row>
+    <row r="371" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A371" s="3">
+        <v>834</v>
+      </c>
+      <c r="B371" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="C371" t="str">
+        <f>VLOOKUP(A371,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1991 DHS, 1996 DHS, 1999 DHS, 2004 DHS, 2010 DHS, 2015 DHS, 2022 DHS</v>
+      </c>
+    </row>
+    <row r="372" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A372" s="3">
+        <v>834</v>
+      </c>
+      <c r="B372" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="C372" t="str">
+        <f>VLOOKUP(A372,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1991 DHS, 1996 DHS, 1999 DHS, 2004 DHS, 2010 DHS, 2015 DHS, 2022 DHS</v>
+      </c>
+    </row>
+    <row r="373" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A373" s="3">
+        <v>834</v>
+      </c>
+      <c r="B373" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="C373" t="str">
+        <f>VLOOKUP(A373,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1991 DHS, 1996 DHS, 1999 DHS, 2004 DHS, 2010 DHS, 2015 DHS, 2022 DHS</v>
+      </c>
+    </row>
+    <row r="374" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A374" s="3">
+        <v>834</v>
+      </c>
+      <c r="B374" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="C374" t="str">
+        <f>VLOOKUP(A374,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1991 DHS, 1996 DHS, 1999 DHS, 2004 DHS, 2010 DHS, 2015 DHS, 2022 DHS</v>
+      </c>
+    </row>
+    <row r="375" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A375" s="3">
+        <v>834</v>
+      </c>
+      <c r="B375" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="C375" t="str">
+        <f>VLOOKUP(A375,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1991 DHS, 1996 DHS, 1999 DHS, 2004 DHS, 2010 DHS, 2015 DHS, 2022 DHS</v>
+      </c>
+    </row>
+    <row r="376" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A376" s="3">
+        <v>834</v>
+      </c>
+      <c r="B376" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="C376" t="str">
+        <f>VLOOKUP(A376,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1991 DHS, 1996 DHS, 1999 DHS, 2004 DHS, 2010 DHS, 2015 DHS, 2022 DHS</v>
+      </c>
+    </row>
+    <row r="377" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A377" s="3">
+        <v>834</v>
+      </c>
+      <c r="B377" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="C377" t="str">
+        <f>VLOOKUP(A377,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1991 DHS, 1996 DHS, 1999 DHS, 2004 DHS, 2010 DHS, 2015 DHS, 2022 DHS</v>
+      </c>
+    </row>
+    <row r="378" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A378" s="3">
+        <v>834</v>
+      </c>
+      <c r="B378" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="C378" t="str">
+        <f>VLOOKUP(A378,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1991 DHS, 1996 DHS, 1999 DHS, 2004 DHS, 2010 DHS, 2015 DHS, 2022 DHS</v>
+      </c>
+    </row>
+    <row r="379" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A379" s="3">
+        <v>834</v>
+      </c>
+      <c r="B379" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="C379" t="str">
+        <f>VLOOKUP(A379,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1991 DHS, 1996 DHS, 1999 DHS, 2004 DHS, 2010 DHS, 2015 DHS, 2022 DHS</v>
+      </c>
+    </row>
+    <row r="380" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A380" s="3">
+        <v>834</v>
+      </c>
+      <c r="B380" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="C380" t="str">
+        <f>VLOOKUP(A380,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1991 DHS, 1996 DHS, 1999 DHS, 2004 DHS, 2010 DHS, 2015 DHS, 2022 DHS</v>
+      </c>
+    </row>
+    <row r="381" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A381" s="3">
+        <v>834</v>
+      </c>
+      <c r="B381" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="C381" t="str">
+        <f>VLOOKUP(A381,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1991 DHS, 1996 DHS, 1999 DHS, 2004 DHS, 2010 DHS, 2015 DHS, 2022 DHS</v>
+      </c>
+    </row>
+    <row r="382" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A382" s="3">
+        <v>834</v>
+      </c>
+      <c r="B382" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="C382" t="str">
+        <f>VLOOKUP(A382,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1991 DHS, 1996 DHS, 1999 DHS, 2004 DHS, 2010 DHS, 2015 DHS, 2022 DHS</v>
+      </c>
+    </row>
+    <row r="383" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A383" s="3">
+        <v>834</v>
+      </c>
+      <c r="B383" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="C383" t="str">
+        <f>VLOOKUP(A383,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1991 DHS, 1996 DHS, 1999 DHS, 2004 DHS, 2010 DHS, 2015 DHS, 2022 DHS</v>
+      </c>
+    </row>
+    <row r="384" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A384" s="3">
+        <v>834</v>
+      </c>
+      <c r="B384" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="C384" t="str">
+        <f>VLOOKUP(A384,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1991 DHS, 1996 DHS, 1999 DHS, 2004 DHS, 2010 DHS, 2015 DHS, 2022 DHS</v>
+      </c>
+    </row>
+    <row r="385" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A385" s="3">
+        <v>834</v>
+      </c>
+      <c r="B385" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="C385" t="str">
+        <f>VLOOKUP(A385,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1991 DHS, 1996 DHS, 1999 DHS, 2004 DHS, 2010 DHS, 2015 DHS, 2022 DHS</v>
+      </c>
+    </row>
+    <row r="386" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A386">
+        <v>840</v>
+      </c>
+      <c r="B386" t="s">
+        <v>631</v>
+      </c>
+      <c r="C386" t="e">
+        <f>VLOOKUP(A386,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="387" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A387">
+        <v>850</v>
+      </c>
+      <c r="B387" t="s">
+        <v>633</v>
+      </c>
+      <c r="C387" t="str">
+        <f>VLOOKUP(A387,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>Some data from proxy country: Dominican Republic</v>
+      </c>
+    </row>
+    <row r="388" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A388">
+        <v>858</v>
+      </c>
+      <c r="B388" t="s">
+        <v>636</v>
+      </c>
+      <c r="C388" t="str">
+        <f>VLOOKUP(A388,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>Some data from proxy country: Brazil</v>
+      </c>
+    </row>
+    <row r="389" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A389">
+        <v>860</v>
+      </c>
+      <c r="B389" t="s">
+        <v>639</v>
+      </c>
+      <c r="C389" t="str">
+        <f>VLOOKUP(A389,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1996 DHS, 2000 MICS, 2006 MICS, 2021 MICS</v>
+      </c>
+    </row>
+    <row r="390" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A390">
+        <v>548</v>
+      </c>
+      <c r="B390" t="s">
+        <v>642</v>
+      </c>
+      <c r="C390" t="str">
+        <f>VLOOKUP(A390,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>2007 MICS, 2023 MICS Some data from proxy country: Indonesia</v>
+      </c>
+    </row>
+    <row r="391" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A391">
+        <v>862</v>
+      </c>
+      <c r="B391" t="s">
+        <v>645</v>
+      </c>
+      <c r="C391" t="str">
+        <f>VLOOKUP(A391,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>Some data from proxy country: Brazil</v>
+      </c>
+    </row>
+    <row r="392" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A392">
+        <v>704</v>
+      </c>
+      <c r="B392" t="s">
+        <v>648</v>
+      </c>
+      <c r="C392" t="str">
+        <f>VLOOKUP(A392,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1997 DHS, 2000 MICS, 2002 DHS, 2006 MICS, 2010 MICS, 2013 MICS, 2020 MICS</v>
+      </c>
+    </row>
+    <row r="393" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A393">
+        <v>732</v>
+      </c>
+      <c r="B393" t="s">
+        <v>654</v>
+      </c>
+      <c r="C393" t="str">
+        <f>VLOOKUP(A393,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>Some data from proxy country: Morocco</v>
+      </c>
+    </row>
+    <row r="394" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A394">
+        <v>887</v>
+      </c>
+      <c r="B394" t="s">
+        <v>657</v>
+      </c>
+      <c r="C394" t="str">
+        <f>VLOOKUP(A394,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1991 DHS, 2013 DHS</v>
+      </c>
+    </row>
+    <row r="395" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A395">
+        <v>894</v>
+      </c>
+      <c r="B395" t="s">
+        <v>660</v>
+      </c>
+      <c r="C395" t="str">
+        <f>VLOOKUP(A395,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1992 DHS, 1996 DHS, 1999 MICS, 2001 DHS, 2007 DHS, 2013 DHS, 2018 DHS, 2024 DHS</v>
+      </c>
+    </row>
+    <row r="396" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A396" s="3">
+        <v>894</v>
+      </c>
+      <c r="B396" s="3" t="s">
+        <v>660</v>
+      </c>
+      <c r="C396" t="str">
+        <f>VLOOKUP(A396,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1992 DHS, 1996 DHS, 1999 MICS, 2001 DHS, 2007 DHS, 2013 DHS, 2018 DHS, 2024 DHS</v>
+      </c>
+    </row>
+    <row r="397" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A397" s="3">
+        <v>894</v>
+      </c>
+      <c r="B397" s="3" t="s">
+        <v>660</v>
+      </c>
+      <c r="C397" t="str">
+        <f>VLOOKUP(A397,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1992 DHS, 1996 DHS, 1999 MICS, 2001 DHS, 2007 DHS, 2013 DHS, 2018 DHS, 2024 DHS</v>
+      </c>
+    </row>
+    <row r="398" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A398" s="3">
+        <v>894</v>
+      </c>
+      <c r="B398" s="3" t="s">
+        <v>660</v>
+      </c>
+      <c r="C398" t="str">
+        <f>VLOOKUP(A398,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1992 DHS, 1996 DHS, 1999 MICS, 2001 DHS, 2007 DHS, 2013 DHS, 2018 DHS, 2024 DHS</v>
+      </c>
+    </row>
+    <row r="399" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A399" s="3">
+        <v>894</v>
+      </c>
+      <c r="B399" s="3" t="s">
+        <v>660</v>
+      </c>
+      <c r="C399" t="str">
+        <f>VLOOKUP(A399,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1992 DHS, 1996 DHS, 1999 MICS, 2001 DHS, 2007 DHS, 2013 DHS, 2018 DHS, 2024 DHS</v>
+      </c>
+    </row>
+    <row r="400" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A400" s="3">
+        <v>894</v>
+      </c>
+      <c r="B400" s="3" t="s">
+        <v>660</v>
+      </c>
+      <c r="C400" t="str">
+        <f>VLOOKUP(A400,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1992 DHS, 1996 DHS, 1999 MICS, 2001 DHS, 2007 DHS, 2013 DHS, 2018 DHS, 2024 DHS</v>
+      </c>
+    </row>
+    <row r="401" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A401" s="3">
+        <v>894</v>
+      </c>
+      <c r="B401" s="3" t="s">
+        <v>660</v>
+      </c>
+      <c r="C401" t="str">
+        <f>VLOOKUP(A401,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1992 DHS, 1996 DHS, 1999 MICS, 2001 DHS, 2007 DHS, 2013 DHS, 2018 DHS, 2024 DHS</v>
+      </c>
+    </row>
+    <row r="402" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A402" s="3">
+        <v>894</v>
+      </c>
+      <c r="B402" s="3" t="s">
+        <v>660</v>
+      </c>
+      <c r="C402" t="str">
+        <f>VLOOKUP(A402,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1992 DHS, 1996 DHS, 1999 MICS, 2001 DHS, 2007 DHS, 2013 DHS, 2018 DHS, 2024 DHS</v>
+      </c>
+    </row>
+    <row r="403" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A403" s="3">
+        <v>894</v>
+      </c>
+      <c r="B403" s="3" t="s">
+        <v>660</v>
+      </c>
+      <c r="C403" t="str">
+        <f>VLOOKUP(A403,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1992 DHS, 1996 DHS, 1999 MICS, 2001 DHS, 2007 DHS, 2013 DHS, 2018 DHS, 2024 DHS</v>
+      </c>
+    </row>
+    <row r="404" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A404" s="3">
+        <v>894</v>
+      </c>
+      <c r="B404" s="3" t="s">
+        <v>660</v>
+      </c>
+      <c r="C404" t="str">
+        <f>VLOOKUP(A404,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1992 DHS, 1996 DHS, 1999 MICS, 2001 DHS, 2007 DHS, 2013 DHS, 2018 DHS, 2024 DHS</v>
+      </c>
+    </row>
+    <row r="405" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A405" s="3">
+        <v>894</v>
+      </c>
+      <c r="B405" s="3" t="s">
+        <v>660</v>
+      </c>
+      <c r="C405" t="str">
+        <f>VLOOKUP(A405,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1992 DHS, 1996 DHS, 1999 MICS, 2001 DHS, 2007 DHS, 2013 DHS, 2018 DHS, 2024 DHS</v>
+      </c>
+    </row>
+    <row r="406" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A406">
+        <v>716</v>
+      </c>
+      <c r="B406" t="s">
+        <v>663</v>
+      </c>
+      <c r="C406" t="str">
+        <f>VLOOKUP(A406,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1994 DHS, 1999 DHS, 2005 DHS, 2009 MICS, 2010 DHS, 2014 MICS, 2015 DHS</v>
+      </c>
+    </row>
+    <row r="407" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A407" s="3">
+        <v>716</v>
+      </c>
+      <c r="B407" s="3" t="s">
+        <v>663</v>
+      </c>
+      <c r="C407" t="str">
+        <f>VLOOKUP(A407,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1994 DHS, 1999 DHS, 2005 DHS, 2009 MICS, 2010 DHS, 2014 MICS, 2015 DHS</v>
+      </c>
+    </row>
+    <row r="408" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A408" s="3">
+        <v>716</v>
+      </c>
+      <c r="B408" s="3" t="s">
+        <v>663</v>
+      </c>
+      <c r="C408" t="str">
+        <f>VLOOKUP(A408,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1994 DHS, 1999 DHS, 2005 DHS, 2009 MICS, 2010 DHS, 2014 MICS, 2015 DHS</v>
+      </c>
+    </row>
+    <row r="409" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A409" s="3">
+        <v>716</v>
+      </c>
+      <c r="B409" s="3" t="s">
+        <v>663</v>
+      </c>
+      <c r="C409" t="str">
+        <f>VLOOKUP(A409,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1994 DHS, 1999 DHS, 2005 DHS, 2009 MICS, 2010 DHS, 2014 MICS, 2015 DHS</v>
+      </c>
+    </row>
+    <row r="410" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A410" s="3">
+        <v>716</v>
+      </c>
+      <c r="B410" s="3" t="s">
+        <v>663</v>
+      </c>
+      <c r="C410" t="str">
+        <f>VLOOKUP(A410,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1994 DHS, 1999 DHS, 2005 DHS, 2009 MICS, 2010 DHS, 2014 MICS, 2015 DHS</v>
+      </c>
+    </row>
+    <row r="411" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A411" s="3">
+        <v>716</v>
+      </c>
+      <c r="B411" s="3" t="s">
+        <v>663</v>
+      </c>
+      <c r="C411" t="str">
+        <f>VLOOKUP(A411,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1994 DHS, 1999 DHS, 2005 DHS, 2009 MICS, 2010 DHS, 2014 MICS, 2015 DHS</v>
+      </c>
+    </row>
+    <row r="412" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A412" s="3">
+        <v>716</v>
+      </c>
+      <c r="B412" s="3" t="s">
+        <v>663</v>
+      </c>
+      <c r="C412" t="str">
+        <f>VLOOKUP(A412,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1994 DHS, 1999 DHS, 2005 DHS, 2009 MICS, 2010 DHS, 2014 MICS, 2015 DHS</v>
+      </c>
+    </row>
+    <row r="413" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A413" s="3">
+        <v>716</v>
+      </c>
+      <c r="B413" s="3" t="s">
+        <v>663</v>
+      </c>
+      <c r="C413" t="str">
+        <f>VLOOKUP(A413,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1994 DHS, 1999 DHS, 2005 DHS, 2009 MICS, 2010 DHS, 2014 MICS, 2015 DHS</v>
+      </c>
+    </row>
+    <row r="414" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A414" s="3">
+        <v>716</v>
+      </c>
+      <c r="B414" s="3" t="s">
+        <v>663</v>
+      </c>
+      <c r="C414" t="str">
+        <f>VLOOKUP(A414,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1994 DHS, 1999 DHS, 2005 DHS, 2009 MICS, 2010 DHS, 2014 MICS, 2015 DHS</v>
+      </c>
+    </row>
+    <row r="415" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A415" s="3">
+        <v>716</v>
+      </c>
+      <c r="B415" s="3" t="s">
+        <v>663</v>
+      </c>
+      <c r="C415" t="str">
+        <f>VLOOKUP(A415,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1994 DHS, 1999 DHS, 2005 DHS, 2009 MICS, 2010 DHS, 2014 MICS, 2015 DHS</v>
+      </c>
+    </row>
+    <row r="416" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A416" s="3">
+        <v>716</v>
+      </c>
+      <c r="B416" s="3" t="s">
+        <v>663</v>
+      </c>
+      <c r="C416" t="str">
+        <f>VLOOKUP(A416,[1]Sources!$A:$M,10,FALSE)</f>
+        <v>1994 DHS, 1999 DHS, 2005 DHS, 2009 MICS, 2010 DHS, 2014 MICS, 2015 DHS</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D46"/>
   <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -37543,7 +46960,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B22"/>
   <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -37734,7 +47151,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:Z23"/>
   <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -39512,7 +48929,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:D2"/>
   <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -39558,21 +48975,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010016926C673858A24ABD1F0F68A585E074" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c1931556e2b88a0a7c72249bbb83367d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="2c9bee02-199a-488a-b277-ba7f212fbf06" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="613c55408f90ae378c42e0f4853623d2" ns3:_="">
     <xsd:import namespace="2c9bee02-199a-488a-b277-ba7f212fbf06"/>
@@ -39774,31 +49176,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{639808B5-4725-4AE9-9DF1-1833AC18DC8B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="2c9bee02-199a-488a-b277-ba7f212fbf06"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3E04ADD-AF0C-45F3-A990-50A9A3A5EFA9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CDC31D53-F79F-4F2D-98CF-E26337BE3FD1}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -39814,4 +49207,28 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3E04ADD-AF0C-45F3-A990-50A9A3A5EFA9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{639808B5-4725-4AE9-9DF1-1833AC18DC8B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="2c9bee02-199a-488a-b277-ba7f212fbf06"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>